--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -715,7 +715,7 @@
     <t>Sporting Gijon</t>
   </si>
   <si>
-    <t>2026-09-25 00:27:30</t>
+    <t>2026-09-25 02:45:47</t>
   </si>
 </sst>
 </file>
@@ -1309,166 +1309,166 @@
         <v>174</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
+        <v>3.05</v>
+      </c>
+      <c r="I2">
         <v>3.2</v>
-      </c>
-      <c r="I2">
-        <v>3.45</v>
       </c>
       <c r="J2">
         <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O2">
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="Q2">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S2">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U2">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
         <v>25</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>15</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO2">
+        <v>18.5</v>
+      </c>
+      <c r="AP2">
         <v>22</v>
       </c>
-      <c r="AP2">
-        <v>21</v>
-      </c>
       <c r="AQ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR2">
+        <v>22</v>
+      </c>
+      <c r="AS2">
+        <v>28</v>
+      </c>
+      <c r="AT2">
+        <v>13.5</v>
+      </c>
+      <c r="AU2">
         <v>8.6</v>
       </c>
-      <c r="AS2">
-        <v>10.5</v>
-      </c>
-      <c r="AT2">
-        <v>12.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AV2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AX2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA2">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="BB2">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1551,10 +1551,10 @@
         <v>175</v>
       </c>
       <c r="F3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1566,7 +1566,7 @@
         <v>5.2</v>
       </c>
       <c r="K3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1575,34 +1575,34 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O3">
         <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R3">
         <v>1.7</v>
       </c>
       <c r="S3">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X3">
         <v>34</v>
@@ -1611,7 +1611,7 @@
         <v>34</v>
       </c>
       <c r="Z3">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>13</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE3">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK3">
         <v>14</v>
@@ -1662,10 +1662,10 @@
         <v>19.5</v>
       </c>
       <c r="AQ3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS3">
         <v>46</v>
@@ -1677,7 +1677,7 @@
         <v>11</v>
       </c>
       <c r="AV3">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AW3">
         <v>34</v>
@@ -1710,7 +1710,7 @@
         <v>4.9</v>
       </c>
       <c r="BG3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
@@ -1793,16 +1793,16 @@
         <v>176</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J4">
         <v>3.85</v>
@@ -1811,28 +1811,28 @@
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4">
         <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
         <v>1.6</v>
       </c>
       <c r="S4">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
         <v>1.56</v>
@@ -1841,10 +1841,10 @@
         <v>2.62</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>24</v>
@@ -1856,7 +1856,7 @@
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB4">
         <v>15.5</v>
@@ -1880,16 +1880,16 @@
         <v>15.5</v>
       </c>
       <c r="AI4">
+        <v>38</v>
+      </c>
+      <c r="AJ4">
         <v>36</v>
       </c>
-      <c r="AJ4">
-        <v>38</v>
-      </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM4">
         <v>60</v>
@@ -1901,19 +1901,19 @@
         <v>19.5</v>
       </c>
       <c r="AP4">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU4">
         <v>8.6</v>
@@ -1922,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX4">
         <v>16</v>
@@ -1934,19 +1934,19 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4">
         <v>11</v>
@@ -1958,7 +1958,7 @@
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4">
         <v>8.6</v>
@@ -1979,13 +1979,13 @@
         <v>5</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4">
         <v>13.5</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS4">
         <v>19.5</v>
@@ -2009,7 +2009,7 @@
         <v>22</v>
       </c>
       <c r="BZ4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA4">
         <v>13.5</v>
@@ -2035,7 +2035,7 @@
         <v>177</v>
       </c>
       <c r="F5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G5">
         <v>1.57</v>
@@ -2044,37 +2044,37 @@
         <v>6.2</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T5">
         <v>1.76</v>
@@ -2083,7 +2083,7 @@
         <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
         <v>2.74</v>
@@ -2092,28 +2092,28 @@
         <v>25</v>
       </c>
       <c r="Y5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA5">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
         <v>11</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -2122,40 +2122,40 @@
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
         <v>6.4</v>
       </c>
       <c r="AO5">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
         <v>23</v>
       </c>
       <c r="AR5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS5">
+        <v>44</v>
+      </c>
+      <c r="AT5">
         <v>9.6</v>
-      </c>
-      <c r="AT5">
-        <v>9.4</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2164,19 +2164,19 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="AX5">
         <v>9.4</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BB5">
         <v>12.5</v>
@@ -2185,16 +2185,16 @@
         <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE5">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2283,10 +2283,10 @@
         <v>2.62</v>
       </c>
       <c r="H6">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -2295,7 +2295,7 @@
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -2304,19 +2304,19 @@
         <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
         <v>1.56</v>
@@ -2325,7 +2325,7 @@
         <v>2.62</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
         <v>1.62</v>
@@ -2337,22 +2337,22 @@
         <v>17</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB6">
         <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6">
         <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF6">
         <v>21</v>
@@ -2379,7 +2379,7 @@
         <v>65</v>
       </c>
       <c r="AN6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO6">
         <v>17.5</v>
@@ -2394,10 +2394,10 @@
         <v>20</v>
       </c>
       <c r="AS6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU6">
         <v>8.199999999999999</v>
@@ -2406,7 +2406,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
         <v>17</v>
@@ -2418,19 +2418,19 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6">
         <v>13</v>
@@ -2451,7 +2451,7 @@
         <v>6.6</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM6">
         <v>22</v>
@@ -2460,7 +2460,7 @@
         <v>6.8</v>
       </c>
       <c r="BO6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP6">
         <v>19.5</v>
@@ -2472,7 +2472,7 @@
         <v>29</v>
       </c>
       <c r="BS6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
@@ -2481,7 +2481,7 @@
         <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BW6">
         <v>14.5</v>
@@ -2493,7 +2493,7 @@
         <v>20</v>
       </c>
       <c r="BZ6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="CA6">
         <v>13</v>
@@ -2519,22 +2519,22 @@
         <v>179</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G7">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2543,7 +2543,7 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
         <v>1.32</v>
@@ -2552,7 +2552,7 @@
         <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2561,16 +2561,16 @@
         <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U7">
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2642,7 +2642,7 @@
         <v>1.25</v>
       </c>
       <c r="AU7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV7">
         <v>8.800000000000001</v>
@@ -2764,19 +2764,19 @@
         <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H8">
         <v>3.25</v>
       </c>
       <c r="I8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2794,7 +2794,7 @@
         <v>2.04</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R8">
         <v>1.34</v>
@@ -2803,16 +2803,16 @@
         <v>3</v>
       </c>
       <c r="T8">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8">
         <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2872,7 +2872,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ8">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="AR8">
         <v>2.5</v>
@@ -2881,7 +2881,7 @@
         <v>2.62</v>
       </c>
       <c r="AT8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8">
         <v>6.2</v>
@@ -2917,7 +2917,7 @@
         <v>2.7</v>
       </c>
       <c r="BF8">
-        <v>2.42</v>
+        <v>12.5</v>
       </c>
       <c r="BG8">
         <v>2.56</v>
@@ -3003,13 +3003,13 @@
         <v>181</v>
       </c>
       <c r="F9">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G9">
         <v>2.52</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I9">
         <v>2.98</v>
@@ -3021,28 +3021,28 @@
         <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
         <v>1.62</v>
       </c>
       <c r="R9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T9">
         <v>1.57</v>
@@ -3054,7 +3054,7 @@
         <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X9">
         <v>24</v>
@@ -3093,13 +3093,13 @@
         <v>36</v>
       </c>
       <c r="AJ9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK9">
         <v>24</v>
       </c>
       <c r="AL9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM9">
         <v>75</v>
@@ -3245,7 +3245,7 @@
         <v>182</v>
       </c>
       <c r="F10">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G10">
         <v>1.3</v>
@@ -3254,7 +3254,7 @@
         <v>10.5</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J10">
         <v>6.8</v>
@@ -3263,34 +3263,34 @@
         <v>7.6</v>
       </c>
       <c r="L10">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q10">
         <v>1.4</v>
       </c>
       <c r="R10">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="T10">
         <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
         <v>1.09</v>
@@ -3341,28 +3341,28 @@
         <v>32</v>
       </c>
       <c r="AL10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AQ10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AR10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AS10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AT10">
         <v>9.199999999999999</v>
@@ -3371,10 +3371,10 @@
         <v>11</v>
       </c>
       <c r="AV10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AW10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AX10">
         <v>7.4</v>
@@ -3386,7 +3386,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BB10">
         <v>7.6</v>
@@ -3395,16 +3395,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD10">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="BE10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BF10">
         <v>2.96</v>
       </c>
       <c r="BG10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3440,7 +3440,7 @@
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10">
         <v>1000</v>
@@ -3487,16 +3487,16 @@
         <v>183</v>
       </c>
       <c r="F11">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G11">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I11">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3505,148 +3505,148 @@
         <v>4.4</v>
       </c>
       <c r="L11">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="O11">
         <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q11">
         <v>1.46</v>
       </c>
       <c r="R11">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T11">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="U11">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y11">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z11">
+        <v>34</v>
+      </c>
+      <c r="AA11">
+        <v>60</v>
+      </c>
+      <c r="AB11">
+        <v>18</v>
+      </c>
+      <c r="AC11">
+        <v>11</v>
+      </c>
+      <c r="AD11">
+        <v>15.5</v>
+      </c>
+      <c r="AE11">
+        <v>34</v>
+      </c>
+      <c r="AF11">
+        <v>19.5</v>
+      </c>
+      <c r="AG11">
+        <v>12</v>
+      </c>
+      <c r="AH11">
+        <v>14.5</v>
+      </c>
+      <c r="AI11">
+        <v>32</v>
+      </c>
+      <c r="AJ11">
+        <v>30</v>
+      </c>
+      <c r="AK11">
+        <v>20</v>
+      </c>
+      <c r="AL11">
+        <v>25</v>
+      </c>
+      <c r="AM11">
         <v>44</v>
       </c>
-      <c r="AA11">
-        <v>75</v>
-      </c>
-      <c r="AB11">
-        <v>21</v>
-      </c>
-      <c r="AC11">
+      <c r="AN11">
+        <v>8.4</v>
+      </c>
+      <c r="AO11">
+        <v>17.5</v>
+      </c>
+      <c r="AP11">
+        <v>9</v>
+      </c>
+      <c r="AQ11">
+        <v>20</v>
+      </c>
+      <c r="AR11">
+        <v>22</v>
+      </c>
+      <c r="AS11">
+        <v>10</v>
+      </c>
+      <c r="AT11">
+        <v>15.5</v>
+      </c>
+      <c r="AU11">
+        <v>9.6</v>
+      </c>
+      <c r="AV11">
+        <v>13.5</v>
+      </c>
+      <c r="AW11">
+        <v>23</v>
+      </c>
+      <c r="AX11">
+        <v>17</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
         <v>12</v>
       </c>
-      <c r="AD11">
-        <v>19</v>
-      </c>
-      <c r="AE11">
-        <v>44</v>
-      </c>
-      <c r="AF11">
-        <v>23</v>
-      </c>
-      <c r="AG11">
-        <v>13</v>
-      </c>
-      <c r="AH11">
-        <v>16</v>
-      </c>
-      <c r="AI11">
-        <v>38</v>
-      </c>
-      <c r="AJ11">
-        <v>36</v>
-      </c>
-      <c r="AK11">
-        <v>23</v>
-      </c>
-      <c r="AL11">
-        <v>30</v>
-      </c>
-      <c r="AM11">
-        <v>50</v>
-      </c>
-      <c r="AN11">
-        <v>12</v>
-      </c>
-      <c r="AO11">
-        <v>21</v>
-      </c>
-      <c r="AP11">
-        <v>4.1</v>
-      </c>
-      <c r="AQ11">
-        <v>4</v>
-      </c>
-      <c r="AR11">
-        <v>4.2</v>
-      </c>
-      <c r="AS11">
-        <v>4.4</v>
-      </c>
-      <c r="AT11">
-        <v>15</v>
-      </c>
-      <c r="AU11">
-        <v>9.4</v>
-      </c>
-      <c r="AV11">
-        <v>12.5</v>
-      </c>
-      <c r="AW11">
-        <v>4.2</v>
-      </c>
-      <c r="AX11">
-        <v>11.5</v>
-      </c>
-      <c r="AY11">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11">
-        <v>11</v>
-      </c>
       <c r="BA11">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BB11">
         <v>17.5</v>
       </c>
       <c r="BC11">
+        <v>16.5</v>
+      </c>
+      <c r="BD11">
+        <v>21</v>
+      </c>
+      <c r="BE11">
+        <v>28</v>
+      </c>
+      <c r="BF11">
+        <v>7.4</v>
+      </c>
+      <c r="BG11">
         <v>15</v>
-      </c>
-      <c r="BD11">
-        <v>17.5</v>
-      </c>
-      <c r="BE11">
-        <v>4.2</v>
-      </c>
-      <c r="BF11">
-        <v>6.6</v>
-      </c>
-      <c r="BG11">
-        <v>14</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3729,16 +3729,16 @@
         <v>184</v>
       </c>
       <c r="F12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G12">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H12">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3747,28 +3747,28 @@
         <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="R12">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="S12">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T12">
         <v>1.48</v>
@@ -3777,10 +3777,10 @@
         <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3831,22 +3831,22 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12">
         <v>10.5</v>
       </c>
       <c r="AR12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AT12">
         <v>9.800000000000001</v>
@@ -3858,7 +3858,7 @@
         <v>9</v>
       </c>
       <c r="AW12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AX12">
         <v>9.4</v>
@@ -3870,25 +3870,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BA12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BB12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BC12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BE12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BF12">
         <v>8.4</v>
       </c>
       <c r="BG12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3971,7 +3971,7 @@
         <v>185</v>
       </c>
       <c r="F13">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G13">
         <v>3.35</v>
@@ -4004,7 +4004,7 @@
         <v>2.28</v>
       </c>
       <c r="Q13">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R13">
         <v>1.55</v>
@@ -4019,7 +4019,7 @@
         <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W13">
         <v>1.43</v>
@@ -4067,7 +4067,7 @@
         <v>36</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>1000</v>
@@ -4228,37 +4228,37 @@
         <v>4.5</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S14">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T14">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U14">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V14">
         <v>1.19</v>
@@ -4267,10 +4267,10 @@
         <v>2.52</v>
       </c>
       <c r="X14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z14">
         <v>60</v>
@@ -4279,61 +4279,61 @@
         <v>170</v>
       </c>
       <c r="AB14">
+        <v>10</v>
+      </c>
+      <c r="AC14">
         <v>10.5</v>
       </c>
-      <c r="AC14">
-        <v>11</v>
-      </c>
       <c r="AD14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI14">
         <v>80</v>
       </c>
       <c r="AJ14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK14">
         <v>18.5</v>
       </c>
       <c r="AL14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM14">
         <v>110</v>
       </c>
       <c r="AN14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO14">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14">
         <v>18</v>
       </c>
       <c r="AR14">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS14">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT14">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14">
         <v>9.6</v>
@@ -4342,19 +4342,19 @@
         <v>17</v>
       </c>
       <c r="AW14">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX14">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ14">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA14">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB14">
         <v>13.5</v>
@@ -4363,16 +4363,16 @@
         <v>14</v>
       </c>
       <c r="BD14">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG14">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4697,22 +4697,22 @@
         <v>188</v>
       </c>
       <c r="F16">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
         <v>2.64</v>
       </c>
       <c r="H16">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I16">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J16">
         <v>3.7</v>
       </c>
       <c r="K16">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -5426,13 +5426,13 @@
         <v>2.28</v>
       </c>
       <c r="G19">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I19">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J19">
         <v>3.55</v>
@@ -5453,10 +5453,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q19">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5910,7 +5910,7 @@
         <v>2.04</v>
       </c>
       <c r="G21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H21">
         <v>3.05</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q21">
         <v>1.3</v>
@@ -8088,19 +8088,19 @@
         <v>2.5</v>
       </c>
       <c r="G30">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H30">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I30">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J30">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K30">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8115,10 +8115,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8127,10 +8127,10 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U30">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -8151,7 +8151,7 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
         <v>1000</v>
@@ -8181,7 +8181,7 @@
         <v>1000</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM30">
         <v>1000</v>
@@ -8193,58 +8193,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>1.09</v>
+        <v>8</v>
       </c>
       <c r="AR30">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
+        <v>1.01</v>
+      </c>
+      <c r="AU30">
+        <v>1.01</v>
+      </c>
+      <c r="AV30">
+        <v>1.01</v>
+      </c>
+      <c r="AW30">
+        <v>1.01</v>
+      </c>
+      <c r="AX30">
+        <v>1.01</v>
+      </c>
+      <c r="AY30">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30">
+        <v>1.01</v>
+      </c>
+      <c r="BA30">
+        <v>1.01</v>
+      </c>
+      <c r="BB30">
+        <v>1.01</v>
+      </c>
+      <c r="BC30">
+        <v>1.01</v>
+      </c>
+      <c r="BD30">
         <v>1.03</v>
       </c>
-      <c r="AU30">
-        <v>1.09</v>
-      </c>
-      <c r="AV30">
-        <v>1.09</v>
-      </c>
-      <c r="AW30">
-        <v>1.09</v>
-      </c>
-      <c r="AX30">
-        <v>1.09</v>
-      </c>
-      <c r="AY30">
-        <v>1.09</v>
-      </c>
-      <c r="AZ30">
-        <v>1.09</v>
-      </c>
-      <c r="BA30">
-        <v>1.09</v>
-      </c>
-      <c r="BB30">
-        <v>1.09</v>
-      </c>
-      <c r="BC30">
-        <v>1.09</v>
-      </c>
-      <c r="BD30">
-        <v>1.09</v>
-      </c>
       <c r="BE30">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -10511,13 +10511,13 @@
         <v>5.5</v>
       </c>
       <c r="H40">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="I40">
         <v>2.1</v>
       </c>
       <c r="J40">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K40">
         <v>4.1</v>
@@ -10747,16 +10747,16 @@
         <v>213</v>
       </c>
       <c r="F41">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G41">
         <v>2.26</v>
       </c>
       <c r="H41">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I41">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J41">
         <v>3.4</v>
@@ -10780,7 +10780,7 @@
         <v>1.92</v>
       </c>
       <c r="Q41">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>4.9</v>
       </c>
       <c r="K42">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11013,19 +11013,19 @@
         <v>1.06</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O42">
         <v>1.31</v>
       </c>
       <c r="P42">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q42">
         <v>1.89</v>
       </c>
       <c r="R42">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S42">
         <v>3.3</v>
@@ -11043,13 +11043,13 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y42">
         <v>23</v>
       </c>
       <c r="Z42">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA42">
         <v>310</v>
@@ -11085,7 +11085,7 @@
         <v>20</v>
       </c>
       <c r="AL42">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM42">
         <v>200</v>
@@ -11103,7 +11103,7 @@
         <v>19.5</v>
       </c>
       <c r="AR42">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS42">
         <v>10</v>
@@ -11118,7 +11118,7 @@
         <v>7.8</v>
       </c>
       <c r="AW42">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX42">
         <v>7.4</v>
@@ -11130,7 +11130,7 @@
         <v>7.8</v>
       </c>
       <c r="BA42">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB42">
         <v>11</v>
@@ -11255,7 +11255,7 @@
         <v>1.06</v>
       </c>
       <c r="N43">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>1.3</v>
@@ -11270,13 +11270,13 @@
         <v>1.39</v>
       </c>
       <c r="S43">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T43">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U43">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11285,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="X43">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y43">
         <v>21</v>
@@ -11324,7 +11324,7 @@
         <v>15.5</v>
       </c>
       <c r="AK43">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL43">
         <v>40</v>
@@ -11333,13 +11333,13 @@
         <v>150</v>
       </c>
       <c r="AN43">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO43">
         <v>130</v>
       </c>
       <c r="AP43">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ43">
         <v>17.5</v>
@@ -11354,7 +11354,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU43">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV43">
         <v>20</v>
@@ -11372,7 +11372,7 @@
         <v>20</v>
       </c>
       <c r="BA43">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB43">
         <v>12.5</v>
@@ -11384,13 +11384,13 @@
         <v>28</v>
       </c>
       <c r="BE43">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF43">
         <v>7.8</v>
       </c>
       <c r="BG43">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11473,16 +11473,16 @@
         <v>216</v>
       </c>
       <c r="F44">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G44">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H44">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I44">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J44">
         <v>2.82</v>
@@ -11503,10 +11503,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Q44">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11515,10 +11515,10 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="U44">
-        <v>1.06</v>
+        <v>1.58</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -11530,109 +11530,109 @@
         <v>6.6</v>
       </c>
       <c r="Y44">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z44">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA44">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB44">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC44">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD44">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE44">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF44">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG44">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH44">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI44">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ44">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK44">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL44">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM44">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN44">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO44">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP44">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ44">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="AR44">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="AS44">
-        <v>1.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT44">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="AU44">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="AV44">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AW44">
-        <v>1.18</v>
+        <v>8.4</v>
       </c>
       <c r="AX44">
-        <v>1.18</v>
+        <v>7</v>
       </c>
       <c r="AY44">
-        <v>1.18</v>
+        <v>6.4</v>
       </c>
       <c r="AZ44">
-        <v>1.18</v>
+        <v>7.4</v>
       </c>
       <c r="BA44">
-        <v>1.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB44">
-        <v>1.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC44">
-        <v>1.18</v>
+        <v>9</v>
       </c>
       <c r="BD44">
-        <v>1.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE44">
-        <v>1.18</v>
+        <v>9.4</v>
       </c>
       <c r="BF44">
-        <v>1.18</v>
+        <v>9</v>
       </c>
       <c r="BG44">
-        <v>1.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH44">
         <v>0</v>
@@ -11739,25 +11739,25 @@
         <v>1.05</v>
       </c>
       <c r="N45">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P45">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q45">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R45">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S45">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T45">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U45">
         <v>2</v>
@@ -11769,13 +11769,13 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y45">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z45">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA45">
         <v>13.5</v>
@@ -11811,22 +11811,22 @@
         <v>110</v>
       </c>
       <c r="AL45">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AM45">
         <v>140</v>
       </c>
       <c r="AN45">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AO45">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AP45">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ45">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR45">
         <v>8.199999999999999</v>
@@ -11853,7 +11853,7 @@
         <v>22</v>
       </c>
       <c r="AZ45">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA45">
         <v>27</v>
@@ -11862,7 +11862,7 @@
         <v>11.5</v>
       </c>
       <c r="BC45">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD45">
         <v>10.5</v>
@@ -11874,7 +11874,7 @@
         <v>11</v>
       </c>
       <c r="BG45">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -12683,19 +12683,19 @@
         <v>221</v>
       </c>
       <c r="F49">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H49">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I49">
         <v>4.5</v>
       </c>
       <c r="J49">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K49">
         <v>3.75</v>
@@ -12716,7 +12716,7 @@
         <v>1.89</v>
       </c>
       <c r="Q49">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -12925,16 +12925,16 @@
         <v>222</v>
       </c>
       <c r="F50">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="G50">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H50">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I50">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J50">
         <v>3.4</v>
@@ -12955,10 +12955,10 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q50">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -13893,22 +13893,22 @@
         <v>226</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G54">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H54">
         <v>3.7</v>
       </c>
       <c r="I54">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J54">
         <v>3.8</v>
       </c>
       <c r="K54">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -13926,7 +13926,7 @@
         <v>2.16</v>
       </c>
       <c r="Q54">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14144,10 +14144,10 @@
         <v>4.9</v>
       </c>
       <c r="I55">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="J55">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K55">
         <v>4.6</v>
@@ -14383,13 +14383,13 @@
         <v>1.46</v>
       </c>
       <c r="H56">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I56">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J56">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K56">
         <v>5.8</v>
@@ -14401,13 +14401,13 @@
         <v>1.03</v>
       </c>
       <c r="N56">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>1.17</v>
       </c>
       <c r="P56">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q56">
         <v>1.51</v>
@@ -14416,10 +14416,10 @@
         <v>1.73</v>
       </c>
       <c r="S56">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T56">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U56">
         <v>2.28</v>
@@ -14434,7 +14434,7 @@
         <v>36</v>
       </c>
       <c r="Y56">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z56">
         <v>75</v>
@@ -14443,16 +14443,16 @@
         <v>210</v>
       </c>
       <c r="AB56">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC56">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD56">
         <v>29</v>
       </c>
       <c r="AE56">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF56">
         <v>11.5</v>
@@ -14464,10 +14464,10 @@
         <v>23</v>
       </c>
       <c r="AI56">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ56">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK56">
         <v>14.5</v>
@@ -14476,34 +14476,34 @@
         <v>26</v>
       </c>
       <c r="AM56">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN56">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AO56">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP56">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ56">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="AR56">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS56">
         <v>10.5</v>
       </c>
       <c r="AT56">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU56">
         <v>12</v>
       </c>
       <c r="AV56">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AW56">
         <v>10</v>
@@ -14515,10 +14515,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ56">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA56">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB56">
         <v>12</v>
@@ -14533,10 +14533,10 @@
         <v>10</v>
       </c>
       <c r="BF56">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG56">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14643,16 +14643,16 @@
         <v>1.09</v>
       </c>
       <c r="N57">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O57">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P57">
         <v>1.8</v>
       </c>
       <c r="Q57">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R57">
         <v>1.31</v>
@@ -14661,10 +14661,10 @@
         <v>4</v>
       </c>
       <c r="T57">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U57">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
         <v>0</v>
@@ -14673,7 +14673,7 @@
         <v>0</v>
       </c>
       <c r="X57">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y57">
         <v>9.4</v>
@@ -14712,16 +14712,16 @@
         <v>65</v>
       </c>
       <c r="AK57">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL57">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM57">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN57">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO57">
         <v>26</v>
@@ -14730,13 +14730,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ57">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR57">
         <v>13.5</v>
       </c>
       <c r="AS57">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT57">
         <v>9.800000000000001</v>
@@ -14748,7 +14748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW57">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX57">
         <v>18</v>
@@ -14763,19 +14763,19 @@
         <v>36</v>
       </c>
       <c r="BB57">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC57">
         <v>32</v>
       </c>
       <c r="BD57">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE57">
         <v>10</v>
       </c>
       <c r="BF57">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="BG57">
         <v>21</v>
@@ -14861,13 +14861,13 @@
         <v>230</v>
       </c>
       <c r="F58">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G58">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H58">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I58">
         <v>2.82</v>
@@ -14885,7 +14885,7 @@
         <v>1.03</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O58">
         <v>1.18</v>
@@ -14906,7 +14906,7 @@
         <v>1.49</v>
       </c>
       <c r="U58">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V58">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>13.5</v>
       </c>
       <c r="AE58">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF58">
         <v>23</v>
@@ -14960,7 +14960,7 @@
         <v>32</v>
       </c>
       <c r="AM58">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN58">
         <v>13.5</v>
@@ -15005,7 +15005,7 @@
         <v>20</v>
       </c>
       <c r="BB58">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC58">
         <v>19</v>
@@ -15014,7 +15014,7 @@
         <v>19.5</v>
       </c>
       <c r="BE58">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BF58">
         <v>11.5</v>
@@ -15136,7 +15136,7 @@
         <v>1.05</v>
       </c>
       <c r="Q59">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15348,7 +15348,7 @@
         <v>2.04</v>
       </c>
       <c r="G60">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H60">
         <v>4.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -715,7 +715,7 @@
     <t>Sporting Gijon</t>
   </si>
   <si>
-    <t>2026-09-25 02:45:47</t>
+    <t>2026-09-25 03:59:38</t>
   </si>
 </sst>
 </file>
@@ -1309,10 +1309,10 @@
         <v>174</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>3.05</v>
@@ -1339,13 +1339,13 @@
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
         <v>1.59</v>
       </c>
       <c r="R2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S2">
         <v>2.46</v>
@@ -1354,10 +1354,10 @@
         <v>1.53</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
         <v>1.73</v>
@@ -1372,7 +1372,7 @@
         <v>25</v>
       </c>
       <c r="AA2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB2">
         <v>15</v>
@@ -1417,7 +1417,7 @@
         <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1444,7 +1444,7 @@
         <v>16</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
         <v>13</v>
@@ -1516,7 +1516,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1551,10 +1551,10 @@
         <v>175</v>
       </c>
       <c r="F3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1566,7 +1566,7 @@
         <v>5.2</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1590,7 +1590,7 @@
         <v>1.7</v>
       </c>
       <c r="S3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T3">
         <v>1.7</v>
@@ -1602,7 +1602,7 @@
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="X3">
         <v>34</v>
@@ -1796,13 +1796,13 @@
         <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
         <v>2.96</v>
       </c>
       <c r="I4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
         <v>3.85</v>
@@ -1811,7 +1811,7 @@
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
         <v>1.04</v>
@@ -1841,10 +1841,10 @@
         <v>2.62</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X4">
         <v>24</v>
@@ -1856,7 +1856,7 @@
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB4">
         <v>15.5</v>
@@ -1883,7 +1883,7 @@
         <v>38</v>
       </c>
       <c r="AJ4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK4">
         <v>23</v>
@@ -1901,7 +1901,7 @@
         <v>19.5</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
@@ -1958,7 +1958,7 @@
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ4">
         <v>8.6</v>
@@ -1979,13 +1979,13 @@
         <v>5</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
         <v>13.5</v>
       </c>
       <c r="BR4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS4">
         <v>19.5</v>
@@ -2009,7 +2009,7 @@
         <v>22</v>
       </c>
       <c r="BZ4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CA4">
         <v>13.5</v>
@@ -2035,7 +2035,7 @@
         <v>177</v>
       </c>
       <c r="F5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
         <v>1.57</v>
@@ -2074,10 +2074,10 @@
         <v>1.57</v>
       </c>
       <c r="S5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U5">
         <v>2.14</v>
@@ -2110,7 +2110,7 @@
         <v>25</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
@@ -2191,7 +2191,7 @@
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG5">
         <v>48</v>
@@ -2286,7 +2286,7 @@
         <v>2.8</v>
       </c>
       <c r="I6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -2295,7 +2295,7 @@
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -2304,13 +2304,13 @@
         <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -2460,7 +2460,7 @@
         <v>6.8</v>
       </c>
       <c r="BO6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP6">
         <v>19.5</v>
@@ -2472,7 +2472,7 @@
         <v>29</v>
       </c>
       <c r="BS6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
@@ -2481,7 +2481,7 @@
         <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BW6">
         <v>14.5</v>
@@ -2493,7 +2493,7 @@
         <v>20</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="CA6">
         <v>13</v>
@@ -2519,28 +2519,28 @@
         <v>179</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G7">
         <v>2.36</v>
       </c>
       <c r="H7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
         <v>3.5</v>
@@ -2561,13 +2561,13 @@
         <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
         <v>1.74</v>
@@ -2597,7 +2597,7 @@
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AG7">
         <v>23</v>
@@ -2627,19 +2627,19 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AQ7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AR7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AT7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AU7">
         <v>5.6</v>
@@ -2648,37 +2648,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
       </c>
       <c r="AY7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AZ7">
         <v>9.199999999999999</v>
       </c>
       <c r="BA7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BB7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BC7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BD7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BE7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF7">
         <v>9.6</v>
       </c>
       <c r="BG7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2767,40 +2767,40 @@
         <v>2.38</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M8">
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
         <v>1.68</v>
@@ -2809,7 +2809,7 @@
         <v>2.16</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
         <v>1.72</v>
@@ -2869,7 +2869,7 @@
         <v>50</v>
       </c>
       <c r="AP8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AQ8">
         <v>10</v>
@@ -2878,7 +2878,7 @@
         <v>2.5</v>
       </c>
       <c r="AS8">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AT8">
         <v>8.800000000000001</v>
@@ -2890,37 +2890,37 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AX8">
         <v>11.5</v>
       </c>
       <c r="AY8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BB8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BC8">
         <v>2.5</v>
       </c>
       <c r="BD8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BE8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BF8">
         <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3033,19 +3033,19 @@
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
         <v>1.62</v>
       </c>
       <c r="R9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U9">
         <v>2.56</v>
@@ -3093,7 +3093,7 @@
         <v>36</v>
       </c>
       <c r="AJ9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK9">
         <v>24</v>
@@ -3245,7 +3245,7 @@
         <v>182</v>
       </c>
       <c r="F10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G10">
         <v>1.3</v>
@@ -3287,7 +3287,7 @@
         <v>2</v>
       </c>
       <c r="T10">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
         <v>2.08</v>
@@ -3299,112 +3299,112 @@
         <v>4.3</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AB10">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AG10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ10">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AK10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP10">
-        <v>1.96</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10">
-        <v>1.96</v>
+        <v>9</v>
       </c>
       <c r="AR10">
-        <v>1.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10">
-        <v>1.96</v>
+        <v>10</v>
       </c>
       <c r="AT10">
+        <v>12.5</v>
+      </c>
+      <c r="AU10">
+        <v>15</v>
+      </c>
+      <c r="AV10">
+        <v>8.6</v>
+      </c>
+      <c r="AW10">
+        <v>10</v>
+      </c>
+      <c r="AX10">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU10">
-        <v>11</v>
-      </c>
-      <c r="AV10">
-        <v>1.96</v>
-      </c>
-      <c r="AW10">
-        <v>1.96</v>
-      </c>
-      <c r="AX10">
-        <v>7.4</v>
-      </c>
       <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
         <v>8</v>
       </c>
-      <c r="AZ10">
-        <v>18.5</v>
-      </c>
       <c r="BA10">
-        <v>1.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BC10">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BD10">
-        <v>1.96</v>
+        <v>8</v>
       </c>
       <c r="BE10">
-        <v>1.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="BG10">
-        <v>1.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3487,16 +3487,16 @@
         <v>183</v>
       </c>
       <c r="F11">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H11">
         <v>3.25</v>
       </c>
       <c r="I11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3511,7 +3511,7 @@
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>1.15</v>
@@ -3520,28 +3520,28 @@
         <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R11">
         <v>1.85</v>
       </c>
       <c r="S11">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T11">
         <v>1.45</v>
       </c>
       <c r="U11">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.83</v>
       </c>
       <c r="X11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y11">
         <v>24</v>
@@ -3559,10 +3559,10 @@
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF11">
         <v>19.5</v>
@@ -3580,10 +3580,10 @@
         <v>30</v>
       </c>
       <c r="AK11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM11">
         <v>44</v>
@@ -3592,19 +3592,19 @@
         <v>8.4</v>
       </c>
       <c r="AO11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP11">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AQ11">
         <v>20</v>
       </c>
       <c r="AR11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AT11">
         <v>15.5</v>
@@ -3625,25 +3625,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC11">
         <v>16.5</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG11">
         <v>15</v>
@@ -3732,7 +3732,7 @@
         <v>2.26</v>
       </c>
       <c r="G12">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -3762,133 +3762,133 @@
         <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R12">
         <v>1.63</v>
       </c>
       <c r="S12">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T12">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
         <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB12">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AC12">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG12">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH12">
+        <v>16</v>
+      </c>
+      <c r="AI12">
+        <v>38</v>
+      </c>
+      <c r="AJ12">
+        <v>34</v>
+      </c>
+      <c r="AK12">
+        <v>23</v>
+      </c>
+      <c r="AL12">
+        <v>32</v>
+      </c>
+      <c r="AM12">
         <v>65</v>
       </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
       <c r="AN12">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP12">
-        <v>1.26</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR12">
-        <v>1.26</v>
+        <v>7</v>
       </c>
       <c r="AS12">
-        <v>1.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AU12">
+        <v>9</v>
+      </c>
+      <c r="AV12">
+        <v>12</v>
+      </c>
+      <c r="AW12">
+        <v>7.4</v>
+      </c>
+      <c r="AX12">
+        <v>15.5</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>7.4</v>
+      </c>
+      <c r="BB12">
+        <v>7.4</v>
+      </c>
+      <c r="BC12">
+        <v>18</v>
+      </c>
+      <c r="BD12">
         <v>7</v>
       </c>
-      <c r="AV12">
-        <v>9</v>
-      </c>
-      <c r="AW12">
-        <v>1.26</v>
-      </c>
-      <c r="AX12">
-        <v>9.4</v>
-      </c>
-      <c r="AY12">
-        <v>8</v>
-      </c>
-      <c r="AZ12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA12">
-        <v>1.26</v>
-      </c>
-      <c r="BB12">
-        <v>1.26</v>
-      </c>
-      <c r="BC12">
-        <v>12</v>
-      </c>
-      <c r="BD12">
-        <v>1.26</v>
-      </c>
       <c r="BE12">
-        <v>1.26</v>
+        <v>8.4</v>
       </c>
       <c r="BF12">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG12">
-        <v>1.26</v>
+        <v>15.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3980,7 +3980,7 @@
         <v>2.24</v>
       </c>
       <c r="I13">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J13">
         <v>3.8</v>
@@ -3995,13 +3995,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O13">
         <v>1.2</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
         <v>1.6</v>
@@ -4010,127 +4010,127 @@
         <v>1.55</v>
       </c>
       <c r="S13">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T13">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
         <v>1.43</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y13">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="Z13">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA13">
+        <v>32</v>
+      </c>
+      <c r="AB13">
+        <v>17.5</v>
+      </c>
+      <c r="AC13">
+        <v>9.6</v>
+      </c>
+      <c r="AD13">
+        <v>12.5</v>
+      </c>
+      <c r="AE13">
+        <v>26</v>
+      </c>
+      <c r="AF13">
+        <v>29</v>
+      </c>
+      <c r="AG13">
+        <v>15</v>
+      </c>
+      <c r="AH13">
+        <v>16</v>
+      </c>
+      <c r="AI13">
         <v>34</v>
       </c>
-      <c r="AB13">
+      <c r="AJ13">
+        <v>60</v>
+      </c>
+      <c r="AK13">
+        <v>34</v>
+      </c>
+      <c r="AL13">
+        <v>38</v>
+      </c>
+      <c r="AM13">
+        <v>70</v>
+      </c>
+      <c r="AN13">
+        <v>24</v>
+      </c>
+      <c r="AO13">
+        <v>13</v>
+      </c>
+      <c r="AP13">
+        <v>19</v>
+      </c>
+      <c r="AQ13">
+        <v>12</v>
+      </c>
+      <c r="AR13">
+        <v>14.5</v>
+      </c>
+      <c r="AS13">
+        <v>6.4</v>
+      </c>
+      <c r="AT13">
+        <v>14.5</v>
+      </c>
+      <c r="AU13">
+        <v>8.4</v>
+      </c>
+      <c r="AV13">
+        <v>10</v>
+      </c>
+      <c r="AW13">
         <v>18</v>
       </c>
-      <c r="AC13">
-        <v>15</v>
-      </c>
-      <c r="AD13">
-        <v>23</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
+      <c r="AX13">
+        <v>21</v>
+      </c>
+      <c r="AY13">
+        <v>12</v>
+      </c>
+      <c r="AZ13">
+        <v>13.5</v>
+      </c>
+      <c r="BA13">
+        <v>6.6</v>
+      </c>
+      <c r="BB13">
         <v>38</v>
       </c>
-      <c r="AH13">
-        <v>17</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>36</v>
-      </c>
-      <c r="AL13">
-        <v>40</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>27</v>
-      </c>
-      <c r="AP13">
-        <v>1.82</v>
-      </c>
-      <c r="AQ13">
+      <c r="BC13">
+        <v>6.4</v>
+      </c>
+      <c r="BD13">
+        <v>6.6</v>
+      </c>
+      <c r="BE13">
+        <v>7.4</v>
+      </c>
+      <c r="BF13">
+        <v>17.5</v>
+      </c>
+      <c r="BG13">
         <v>11</v>
-      </c>
-      <c r="AR13">
-        <v>10.5</v>
-      </c>
-      <c r="AS13">
-        <v>1.72</v>
-      </c>
-      <c r="AT13">
-        <v>10.5</v>
-      </c>
-      <c r="AU13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV13">
-        <v>8</v>
-      </c>
-      <c r="AW13">
-        <v>17</v>
-      </c>
-      <c r="AX13">
-        <v>1.82</v>
-      </c>
-      <c r="AY13">
-        <v>9</v>
-      </c>
-      <c r="AZ13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA13">
-        <v>1.82</v>
-      </c>
-      <c r="BB13">
-        <v>1.82</v>
-      </c>
-      <c r="BC13">
-        <v>1.72</v>
-      </c>
-      <c r="BD13">
-        <v>1.73</v>
-      </c>
-      <c r="BE13">
-        <v>1.82</v>
-      </c>
-      <c r="BF13">
-        <v>16.5</v>
-      </c>
-      <c r="BG13">
-        <v>10</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4249,7 +4249,7 @@
         <v>1.7</v>
       </c>
       <c r="R14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S14">
         <v>2.78</v>
@@ -4273,7 +4273,7 @@
         <v>23</v>
       </c>
       <c r="Z14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA14">
         <v>170</v>
@@ -4321,25 +4321,25 @@
         <v>85</v>
       </c>
       <c r="AP14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AR14">
         <v>9.6</v>
       </c>
       <c r="AS14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT14">
         <v>8.800000000000001</v>
       </c>
       <c r="AU14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV14">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="AW14">
         <v>10</v>
@@ -4363,10 +4363,10 @@
         <v>14</v>
       </c>
       <c r="BD14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF14">
         <v>6.6</v>
@@ -4709,7 +4709,7 @@
         <v>2.98</v>
       </c>
       <c r="J16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
         <v>4.3</v>
@@ -5432,7 +5432,7 @@
         <v>3.15</v>
       </c>
       <c r="I19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J19">
         <v>3.55</v>
@@ -5456,7 +5456,7 @@
         <v>1.99</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>3.85</v>
       </c>
       <c r="Q21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -8085,22 +8085,22 @@
         <v>202</v>
       </c>
       <c r="F30">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G30">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I30">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J30">
         <v>2.94</v>
       </c>
       <c r="K30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8115,10 +8115,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q30">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8127,10 +8127,10 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U30">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -8139,112 +8139,112 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL30">
         <v>75</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -10505,10 +10505,10 @@
         <v>212</v>
       </c>
       <c r="F40">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="G40">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="H40">
         <v>1.89</v>
@@ -10517,7 +10517,7 @@
         <v>2.1</v>
       </c>
       <c r="J40">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K40">
         <v>4.1</v>
@@ -10777,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q41">
         <v>1.97</v>
@@ -10992,7 +10992,7 @@
         <v>1.49</v>
       </c>
       <c r="G42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H42">
         <v>7.6</v>
@@ -11019,10 +11019,10 @@
         <v>1.31</v>
       </c>
       <c r="P42">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q42">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R42">
         <v>1.39</v>
@@ -11085,7 +11085,7 @@
         <v>20</v>
       </c>
       <c r="AL42">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM42">
         <v>200</v>
@@ -11246,7 +11246,7 @@
         <v>4.3</v>
       </c>
       <c r="K43">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11264,7 +11264,7 @@
         <v>2.02</v>
       </c>
       <c r="Q43">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R43">
         <v>1.39</v>
@@ -11273,10 +11273,10 @@
         <v>3.15</v>
       </c>
       <c r="T43">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U43">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11291,7 +11291,7 @@
         <v>21</v>
       </c>
       <c r="Z43">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA43">
         <v>210</v>
@@ -11333,7 +11333,7 @@
         <v>150</v>
       </c>
       <c r="AN43">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO43">
         <v>130</v>
@@ -11506,7 +11506,7 @@
         <v>1.37</v>
       </c>
       <c r="Q44">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11515,10 +11515,10 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="U44">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -11545,10 +11545,10 @@
         <v>7.4</v>
       </c>
       <c r="AD44">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE44">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF44">
         <v>26</v>
@@ -11578,61 +11578,61 @@
         <v>150</v>
       </c>
       <c r="AO44">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP44">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AQ44">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AR44">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AS44">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AT44">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU44">
         <v>5.5</v>
       </c>
       <c r="AV44">
+        <v>6</v>
+      </c>
+      <c r="AW44">
+        <v>17</v>
+      </c>
+      <c r="AX44">
+        <v>6.6</v>
+      </c>
+      <c r="AY44">
         <v>6.2</v>
       </c>
-      <c r="AW44">
-        <v>8.4</v>
-      </c>
-      <c r="AX44">
-        <v>7</v>
-      </c>
-      <c r="AY44">
-        <v>6.4</v>
-      </c>
       <c r="AZ44">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA44">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB44">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BC44">
+        <v>23</v>
+      </c>
+      <c r="BD44">
         <v>9</v>
       </c>
-      <c r="BD44">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE44">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF44">
         <v>9</v>
       </c>
       <c r="BG44">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BH44">
         <v>0</v>
@@ -11715,19 +11715,19 @@
         <v>217</v>
       </c>
       <c r="F45">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G45">
         <v>8.199999999999999</v>
       </c>
       <c r="H45">
+        <v>1.47</v>
+      </c>
+      <c r="I45">
         <v>1.48</v>
       </c>
-      <c r="I45">
-        <v>1.49</v>
-      </c>
       <c r="J45">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K45">
         <v>5</v>
@@ -11745,10 +11745,10 @@
         <v>1.25</v>
       </c>
       <c r="P45">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q45">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R45">
         <v>1.52</v>
@@ -11769,7 +11769,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y45">
         <v>9.6</v>
@@ -11859,7 +11859,7 @@
         <v>27</v>
       </c>
       <c r="BB45">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC45">
         <v>10.5</v>
@@ -11868,25 +11868,25 @@
         <v>10.5</v>
       </c>
       <c r="BE45">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF45">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG45">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH45">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI45">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BJ45">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK45">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL45">
         <v>1000</v>
@@ -11895,46 +11895,46 @@
         <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO45">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BP45">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BQ45">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BR45">
         <v>1000</v>
       </c>
       <c r="BS45">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BT45">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BU45">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BV45">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BW45">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX45">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY45">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BZ45">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA45">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB45" t="s">
         <v>233</v>
@@ -12686,10 +12686,10 @@
         <v>2</v>
       </c>
       <c r="G49">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I49">
         <v>4.5</v>
@@ -12931,7 +12931,7 @@
         <v>2.02</v>
       </c>
       <c r="H50">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I50">
         <v>4.7</v>
@@ -13651,7 +13651,7 @@
         <v>225</v>
       </c>
       <c r="F53">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="G53">
         <v>2.4</v>
@@ -13660,13 +13660,13 @@
         <v>2.84</v>
       </c>
       <c r="I53">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J53">
         <v>3.75</v>
       </c>
       <c r="K53">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -14135,22 +14135,22 @@
         <v>227</v>
       </c>
       <c r="F55">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G55">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H55">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I55">
         <v>7.4</v>
       </c>
       <c r="J55">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K55">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14165,10 +14165,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q55">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14383,10 +14383,10 @@
         <v>1.46</v>
       </c>
       <c r="H56">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I56">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J56">
         <v>5.5</v>
@@ -14407,7 +14407,7 @@
         <v>1.17</v>
       </c>
       <c r="P56">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q56">
         <v>1.51</v>
@@ -14416,13 +14416,13 @@
         <v>1.73</v>
       </c>
       <c r="S56">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T56">
         <v>1.73</v>
       </c>
       <c r="U56">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V56">
         <v>0</v>
@@ -14533,7 +14533,7 @@
         <v>10</v>
       </c>
       <c r="BF56">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG56">
         <v>10</v>
@@ -14649,10 +14649,10 @@
         <v>1.39</v>
       </c>
       <c r="P57">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q57">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R57">
         <v>1.31</v>
@@ -14861,16 +14861,16 @@
         <v>230</v>
       </c>
       <c r="F58">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G58">
         <v>2.6</v>
       </c>
       <c r="H58">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I58">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J58">
         <v>3.85</v>
@@ -14906,7 +14906,7 @@
         <v>1.49</v>
       </c>
       <c r="U58">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V58">
         <v>0</v>
@@ -14990,7 +14990,7 @@
         <v>11.5</v>
       </c>
       <c r="AW58">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX58">
         <v>18</v>
@@ -15002,13 +15002,13 @@
         <v>12</v>
       </c>
       <c r="BA58">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB58">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC58">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD58">
         <v>19.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -715,7 +715,7 @@
     <t>Sporting Gijon</t>
   </si>
   <si>
-    <t>2026-09-25 03:59:38</t>
+    <t>2026-09-25 06:19:10</t>
   </si>
 </sst>
 </file>
@@ -1315,10 +1315,10 @@
         <v>2.34</v>
       </c>
       <c r="H2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1330,7 +1330,7 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
         <v>5.8</v>
@@ -1348,7 +1348,7 @@
         <v>1.65</v>
       </c>
       <c r="S2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T2">
         <v>1.53</v>
@@ -1357,25 +1357,25 @@
         <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y2">
         <v>18</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
         <v>9.800000000000001</v>
@@ -1396,13 +1396,13 @@
         <v>15</v>
       </c>
       <c r="AI2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ2">
         <v>34</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2">
         <v>27</v>
@@ -1411,13 +1411,13 @@
         <v>55</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
         <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1432,10 +1432,10 @@
         <v>13.5</v>
       </c>
       <c r="AU2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
         <v>19</v>
@@ -1450,7 +1450,7 @@
         <v>13</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BB2">
         <v>20</v>
@@ -1459,10 +1459,10 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BE2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
@@ -1474,13 +1474,13 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1492,13 +1492,13 @@
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1516,7 +1516,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1551,10 +1551,10 @@
         <v>175</v>
       </c>
       <c r="F3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1566,7 +1566,7 @@
         <v>5.2</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1593,7 +1593,7 @@
         <v>2.34</v>
       </c>
       <c r="T3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3">
         <v>2.3</v>
@@ -1602,13 +1602,13 @@
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="X3">
         <v>34</v>
       </c>
       <c r="Y3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z3">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK3">
         <v>14</v>
@@ -1677,7 +1677,7 @@
         <v>11</v>
       </c>
       <c r="AV3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AW3">
         <v>34</v>
@@ -1701,76 +1701,76 @@
         <v>12</v>
       </c>
       <c r="BD3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE3">
         <v>34</v>
       </c>
       <c r="BF3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG3">
         <v>34</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP3">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BT3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BV3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>233</v>
@@ -1856,7 +1856,7 @@
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB4">
         <v>15.5</v>
@@ -1880,85 +1880,85 @@
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN4">
         <v>13</v>
       </c>
       <c r="AO4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP4">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BB4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BE4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
         <v>11</v>
       </c>
       <c r="BG4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ4">
         <v>8.6</v>
@@ -1979,7 +1979,7 @@
         <v>5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
         <v>13.5</v>
@@ -2000,7 +2000,7 @@
         <v>22</v>
       </c>
       <c r="BW4">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX4">
         <v>30</v>
@@ -2035,22 +2035,22 @@
         <v>177</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
         <v>6.2</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -2068,7 +2068,7 @@
         <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
         <v>1.57</v>
@@ -2077,25 +2077,25 @@
         <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X5">
         <v>25</v>
       </c>
       <c r="Y5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -2107,7 +2107,7 @@
         <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -2143,16 +2143,16 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
         <v>23</v>
       </c>
       <c r="AR5">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AS5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
@@ -2161,46 +2161,46 @@
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW5">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BB5">
         <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD5">
         <v>19.5</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BF5">
         <v>5.9</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -2280,13 +2280,13 @@
         <v>2.48</v>
       </c>
       <c r="G6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
         <v>2.8</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -2295,13 +2295,13 @@
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -2313,7 +2313,7 @@
         <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S6">
         <v>2.6</v>
@@ -2322,7 +2322,7 @@
         <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2331,10 +2331,10 @@
         <v>1.62</v>
       </c>
       <c r="X6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z6">
         <v>24</v>
@@ -2343,7 +2343,7 @@
         <v>46</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -2370,34 +2370,34 @@
         <v>38</v>
       </c>
       <c r="AK6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL6">
         <v>32</v>
       </c>
       <c r="AM6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN6">
         <v>15</v>
       </c>
       <c r="AO6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ6">
         <v>14.5</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS6">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AT6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU6">
         <v>8.199999999999999</v>
@@ -2406,31 +2406,31 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX6">
         <v>17</v>
       </c>
       <c r="AY6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6">
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BB6">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BE6">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF6">
         <v>13</v>
@@ -2454,7 +2454,7 @@
         <v>90</v>
       </c>
       <c r="BM6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BN6">
         <v>6.8</v>
@@ -2463,10 +2463,10 @@
         <v>4.7</v>
       </c>
       <c r="BP6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BR6">
         <v>29</v>
@@ -2487,7 +2487,7 @@
         <v>14.5</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY6">
         <v>20</v>
@@ -2519,16 +2519,16 @@
         <v>179</v>
       </c>
       <c r="F7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G7">
         <v>2.36</v>
       </c>
       <c r="H7">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
         <v>3.2</v>
@@ -2543,40 +2543,40 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
         <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
         <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X7">
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z7">
         <v>1000</v>
@@ -2591,7 +2591,7 @@
         <v>970</v>
       </c>
       <c r="AD7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2600,7 +2600,7 @@
         <v>38</v>
       </c>
       <c r="AG7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH7">
         <v>1000</v>
@@ -2627,64 +2627,64 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AQ7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AS7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AT7">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AU7">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV7">
         <v>8.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
       </c>
       <c r="AY7">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BA7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BB7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BC7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BD7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BE7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BF7">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2761,16 +2761,16 @@
         <v>180</v>
       </c>
       <c r="F8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H8">
         <v>3.3</v>
       </c>
       <c r="I8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2779,7 +2779,7 @@
         <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2794,133 +2794,133 @@
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T8">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y8">
+        <v>16.5</v>
+      </c>
+      <c r="Z8">
+        <v>30</v>
+      </c>
+      <c r="AA8">
+        <v>75</v>
+      </c>
+      <c r="AB8">
+        <v>13</v>
+      </c>
+      <c r="AC8">
+        <v>8.6</v>
+      </c>
+      <c r="AD8">
+        <v>17.5</v>
+      </c>
+      <c r="AE8">
+        <v>46</v>
+      </c>
+      <c r="AF8">
+        <v>19</v>
+      </c>
+      <c r="AG8">
+        <v>14</v>
+      </c>
+      <c r="AH8">
         <v>20</v>
       </c>
-      <c r="Z8">
-        <v>34</v>
-      </c>
-      <c r="AA8">
-        <v>90</v>
-      </c>
-      <c r="AB8">
+      <c r="AI8">
+        <v>60</v>
+      </c>
+      <c r="AJ8">
+        <v>32</v>
+      </c>
+      <c r="AK8">
+        <v>30</v>
+      </c>
+      <c r="AL8">
+        <v>44</v>
+      </c>
+      <c r="AM8">
+        <v>110</v>
+      </c>
+      <c r="AN8">
+        <v>22</v>
+      </c>
+      <c r="AO8">
+        <v>42</v>
+      </c>
+      <c r="AP8">
+        <v>13</v>
+      </c>
+      <c r="AQ8">
+        <v>12</v>
+      </c>
+      <c r="AR8">
+        <v>18</v>
+      </c>
+      <c r="AS8">
+        <v>4.6</v>
+      </c>
+      <c r="AT8">
+        <v>9.6</v>
+      </c>
+      <c r="AU8">
+        <v>7.4</v>
+      </c>
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>4.5</v>
+      </c>
+      <c r="AX8">
+        <v>13</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
         <v>15</v>
       </c>
-      <c r="AC8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD8">
-        <v>20</v>
-      </c>
-      <c r="AE8">
-        <v>55</v>
-      </c>
-      <c r="AF8">
-        <v>22</v>
-      </c>
-      <c r="AG8">
-        <v>16</v>
-      </c>
-      <c r="AH8">
-        <v>24</v>
-      </c>
-      <c r="AI8">
-        <v>65</v>
-      </c>
-      <c r="AJ8">
-        <v>46</v>
-      </c>
-      <c r="AK8">
-        <v>34</v>
-      </c>
-      <c r="AL8">
-        <v>50</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>25</v>
-      </c>
-      <c r="AO8">
-        <v>50</v>
-      </c>
-      <c r="AP8">
-        <v>2.72</v>
-      </c>
-      <c r="AQ8">
-        <v>10</v>
-      </c>
-      <c r="AR8">
-        <v>2.5</v>
-      </c>
-      <c r="AS8">
-        <v>2.64</v>
-      </c>
-      <c r="AT8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8">
-        <v>6.2</v>
-      </c>
-      <c r="AV8">
-        <v>10.5</v>
-      </c>
-      <c r="AW8">
-        <v>2.58</v>
-      </c>
-      <c r="AX8">
-        <v>11.5</v>
-      </c>
-      <c r="AY8">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8">
-        <v>13.5</v>
-      </c>
       <c r="BA8">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="BB8">
-        <v>2.56</v>
+        <v>4.3</v>
       </c>
       <c r="BC8">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="BD8">
-        <v>2.58</v>
+        <v>26</v>
       </c>
       <c r="BE8">
-        <v>2.72</v>
+        <v>4.7</v>
       </c>
       <c r="BF8">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG8">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3015,7 +3015,7 @@
         <v>2.98</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K9">
         <v>4.1</v>
@@ -3033,19 +3033,19 @@
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S9">
         <v>2.56</v>
       </c>
       <c r="T9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U9">
         <v>2.56</v>
@@ -3057,7 +3057,7 @@
         <v>1.66</v>
       </c>
       <c r="X9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y9">
         <v>16.5</v>
@@ -3066,25 +3066,25 @@
         <v>24</v>
       </c>
       <c r="AA9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB9">
         <v>15</v>
       </c>
       <c r="AC9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
         <v>13.5</v>
       </c>
       <c r="AE9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF9">
         <v>19.5</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
         <v>15</v>
@@ -3093,37 +3093,37 @@
         <v>36</v>
       </c>
       <c r="AJ9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9">
         <v>32</v>
       </c>
       <c r="AM9">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="AN9">
         <v>13.5</v>
       </c>
       <c r="AO9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP9">
         <v>20</v>
       </c>
       <c r="AQ9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR9">
         <v>20</v>
       </c>
       <c r="AS9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AT9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU9">
         <v>8.6</v>
@@ -3132,7 +3132,7 @@
         <v>12</v>
       </c>
       <c r="AW9">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="AX9">
         <v>17</v>
@@ -3141,28 +3141,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB9">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BC9">
         <v>20</v>
       </c>
       <c r="BD9">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BF9">
         <v>12</v>
       </c>
       <c r="BG9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH9">
         <v>5.5</v>
@@ -3254,7 +3254,7 @@
         <v>10.5</v>
       </c>
       <c r="I10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J10">
         <v>6.8</v>
@@ -3290,7 +3290,7 @@
         <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
         <v>1.09</v>
@@ -3308,7 +3308,7 @@
         <v>140</v>
       </c>
       <c r="AA10">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AB10">
         <v>14</v>
@@ -3329,7 +3329,7 @@
         <v>12</v>
       </c>
       <c r="AH10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI10">
         <v>120</v>
@@ -3338,7 +3338,7 @@
         <v>11.5</v>
       </c>
       <c r="AK10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL10">
         <v>36</v>
@@ -3347,13 +3347,13 @@
         <v>130</v>
       </c>
       <c r="AN10">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AO10">
         <v>150</v>
       </c>
       <c r="AP10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10">
         <v>9</v>
@@ -3383,7 +3383,7 @@
         <v>10</v>
       </c>
       <c r="AZ10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BA10">
         <v>9.800000000000001</v>
@@ -3428,13 +3428,13 @@
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3487,7 +3487,7 @@
         <v>183</v>
       </c>
       <c r="F11">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G11">
         <v>2.2</v>
@@ -3517,25 +3517,25 @@
         <v>1.15</v>
       </c>
       <c r="P11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T11">
         <v>1.45</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
         <v>1.83</v>
@@ -3544,22 +3544,22 @@
         <v>34</v>
       </c>
       <c r="Y11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z11">
         <v>34</v>
       </c>
       <c r="AA11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC11">
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE11">
         <v>32</v>
@@ -3571,7 +3571,7 @@
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI11">
         <v>32</v>
@@ -3589,34 +3589,34 @@
         <v>44</v>
       </c>
       <c r="AN11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AQ11">
         <v>20</v>
       </c>
       <c r="AR11">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AT11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU11">
         <v>9.6</v>
       </c>
       <c r="AV11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX11">
         <v>17</v>
@@ -3628,10 +3628,10 @@
         <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC11">
         <v>16.5</v>
@@ -3652,13 +3652,13 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3667,7 +3667,7 @@
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO11">
         <v>4.5</v>
@@ -3682,7 +3682,7 @@
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT11">
         <v>1000</v>
@@ -3732,7 +3732,7 @@
         <v>2.26</v>
       </c>
       <c r="G12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -3747,7 +3747,7 @@
         <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
         <v>1.04</v>
@@ -3765,16 +3765,16 @@
         <v>1.58</v>
       </c>
       <c r="R12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S12">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T12">
         <v>1.54</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V12">
         <v>1.46</v>
@@ -3783,7 +3783,7 @@
         <v>1.74</v>
       </c>
       <c r="X12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y12">
         <v>19</v>
@@ -3810,7 +3810,7 @@
         <v>19.5</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
         <v>16</v>
@@ -3822,7 +3822,7 @@
         <v>34</v>
       </c>
       <c r="AK12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -3834,55 +3834,55 @@
         <v>12</v>
       </c>
       <c r="AO12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP12">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
         <v>15.5</v>
       </c>
       <c r="AR12">
+        <v>19.5</v>
+      </c>
+      <c r="AS12">
         <v>7</v>
       </c>
-      <c r="AS12">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU12">
         <v>9</v>
       </c>
       <c r="AV12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW12">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX12">
         <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
         <v>13</v>
       </c>
       <c r="BA12">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB12">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BC12">
         <v>18</v>
       </c>
       <c r="BD12">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BE12">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF12">
         <v>10</v>
@@ -3894,13 +3894,13 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3918,7 +3918,7 @@
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12">
         <v>1000</v>
@@ -3971,28 +3971,28 @@
         <v>185</v>
       </c>
       <c r="F13">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H13">
         <v>2.24</v>
       </c>
       <c r="I13">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J13">
         <v>3.8</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.27</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
         <v>5.1</v>
@@ -4004,22 +4004,22 @@
         <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R13">
         <v>1.55</v>
       </c>
       <c r="S13">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U13">
         <v>2.52</v>
       </c>
       <c r="V13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W13">
         <v>1.43</v>
@@ -4028,25 +4028,25 @@
         <v>26</v>
       </c>
       <c r="Y13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AA13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB13">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC13">
         <v>9.6</v>
       </c>
       <c r="AD13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF13">
         <v>29</v>
@@ -4064,10 +4064,10 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>70</v>
@@ -4079,19 +4079,19 @@
         <v>13</v>
       </c>
       <c r="AP13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR13">
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU13">
         <v>8.4</v>
@@ -4100,37 +4100,37 @@
         <v>10</v>
       </c>
       <c r="AW13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13">
         <v>12</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA13">
+        <v>6</v>
+      </c>
+      <c r="BB13">
+        <v>6.4</v>
+      </c>
+      <c r="BC13">
+        <v>6</v>
+      </c>
+      <c r="BD13">
+        <v>6.2</v>
+      </c>
+      <c r="BE13">
         <v>6.6</v>
       </c>
-      <c r="BB13">
-        <v>38</v>
-      </c>
-      <c r="BC13">
-        <v>6.4</v>
-      </c>
-      <c r="BD13">
-        <v>6.6</v>
-      </c>
-      <c r="BE13">
-        <v>7.4</v>
-      </c>
       <c r="BF13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4154,7 +4154,7 @@
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP13">
         <v>1000</v>
@@ -4172,7 +4172,7 @@
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -4213,7 +4213,7 @@
         <v>186</v>
       </c>
       <c r="F14">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G14">
         <v>1.65</v>
@@ -4231,7 +4231,7 @@
         <v>4.9</v>
       </c>
       <c r="L14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -4246,13 +4246,13 @@
         <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S14">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T14">
         <v>1.81</v>
@@ -4264,34 +4264,34 @@
         <v>1.19</v>
       </c>
       <c r="W14">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA14">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE14">
         <v>90</v>
       </c>
       <c r="AF14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
@@ -4312,25 +4312,25 @@
         <v>36</v>
       </c>
       <c r="AM14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN14">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AO14">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP14">
-        <v>18</v>
+        <v>5.3</v>
       </c>
       <c r="AQ14">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AR14">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS14">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AT14">
         <v>8.800000000000001</v>
@@ -4339,10 +4339,10 @@
         <v>9.4</v>
       </c>
       <c r="AV14">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="AW14">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4351,10 +4351,10 @@
         <v>9</v>
       </c>
       <c r="AZ14">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BB14">
         <v>13.5</v>
@@ -4363,22 +4363,22 @@
         <v>14</v>
       </c>
       <c r="BD14">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE14">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF14">
         <v>6.6</v>
       </c>
       <c r="BG14">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
@@ -4396,7 +4396,7 @@
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP14">
         <v>1000</v>
@@ -4473,16 +4473,16 @@
         <v>6.6</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
         <v>1.79</v>
@@ -4491,190 +4491,190 @@
         <v>1.73</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>233</v>
@@ -4697,16 +4697,16 @@
         <v>188</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G16">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H16">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J16">
         <v>3.65</v>
@@ -4715,16 +4715,16 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
         <v>2.22</v>
@@ -4733,190 +4733,190 @@
         <v>1.58</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>233</v>
@@ -4948,10 +4948,10 @@
         <v>2.48</v>
       </c>
       <c r="I17">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J17">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K17">
         <v>5.2</v>
@@ -5423,16 +5423,16 @@
         <v>191</v>
       </c>
       <c r="F19">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G19">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I19">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J19">
         <v>3.55</v>
@@ -5453,10 +5453,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q19">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5907,13 +5907,13 @@
         <v>193</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G21">
         <v>2.2</v>
       </c>
       <c r="H21">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I21">
         <v>3.35</v>
@@ -5922,7 +5922,7 @@
         <v>4.4</v>
       </c>
       <c r="K21">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q21">
         <v>1.29</v>
@@ -8085,13 +8085,13 @@
         <v>202</v>
       </c>
       <c r="F30">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G30">
         <v>2.74</v>
       </c>
       <c r="H30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I30">
         <v>3.6</v>
@@ -8118,7 +8118,7 @@
         <v>1.53</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8139,13 +8139,13 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA30">
         <v>75</v>
@@ -8154,7 +8154,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD30">
         <v>16</v>
@@ -8169,19 +8169,19 @@
         <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ30">
         <v>48</v>
       </c>
       <c r="AK30">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL30">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM30">
         <v>210</v>
@@ -8190,7 +8190,7 @@
         <v>42</v>
       </c>
       <c r="AO30">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP30">
         <v>7.6</v>
@@ -8202,10 +8202,10 @@
         <v>18.5</v>
       </c>
       <c r="AS30">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT30">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU30">
         <v>6.2</v>
@@ -8214,7 +8214,7 @@
         <v>13</v>
       </c>
       <c r="AW30">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX30">
         <v>13</v>
@@ -8226,25 +8226,25 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB30">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC30">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD30">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BE30">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF30">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG30">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -10505,22 +10505,22 @@
         <v>212</v>
       </c>
       <c r="F40">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G40">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H40">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I40">
         <v>2.1</v>
       </c>
       <c r="J40">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K40">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10747,16 +10747,16 @@
         <v>213</v>
       </c>
       <c r="F41">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G41">
         <v>2.26</v>
       </c>
       <c r="H41">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J41">
         <v>3.4</v>
@@ -10777,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q41">
         <v>1.97</v>
@@ -10992,16 +10992,16 @@
         <v>1.49</v>
       </c>
       <c r="G42">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H42">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J42">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K42">
         <v>5</v>
@@ -11013,28 +11013,28 @@
         <v>1.06</v>
       </c>
       <c r="N42">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P42">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q42">
+        <v>1.87</v>
+      </c>
+      <c r="R42">
+        <v>1.4</v>
+      </c>
+      <c r="S42">
+        <v>3.25</v>
+      </c>
+      <c r="T42">
+        <v>2.06</v>
+      </c>
+      <c r="U42">
         <v>1.88</v>
-      </c>
-      <c r="R42">
-        <v>1.39</v>
-      </c>
-      <c r="S42">
-        <v>3.3</v>
-      </c>
-      <c r="T42">
-        <v>2.08</v>
-      </c>
-      <c r="U42">
-        <v>1.85</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -11046,19 +11046,19 @@
         <v>18</v>
       </c>
       <c r="Y42">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z42">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA42">
         <v>310</v>
       </c>
       <c r="AB42">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC42">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD42">
         <v>29</v>
@@ -11073,40 +11073,40 @@
         <v>10.5</v>
       </c>
       <c r="AH42">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI42">
         <v>130</v>
       </c>
       <c r="AJ42">
+        <v>13</v>
+      </c>
+      <c r="AK42">
+        <v>16.5</v>
+      </c>
+      <c r="AL42">
+        <v>38</v>
+      </c>
+      <c r="AM42">
+        <v>190</v>
+      </c>
+      <c r="AN42">
+        <v>7.8</v>
+      </c>
+      <c r="AO42">
+        <v>200</v>
+      </c>
+      <c r="AP42">
+        <v>15</v>
+      </c>
+      <c r="AQ42">
+        <v>21</v>
+      </c>
+      <c r="AR42">
+        <v>12</v>
+      </c>
+      <c r="AS42">
         <v>13.5</v>
-      </c>
-      <c r="AK42">
-        <v>20</v>
-      </c>
-      <c r="AL42">
-        <v>46</v>
-      </c>
-      <c r="AM42">
-        <v>200</v>
-      </c>
-      <c r="AN42">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO42">
-        <v>210</v>
-      </c>
-      <c r="AP42">
-        <v>14</v>
-      </c>
-      <c r="AQ42">
-        <v>19.5</v>
-      </c>
-      <c r="AR42">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS42">
-        <v>10</v>
       </c>
       <c r="AT42">
         <v>7</v>
@@ -11115,25 +11115,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV42">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AW42">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AX42">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY42">
         <v>9</v>
       </c>
       <c r="AZ42">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BA42">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BB42">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC42">
         <v>14.5</v>
@@ -11142,13 +11142,13 @@
         <v>32</v>
       </c>
       <c r="BE42">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF42">
         <v>7.2</v>
       </c>
       <c r="BG42">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11160,7 +11160,7 @@
         <v>1000</v>
       </c>
       <c r="BK42">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11178,7 +11178,7 @@
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR42">
         <v>1000</v>
@@ -11190,7 +11190,7 @@
         <v>1000</v>
       </c>
       <c r="BU42">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV42">
         <v>1000</v>
@@ -11237,7 +11237,7 @@
         <v>1.63</v>
       </c>
       <c r="H43">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>6.8</v>
@@ -11246,7 +11246,7 @@
         <v>4.3</v>
       </c>
       <c r="K43">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11258,13 +11258,13 @@
         <v>4</v>
       </c>
       <c r="O43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P43">
         <v>2.02</v>
       </c>
       <c r="Q43">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R43">
         <v>1.39</v>
@@ -11273,7 +11273,7 @@
         <v>3.15</v>
       </c>
       <c r="T43">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U43">
         <v>1.93</v>
@@ -11288,13 +11288,13 @@
         <v>17</v>
       </c>
       <c r="Y43">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z43">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA43">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB43">
         <v>8.800000000000001</v>
@@ -11309,22 +11309,22 @@
         <v>110</v>
       </c>
       <c r="AF43">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG43">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH43">
         <v>24</v>
       </c>
       <c r="AI43">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ43">
         <v>15.5</v>
       </c>
       <c r="AK43">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL43">
         <v>40</v>
@@ -11336,73 +11336,73 @@
         <v>9</v>
       </c>
       <c r="AO43">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP43">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ43">
         <v>17.5</v>
       </c>
       <c r="AR43">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS43">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT43">
         <v>8.199999999999999</v>
       </c>
       <c r="AU43">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV43">
         <v>20</v>
       </c>
       <c r="AW43">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX43">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY43">
+        <v>9</v>
+      </c>
+      <c r="AZ43">
+        <v>19</v>
+      </c>
+      <c r="BA43">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AZ43">
-        <v>20</v>
-      </c>
-      <c r="BA43">
-        <v>10</v>
       </c>
       <c r="BB43">
         <v>12.5</v>
       </c>
       <c r="BC43">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD43">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE43">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF43">
         <v>7.8</v>
       </c>
       <c r="BG43">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH43">
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL43">
         <v>1000</v>
@@ -11414,13 +11414,13 @@
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR43">
         <v>1000</v>
@@ -11432,7 +11432,7 @@
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV43">
         <v>1000</v>
@@ -11473,7 +11473,7 @@
         <v>216</v>
       </c>
       <c r="F44">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -11482,7 +11482,7 @@
         <v>2.54</v>
       </c>
       <c r="I44">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="J44">
         <v>2.82</v>
@@ -11503,7 +11503,7 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q44">
         <v>3.55</v>
@@ -11518,7 +11518,7 @@
         <v>2.62</v>
       </c>
       <c r="U44">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -11530,91 +11530,91 @@
         <v>6.6</v>
       </c>
       <c r="Y44">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z44">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA44">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB44">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC44">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD44">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE44">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF44">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG44">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH44">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI44">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ44">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK44">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL44">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM44">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN44">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO44">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP44">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ44">
         <v>5.1</v>
       </c>
       <c r="AR44">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS44">
         <v>16.5</v>
       </c>
       <c r="AT44">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU44">
         <v>5.5</v>
       </c>
       <c r="AV44">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW44">
         <v>17</v>
       </c>
       <c r="AX44">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AY44">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AZ44">
-        <v>7.2</v>
+        <v>1.18</v>
       </c>
       <c r="BA44">
-        <v>8.800000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="BB44">
         <v>22</v>
@@ -11623,13 +11623,13 @@
         <v>23</v>
       </c>
       <c r="BD44">
-        <v>9</v>
+        <v>1.18</v>
       </c>
       <c r="BE44">
-        <v>8.800000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="BF44">
-        <v>9</v>
+        <v>1.18</v>
       </c>
       <c r="BG44">
         <v>18</v>
@@ -11715,22 +11715,22 @@
         <v>217</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G45">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H45">
+        <v>1.46</v>
+      </c>
+      <c r="I45">
         <v>1.47</v>
       </c>
-      <c r="I45">
-        <v>1.48</v>
-      </c>
       <c r="J45">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K45">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -11742,25 +11742,25 @@
         <v>4.7</v>
       </c>
       <c r="O45">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P45">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q45">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R45">
         <v>1.52</v>
       </c>
       <c r="S45">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T45">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U45">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -11775,10 +11775,10 @@
         <v>9.6</v>
       </c>
       <c r="Z45">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA45">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB45">
         <v>28</v>
@@ -11787,55 +11787,55 @@
         <v>11.5</v>
       </c>
       <c r="AD45">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE45">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF45">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG45">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH45">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI45">
         <v>36</v>
       </c>
       <c r="AJ45">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AK45">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AL45">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AM45">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN45">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AO45">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP45">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AQ45">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR45">
         <v>8.199999999999999</v>
       </c>
       <c r="AS45">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT45">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU45">
         <v>10</v>
@@ -11844,19 +11844,19 @@
         <v>9.4</v>
       </c>
       <c r="AW45">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX45">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AY45">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AZ45">
         <v>19.5</v>
       </c>
       <c r="BA45">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB45">
         <v>11</v>
@@ -11871,7 +11871,7 @@
         <v>10.5</v>
       </c>
       <c r="BF45">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG45">
         <v>5.8</v>
@@ -11880,16 +11880,16 @@
         <v>3.95</v>
       </c>
       <c r="BI45">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ45">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK45">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL45">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM45">
         <v>1.01</v>
@@ -12686,16 +12686,16 @@
         <v>2</v>
       </c>
       <c r="G49">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H49">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I49">
         <v>4.5</v>
       </c>
       <c r="J49">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K49">
         <v>3.75</v>
@@ -12713,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q49">
         <v>2</v>
@@ -12937,7 +12937,7 @@
         <v>4.7</v>
       </c>
       <c r="J50">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K50">
         <v>3.65</v>
@@ -12955,10 +12955,10 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -13899,16 +13899,16 @@
         <v>2.12</v>
       </c>
       <c r="H54">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I54">
         <v>4.1</v>
       </c>
       <c r="J54">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K54">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -14135,22 +14135,22 @@
         <v>227</v>
       </c>
       <c r="F55">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="G55">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="H55">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I55">
         <v>7.4</v>
       </c>
       <c r="J55">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K55">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14165,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q55">
         <v>2.22</v>
@@ -14377,10 +14377,10 @@
         <v>228</v>
       </c>
       <c r="F56">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G56">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H56">
         <v>7.6</v>
@@ -14392,7 +14392,7 @@
         <v>5.5</v>
       </c>
       <c r="K56">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -14401,13 +14401,13 @@
         <v>1.03</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O56">
         <v>1.17</v>
       </c>
       <c r="P56">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q56">
         <v>1.51</v>
@@ -14416,10 +14416,10 @@
         <v>1.73</v>
       </c>
       <c r="S56">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T56">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U56">
         <v>2.24</v>
@@ -14431,16 +14431,16 @@
         <v>0</v>
       </c>
       <c r="X56">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y56">
         <v>36</v>
       </c>
       <c r="Z56">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA56">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AB56">
         <v>11.5</v>
@@ -14449,94 +14449,94 @@
         <v>14</v>
       </c>
       <c r="AD56">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE56">
         <v>90</v>
       </c>
       <c r="AF56">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG56">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH56">
         <v>23</v>
       </c>
       <c r="AI56">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ56">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK56">
         <v>14.5</v>
       </c>
       <c r="AL56">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM56">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN56">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AO56">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP56">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AQ56">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="AR56">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AS56">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AT56">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU56">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AV56">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AW56">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AX56">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY56">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AZ56">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="BA56">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BB56">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC56">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BD56">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BE56">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BF56">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG56">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14560,7 +14560,7 @@
         <v>1000</v>
       </c>
       <c r="BO56">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP56">
         <v>1000</v>
@@ -14619,16 +14619,16 @@
         <v>229</v>
       </c>
       <c r="F57">
+        <v>3.15</v>
+      </c>
+      <c r="G57">
         <v>3.2</v>
       </c>
-      <c r="G57">
-        <v>3.3</v>
-      </c>
       <c r="H57">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I57">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J57">
         <v>3.45</v>
@@ -14643,7 +14643,7 @@
         <v>1.09</v>
       </c>
       <c r="N57">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O57">
         <v>1.39</v>
@@ -14655,13 +14655,13 @@
         <v>2.14</v>
       </c>
       <c r="R57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S57">
         <v>4</v>
       </c>
       <c r="T57">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U57">
         <v>2.06</v>
@@ -14676,13 +14676,13 @@
         <v>12.5</v>
       </c>
       <c r="Y57">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z57">
         <v>16.5</v>
       </c>
       <c r="AA57">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB57">
         <v>11.5</v>
@@ -14703,10 +14703,10 @@
         <v>15</v>
       </c>
       <c r="AH57">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI57">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ57">
         <v>65</v>
@@ -14730,7 +14730,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ57">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR57">
         <v>13.5</v>
@@ -14748,49 +14748,49 @@
         <v>10.5</v>
       </c>
       <c r="AW57">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX57">
         <v>18</v>
       </c>
       <c r="AY57">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ57">
         <v>17</v>
       </c>
       <c r="BA57">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB57">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC57">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD57">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE57">
         <v>10</v>
       </c>
       <c r="BF57">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG57">
         <v>21</v>
       </c>
       <c r="BH57">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI57">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ57">
         <v>1000</v>
       </c>
       <c r="BK57">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL57">
         <v>1000</v>
@@ -14802,7 +14802,7 @@
         <v>1000</v>
       </c>
       <c r="BO57">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP57">
         <v>1000</v>
@@ -14820,7 +14820,7 @@
         <v>1000</v>
       </c>
       <c r="BU57">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV57">
         <v>1000</v>
@@ -14861,16 +14861,16 @@
         <v>230</v>
       </c>
       <c r="F58">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G58">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H58">
+        <v>2.76</v>
+      </c>
+      <c r="I58">
         <v>2.8</v>
-      </c>
-      <c r="I58">
-        <v>2.84</v>
       </c>
       <c r="J58">
         <v>3.85</v>
@@ -14888,19 +14888,19 @@
         <v>6.2</v>
       </c>
       <c r="O58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P58">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q58">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R58">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S58">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T58">
         <v>1.49</v>
@@ -14915,22 +14915,22 @@
         <v>0</v>
       </c>
       <c r="X58">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y58">
         <v>19</v>
       </c>
       <c r="Z58">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA58">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB58">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC58">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD58">
         <v>13.5</v>
@@ -14945,19 +14945,19 @@
         <v>13</v>
       </c>
       <c r="AH58">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI58">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ58">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK58">
         <v>24</v>
       </c>
       <c r="AL58">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM58">
         <v>65</v>
@@ -14978,7 +14978,7 @@
         <v>19</v>
       </c>
       <c r="AS58">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT58">
         <v>15.5</v>
@@ -14990,10 +14990,10 @@
         <v>11.5</v>
       </c>
       <c r="AW58">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX58">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY58">
         <v>11</v>
@@ -15002,37 +15002,37 @@
         <v>12</v>
       </c>
       <c r="BA58">
+        <v>7.6</v>
+      </c>
+      <c r="BB58">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC58">
         <v>19.5</v>
       </c>
-      <c r="BB58">
+      <c r="BD58">
+        <v>7.6</v>
+      </c>
+      <c r="BE58">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BC58">
-        <v>18.5</v>
-      </c>
-      <c r="BD58">
-        <v>19.5</v>
-      </c>
-      <c r="BE58">
-        <v>42</v>
       </c>
       <c r="BF58">
         <v>11.5</v>
       </c>
       <c r="BG58">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH58">
         <v>1000</v>
       </c>
       <c r="BI58">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BJ58">
         <v>1000</v>
       </c>
       <c r="BK58">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL58">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
         <v>1000</v>
       </c>
       <c r="BQ58">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR58">
         <v>1000</v>
@@ -15062,13 +15062,13 @@
         <v>1000</v>
       </c>
       <c r="BU58">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV58">
         <v>1000</v>
       </c>
       <c r="BW58">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX58">
         <v>1000</v>
@@ -15136,7 +15136,7 @@
         <v>1.05</v>
       </c>
       <c r="Q59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15345,22 +15345,22 @@
         <v>232</v>
       </c>
       <c r="F60">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G60">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="H60">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I60">
         <v>4.7</v>
       </c>
       <c r="J60">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K60">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -15375,10 +15375,10 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Q60">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="R60">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="251">
   <si>
     <t>League</t>
   </si>
@@ -304,6 +304,9 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>Uruguayan Segunda Division</t>
+  </si>
+  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -478,21 +481,21 @@
     <t>Gefle</t>
   </si>
   <si>
+    <t>Jesenice</t>
+  </si>
+  <si>
+    <t>Beltinci</t>
+  </si>
+  <si>
+    <t>Slovan Ljublana</t>
+  </si>
+  <si>
+    <t>Assyriska FF</t>
+  </si>
+  <si>
     <t>Criciuma</t>
   </si>
   <si>
-    <t>Beltinci</t>
-  </si>
-  <si>
-    <t>Slovan Ljublana</t>
-  </si>
-  <si>
-    <t>Jesenice</t>
-  </si>
-  <si>
-    <t>Assyriska FF</t>
-  </si>
-  <si>
     <t>Mallorca</t>
   </si>
   <si>
@@ -553,6 +556,9 @@
     <t>Norway</t>
   </si>
   <si>
+    <t>Cerrito</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
@@ -670,21 +676,21 @@
     <t>Vasalunds IF</t>
   </si>
   <si>
+    <t>NK Dren Vrhnika</t>
+  </si>
+  <si>
+    <t>Krka</t>
+  </si>
+  <si>
+    <t>Brezice</t>
+  </si>
+  <si>
+    <t>Pitea</t>
+  </si>
+  <si>
     <t>Avai</t>
   </si>
   <si>
-    <t>Krka</t>
-  </si>
-  <si>
-    <t>Brezice</t>
-  </si>
-  <si>
-    <t>NK Dren Vrhnika</t>
-  </si>
-  <si>
-    <t>Pitea</t>
-  </si>
-  <si>
     <t>Almeria</t>
   </si>
   <si>
@@ -745,6 +751,9 @@
     <t>Portugal</t>
   </si>
   <si>
+    <t>La Luz FC</t>
+  </si>
+  <si>
     <t>Cuiaba</t>
   </si>
   <si>
@@ -757,7 +766,7 @@
     <t>HUSA Agadir</t>
   </si>
   <si>
-    <t>2026-09-25 08:39:13</t>
+    <t>2026-09-25 11:01:06</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB65"/>
+  <dimension ref="A1:CB66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1339,28 +1348,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F2">
         <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
         <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1372,10 +1381,10 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O2">
         <v>1.19</v>
@@ -1384,7 +1393,7 @@
         <v>2.58</v>
       </c>
       <c r="Q2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R2">
         <v>1.65</v>
@@ -1396,13 +1405,13 @@
         <v>1.53</v>
       </c>
       <c r="U2">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
         <v>25</v>
@@ -1414,13 +1423,13 @@
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB2">
         <v>15</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -1453,7 +1462,7 @@
         <v>55</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO2">
         <v>18.5</v>
@@ -1573,7 +1582,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1581,34 +1590,34 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>7.4</v>
       </c>
       <c r="J3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1623,7 +1632,7 @@
         <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q3">
         <v>1.53</v>
@@ -1632,25 +1641,25 @@
         <v>1.7</v>
       </c>
       <c r="S3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T3">
         <v>1.7</v>
       </c>
       <c r="U3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z3">
         <v>1000</v>
@@ -1728,7 +1737,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>18</v>
@@ -1815,7 +1824,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1823,25 +1832,25 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F4">
         <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>3.1</v>
@@ -1853,25 +1862,25 @@
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O4">
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q4">
         <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S4">
         <v>2.62</v>
@@ -1886,10 +1895,10 @@
         <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y4">
         <v>17.5</v>
@@ -1913,16 +1922,16 @@
         <v>32</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG4">
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
         <v>38</v>
@@ -1931,10 +1940,10 @@
         <v>24</v>
       </c>
       <c r="AL4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM4">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AN4">
         <v>13</v>
@@ -1943,7 +1952,7 @@
         <v>21</v>
       </c>
       <c r="AP4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ4">
         <v>15</v>
@@ -1955,7 +1964,7 @@
         <v>26</v>
       </c>
       <c r="AT4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU4">
         <v>8.4</v>
@@ -1964,10 +1973,10 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
@@ -1985,7 +1994,7 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE4">
         <v>29</v>
@@ -1994,10 +2003,10 @@
         <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI4">
         <v>3.75</v>
@@ -2015,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="BN4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
         <v>5</v>
@@ -2027,37 +2036,37 @@
         <v>13.5</v>
       </c>
       <c r="BR4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
+        <v>23</v>
+      </c>
+      <c r="BW4">
+        <v>16</v>
+      </c>
+      <c r="BX4">
+        <v>32</v>
+      </c>
+      <c r="BY4">
         <v>22</v>
       </c>
-      <c r="BW4">
-        <v>17.5</v>
-      </c>
-      <c r="BX4">
-        <v>30</v>
-      </c>
-      <c r="BY4">
-        <v>21</v>
-      </c>
       <c r="BZ4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2065,22 +2074,22 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F5">
         <v>1.53</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H5">
         <v>6.2</v>
@@ -2299,7 +2308,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2307,28 +2316,28 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F6">
         <v>2.48</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -2349,28 +2358,28 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
         <v>1.59</v>
       </c>
       <c r="S6">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
         <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X6">
         <v>23</v>
@@ -2388,19 +2397,19 @@
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
         <v>28</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH6">
         <v>15</v>
@@ -2421,13 +2430,13 @@
         <v>60</v>
       </c>
       <c r="AN6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6">
         <v>14.5</v>
@@ -2439,7 +2448,7 @@
         <v>25</v>
       </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU6">
         <v>8.199999999999999</v>
@@ -2448,7 +2457,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX6">
         <v>17</v>
@@ -2484,7 +2493,7 @@
         <v>4.8</v>
       </c>
       <c r="BI6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6">
         <v>9.800000000000001</v>
@@ -2502,7 +2511,7 @@
         <v>6.8</v>
       </c>
       <c r="BO6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
         <v>19.5</v>
@@ -2523,7 +2532,7 @@
         <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW6">
         <v>14.5</v>
@@ -2541,7 +2550,7 @@
         <v>13</v>
       </c>
       <c r="CB6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2549,22 +2558,22 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F7">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H7">
         <v>3.15</v>
@@ -2576,7 +2585,7 @@
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2585,7 +2594,7 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
         <v>1.32</v>
@@ -2612,7 +2621,7 @@
         <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2633,7 +2642,7 @@
         <v>970</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2669,58 +2678,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AS7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT7">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AU7">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AV7">
         <v>8.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AX7">
         <v>8.800000000000001</v>
       </c>
       <c r="AY7">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AZ7">
         <v>9.6</v>
       </c>
       <c r="BA7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BB7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BD7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BE7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF7">
         <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2783,7 +2792,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2791,28 +2800,28 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G8">
         <v>2.4</v>
       </c>
       <c r="H8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2827,7 +2836,7 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>1.3</v>
@@ -2836,25 +2845,25 @@
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
         <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X8">
         <v>19</v>
@@ -2872,7 +2881,7 @@
         <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
         <v>17.5</v>
@@ -2920,7 +2929,7 @@
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT8">
         <v>9.6</v>
@@ -2932,7 +2941,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX8">
         <v>13</v>
@@ -2944,25 +2953,25 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB8">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC8">
         <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE8">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF8">
         <v>15</v>
       </c>
       <c r="BG8">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3025,7 +3034,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3033,28 +3042,28 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F9">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="G9">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="I9">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="J9">
         <v>3.9</v>
@@ -3069,13 +3078,13 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
         <v>1.62</v>
@@ -3084,127 +3093,127 @@
         <v>1.6</v>
       </c>
       <c r="S9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W9">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="X9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y9">
+        <v>16</v>
+      </c>
+      <c r="Z9">
+        <v>21</v>
+      </c>
+      <c r="AA9">
+        <v>60</v>
+      </c>
+      <c r="AB9">
         <v>16.5</v>
-      </c>
-      <c r="Z9">
-        <v>24</v>
-      </c>
-      <c r="AA9">
-        <v>65</v>
-      </c>
-      <c r="AB9">
-        <v>15</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>15</v>
       </c>
       <c r="AI9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM9">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN9">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS9">
         <v>32</v>
       </c>
       <c r="AT9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU9">
         <v>8.6</v>
       </c>
       <c r="AV9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AX9">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
         <v>13</v>
       </c>
       <c r="BA9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC9">
         <v>20</v>
       </c>
       <c r="BD9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE9">
         <v>38</v>
       </c>
       <c r="BF9">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH9">
         <v>5.5</v>
@@ -3267,7 +3276,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3275,19 +3284,19 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F10">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G10">
         <v>2.36</v>
@@ -3317,10 +3326,10 @@
         <v>1.19</v>
       </c>
       <c r="P10">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R10">
         <v>1.64</v>
@@ -3332,7 +3341,7 @@
         <v>1.54</v>
       </c>
       <c r="U10">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V10">
         <v>1.46</v>
@@ -3371,7 +3380,7 @@
         <v>12</v>
       </c>
       <c r="AH10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI10">
         <v>38</v>
@@ -3446,7 +3455,7 @@
         <v>10</v>
       </c>
       <c r="BG10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3509,7 +3518,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3517,28 +3526,28 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G11">
         <v>1.3</v>
       </c>
       <c r="H11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J11">
         <v>6.8</v>
@@ -3547,34 +3556,34 @@
         <v>7.4</v>
       </c>
       <c r="L11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M11">
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P11">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R11">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="S11">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="T11">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V11">
         <v>1.09</v>
@@ -3583,46 +3592,46 @@
         <v>4.3</v>
       </c>
       <c r="X11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z11">
         <v>1000</v>
       </c>
       <c r="AA11">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC11">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG11">
+        <v>11.5</v>
+      </c>
+      <c r="AH11">
+        <v>30</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
         <v>10.5</v>
       </c>
-      <c r="AG11">
-        <v>12</v>
-      </c>
-      <c r="AH11">
-        <v>28</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>11.5</v>
-      </c>
       <c r="AK11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL11">
         <v>32</v>
@@ -3631,16 +3640,16 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
+        <v>24</v>
+      </c>
+      <c r="AQ11">
         <v>25</v>
-      </c>
-      <c r="AQ11">
-        <v>26</v>
       </c>
       <c r="AR11">
         <v>38</v>
@@ -3649,46 +3658,46 @@
         <v>55</v>
       </c>
       <c r="AT11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AU11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW11">
+        <v>44</v>
+      </c>
+      <c r="AX11">
+        <v>9</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>19</v>
+      </c>
+      <c r="BA11">
+        <v>38</v>
+      </c>
+      <c r="BB11">
+        <v>9.4</v>
+      </c>
+      <c r="BC11">
+        <v>12.5</v>
+      </c>
+      <c r="BD11">
+        <v>21</v>
+      </c>
+      <c r="BE11">
+        <v>40</v>
+      </c>
+      <c r="BF11">
+        <v>3.5</v>
+      </c>
+      <c r="BG11">
         <v>42</v>
-      </c>
-      <c r="AX11">
-        <v>9.6</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11">
-        <v>18</v>
-      </c>
-      <c r="BA11">
-        <v>36</v>
-      </c>
-      <c r="BB11">
-        <v>10</v>
-      </c>
-      <c r="BC11">
-        <v>11.5</v>
-      </c>
-      <c r="BD11">
-        <v>19</v>
-      </c>
-      <c r="BE11">
-        <v>38</v>
-      </c>
-      <c r="BF11">
-        <v>3.2</v>
-      </c>
-      <c r="BG11">
-        <v>40</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3751,7 +3760,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3759,34 +3768,34 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F12">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J12">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.25</v>
@@ -3819,16 +3828,16 @@
         <v>3.05</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12">
         <v>32</v>
       </c>
       <c r="Y12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z12">
         <v>34</v>
@@ -3837,7 +3846,7 @@
         <v>75</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC12">
         <v>10.5</v>
@@ -3852,7 +3861,7 @@
         <v>19.5</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
         <v>14</v>
@@ -3861,7 +3870,7 @@
         <v>32</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK12">
         <v>19.5</v>
@@ -3879,19 +3888,19 @@
         <v>17.5</v>
       </c>
       <c r="AP12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ12">
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU12">
         <v>9.4</v>
@@ -3900,10 +3909,10 @@
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
@@ -3915,13 +3924,13 @@
         <v>22</v>
       </c>
       <c r="BB12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE12">
         <v>29</v>
@@ -3930,10 +3939,10 @@
         <v>7.8</v>
       </c>
       <c r="BG12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI12">
         <v>4</v>
@@ -3993,7 +4002,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -4001,28 +4010,28 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F13">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="G13">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H13">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="I13">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="J13">
         <v>3.8</v>
@@ -4049,22 +4058,22 @@
         <v>1.61</v>
       </c>
       <c r="R13">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S13">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T13">
         <v>1.59</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
         <v>26</v>
@@ -4073,13 +4082,13 @@
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC13">
         <v>9.6</v>
@@ -4088,7 +4097,7 @@
         <v>12</v>
       </c>
       <c r="AE13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF13">
         <v>30</v>
@@ -4118,7 +4127,7 @@
         <v>24</v>
       </c>
       <c r="AO13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP13">
         <v>19</v>
@@ -4130,7 +4139,7 @@
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT13">
         <v>14.5</v>
@@ -4154,25 +4163,25 @@
         <v>13</v>
       </c>
       <c r="BA13">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB13">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC13">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD13">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
         <v>18</v>
       </c>
       <c r="BG13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4235,7 +4244,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4243,16 +4252,16 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F14">
         <v>1.58</v>
@@ -4270,7 +4279,7 @@
         <v>4.5</v>
       </c>
       <c r="K14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
         <v>1.3</v>
@@ -4279,25 +4288,25 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T14">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U14">
         <v>2.08</v>
@@ -4306,13 +4315,13 @@
         <v>1.19</v>
       </c>
       <c r="W14">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X14">
         <v>25</v>
       </c>
       <c r="Y14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z14">
         <v>60</v>
@@ -4321,13 +4330,13 @@
         <v>180</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE14">
         <v>80</v>
@@ -4339,7 +4348,7 @@
         <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI14">
         <v>80</v>
@@ -4351,31 +4360,31 @@
         <v>18.5</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM14">
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU14">
         <v>9.4</v>
@@ -4384,7 +4393,7 @@
         <v>17</v>
       </c>
       <c r="AW14">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4393,10 +4402,10 @@
         <v>9</v>
       </c>
       <c r="AZ14">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA14">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB14">
         <v>13.5</v>
@@ -4405,16 +4414,16 @@
         <v>14</v>
       </c>
       <c r="BD14">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF14">
         <v>6.6</v>
       </c>
       <c r="BG14">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4477,7 +4486,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4485,16 +4494,16 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F15">
         <v>2.42</v>
@@ -4506,7 +4515,7 @@
         <v>2.6</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J15">
         <v>3.65</v>
@@ -4545,7 +4554,7 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.62</v>
@@ -4719,7 +4728,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4727,16 +4736,16 @@
         <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F16">
         <v>2.28</v>
@@ -4763,7 +4772,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>1.01</v>
@@ -4778,7 +4787,7 @@
         <v>1.26</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4961,7 +4970,7 @@
         <v>1.31</v>
       </c>
       <c r="CB16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4969,25 +4978,25 @@
         <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F17">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
         <v>2.64</v>
       </c>
       <c r="H17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I17">
         <v>3.45</v>
@@ -5005,13 +5014,13 @@
         <v>1.11</v>
       </c>
       <c r="N17">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O17">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P17">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q17">
         <v>2.56</v>
@@ -5035,7 +5044,7 @@
         <v>1.61</v>
       </c>
       <c r="X17">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y17">
         <v>9.800000000000001</v>
@@ -5053,10 +5062,10 @@
         <v>7.6</v>
       </c>
       <c r="AD17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF17">
         <v>14.5</v>
@@ -5113,7 +5122,7 @@
         <v>9</v>
       </c>
       <c r="AX17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY17">
         <v>11.5</v>
@@ -5203,7 +5212,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5211,16 +5220,16 @@
         <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F18">
         <v>2.48</v>
@@ -5247,7 +5256,7 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O18">
         <v>1.01</v>
@@ -5445,7 +5454,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5453,16 +5462,16 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F19">
         <v>2.88</v>
@@ -5573,52 +5582,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5687,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5695,28 +5704,28 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F20">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G20">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
         <v>3.55</v>
@@ -5725,211 +5734,211 @@
         <v>3.65</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q20">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="CB20" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5937,16 +5946,16 @@
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F21">
         <v>1.1</v>
@@ -5967,16 +5976,16 @@
         <v>930</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P21">
         <v>1.1</v>
@@ -5985,193 +5994,193 @@
         <v>1.01</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6179,22 +6188,22 @@
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F22">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G22">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H22">
         <v>3</v>
@@ -6209,211 +6218,211 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P22">
         <v>3.9</v>
       </c>
       <c r="Q22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6421,16 +6430,16 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F23">
         <v>1.1</v>
@@ -6448,7 +6457,7 @@
         <v>1.1</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>920</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6655,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6663,16 +6672,16 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F24">
         <v>1.1</v>
@@ -6690,19 +6699,19 @@
         <v>1.1</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>880</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
         <v>1.1</v>
@@ -6711,193 +6720,193 @@
         <v>1.01</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6905,16 +6914,16 @@
         <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F25">
         <v>1.1</v>
@@ -6932,19 +6941,19 @@
         <v>1.1</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>920</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P25">
         <v>1.1</v>
@@ -6953,193 +6962,193 @@
         <v>1.01</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7147,16 +7156,16 @@
         <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F26">
         <v>1.1</v>
@@ -7174,19 +7183,19 @@
         <v>1.1</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>880</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26">
         <v>1.1</v>
@@ -7195,193 +7204,193 @@
         <v>1.01</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7389,58 +7398,58 @@
         <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F27">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G27">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I27">
         <v>3.6</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K27">
         <v>3.2</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P27">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q27">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T27">
         <v>2.06</v>
@@ -7449,10 +7458,10 @@
         <v>1.78</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X27">
         <v>9.4</v>
@@ -7485,7 +7494,7 @@
         <v>13.5</v>
       </c>
       <c r="AH27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI27">
         <v>90</v>
@@ -7563,67 +7572,67 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7631,16 +7640,16 @@
         <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F28">
         <v>1.1</v>
@@ -7658,19 +7667,19 @@
         <v>1.1</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>920</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P28">
         <v>1.1</v>
@@ -7679,193 +7688,193 @@
         <v>1.01</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7873,16 +7882,16 @@
         <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F29">
         <v>1.1</v>
@@ -7900,19 +7909,19 @@
         <v>1.1</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>930</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P29">
         <v>1.1</v>
@@ -7921,193 +7930,193 @@
         <v>1.01</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8115,16 +8124,16 @@
         <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F30">
         <v>1.1</v>
@@ -8145,211 +8154,211 @@
         <v>950</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P30">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Q30">
         <v>1.01</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8357,16 +8366,16 @@
         <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F31">
         <v>1.1</v>
@@ -8384,19 +8393,19 @@
         <v>1.1</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>880</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P31">
         <v>1.1</v>
@@ -8405,193 +8414,193 @@
         <v>1.01</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8599,16 +8608,16 @@
         <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F32">
         <v>1.1</v>
@@ -8626,19 +8635,19 @@
         <v>1.1</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>880</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P32">
         <v>1.1</v>
@@ -8647,193 +8656,193 @@
         <v>1.01</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8841,16 +8850,16 @@
         <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F33">
         <v>1.5</v>
@@ -9075,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9083,19 +9092,19 @@
         <v>81</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E34" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F34">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G34">
         <v>5.5</v>
@@ -9107,7 +9116,7 @@
         <v>2.1</v>
       </c>
       <c r="J34">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K34">
         <v>4.2</v>
@@ -9317,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9325,16 +9334,16 @@
         <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F35">
         <v>1.1</v>
@@ -9352,7 +9361,7 @@
         <v>1.1</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9559,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9567,16 +9576,16 @@
         <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F36">
         <v>2.26</v>
@@ -9801,42 +9810,42 @@
         <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9851,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q37">
         <v>1.01</v>
@@ -10043,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -10051,16 +10060,16 @@
         <v>91</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F38">
         <v>1.1</v>
@@ -10285,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10293,16 +10302,16 @@
         <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E39" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F39">
         <v>1.1</v>
@@ -10527,24 +10536,24 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F40">
         <v>1.1</v>
@@ -10562,7 +10571,7 @@
         <v>1.1</v>
       </c>
       <c r="K40">
-        <v>950</v>
+        <v>870</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10577,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q40">
         <v>1.01</v>
@@ -10769,42 +10778,42 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F41">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10819,7 +10828,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Q41">
         <v>1.01</v>
@@ -11011,7 +11020,7 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -11019,19 +11028,19 @@
         <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E42" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F42">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G42">
         <v>2.26</v>
@@ -11040,7 +11049,7 @@
         <v>3.65</v>
       </c>
       <c r="I42">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J42">
         <v>3.4</v>
@@ -11061,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q42">
         <v>1.97</v>
@@ -11253,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11261,19 +11270,19 @@
         <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E43" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F43">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G43">
         <v>1000</v>
@@ -11282,13 +11291,13 @@
         <v>1.1</v>
       </c>
       <c r="I43">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J43">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K43">
-        <v>1000</v>
+        <v>830</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11495,7 +11504,7 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11503,16 +11512,16 @@
         <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F44">
         <v>1.1</v>
@@ -11530,7 +11539,7 @@
         <v>1.1</v>
       </c>
       <c r="K44">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11737,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11745,16 +11754,16 @@
         <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F45">
         <v>1.1</v>
@@ -11772,7 +11781,7 @@
         <v>1.1</v>
       </c>
       <c r="K45">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -11979,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11987,16 +11996,16 @@
         <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F46">
         <v>1.1</v>
@@ -12014,7 +12023,7 @@
         <v>1.1</v>
       </c>
       <c r="K46">
-        <v>100</v>
+        <v>930</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -12221,7 +12230,7 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12229,19 +12238,19 @@
         <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F47">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G47">
         <v>3.95</v>
@@ -12250,13 +12259,13 @@
         <v>2.5</v>
       </c>
       <c r="I47">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J47">
         <v>2.9</v>
       </c>
       <c r="K47">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12271,7 +12280,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q47">
         <v>3.55</v>
@@ -12286,7 +12295,7 @@
         <v>2.72</v>
       </c>
       <c r="U47">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -12298,7 +12307,7 @@
         <v>6.6</v>
       </c>
       <c r="Y47">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z47">
         <v>14.5</v>
@@ -12307,10 +12316,10 @@
         <v>44</v>
       </c>
       <c r="AB47">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC47">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD47">
         <v>15</v>
@@ -12319,19 +12328,19 @@
         <v>48</v>
       </c>
       <c r="AF47">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG47">
         <v>21</v>
       </c>
       <c r="AH47">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI47">
         <v>110</v>
       </c>
       <c r="AJ47">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK47">
         <v>90</v>
@@ -12340,7 +12349,7 @@
         <v>150</v>
       </c>
       <c r="AM47">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AN47">
         <v>170</v>
@@ -12349,7 +12358,7 @@
         <v>60</v>
       </c>
       <c r="AP47">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ47">
         <v>5.5</v>
@@ -12358,7 +12367,7 @@
         <v>11.5</v>
       </c>
       <c r="AS47">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT47">
         <v>7.6</v>
@@ -12370,37 +12379,37 @@
         <v>12</v>
       </c>
       <c r="AW47">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX47">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AY47">
         <v>16.5</v>
       </c>
       <c r="AZ47">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA47">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB47">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BC47">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD47">
+        <v>9</v>
+      </c>
+      <c r="BE47">
         <v>9.4</v>
       </c>
-      <c r="BD47">
-        <v>9.4</v>
-      </c>
-      <c r="BE47">
-        <v>9.6</v>
-      </c>
       <c r="BF47">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG47">
-        <v>8.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BH47">
         <v>0</v>
@@ -12463,7 +12472,7 @@
         <v>0</v>
       </c>
       <c r="CB47" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:80">
@@ -12471,25 +12480,25 @@
         <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E48" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F48">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G48">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H48">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I48">
         <v>1.47</v>
@@ -12498,7 +12507,7 @@
         <v>5</v>
       </c>
       <c r="K48">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -12510,25 +12519,25 @@
         <v>4.8</v>
       </c>
       <c r="O48">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q48">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R48">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S48">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T48">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U48">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -12543,16 +12552,16 @@
         <v>9.6</v>
       </c>
       <c r="Z48">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AA48">
         <v>13</v>
       </c>
       <c r="AB48">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AC48">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD48">
         <v>11</v>
@@ -12561,10 +12570,10 @@
         <v>15</v>
       </c>
       <c r="AF48">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG48">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH48">
         <v>24</v>
@@ -12582,7 +12591,7 @@
         <v>120</v>
       </c>
       <c r="AM48">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN48">
         <v>170</v>
@@ -12591,7 +12600,7 @@
         <v>6.4</v>
       </c>
       <c r="AP48">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ48">
         <v>8.199999999999999</v>
@@ -12600,10 +12609,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS48">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT48">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AU48">
         <v>10</v>
@@ -12615,34 +12624,34 @@
         <v>13</v>
       </c>
       <c r="AX48">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY48">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AZ48">
         <v>19.5</v>
       </c>
       <c r="BA48">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BB48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC48">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BD48">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BE48">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF48">
         <v>16.5</v>
       </c>
       <c r="BG48">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH48">
         <v>3.9</v>
@@ -12651,10 +12660,10 @@
         <v>3.65</v>
       </c>
       <c r="BJ48">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK48">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL48">
         <v>140</v>
@@ -12663,7 +12672,7 @@
         <v>1.01</v>
       </c>
       <c r="BN48">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BO48">
         <v>10</v>
@@ -12705,7 +12714,7 @@
         <v>10</v>
       </c>
       <c r="CB48" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:80">
@@ -12713,25 +12722,25 @@
         <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E49" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F49">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G49">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H49">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I49">
         <v>6.6</v>
@@ -12755,16 +12764,16 @@
         <v>1.3</v>
       </c>
       <c r="P49">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q49">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="R49">
         <v>1.4</v>
       </c>
       <c r="S49">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T49">
         <v>1.99</v>
@@ -12782,13 +12791,13 @@
         <v>17</v>
       </c>
       <c r="Y49">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z49">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA49">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB49">
         <v>8.800000000000001</v>
@@ -12818,7 +12827,7 @@
         <v>15.5</v>
       </c>
       <c r="AK49">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL49">
         <v>40</v>
@@ -12827,7 +12836,7 @@
         <v>150</v>
       </c>
       <c r="AN49">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO49">
         <v>140</v>
@@ -12842,7 +12851,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS49">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT49">
         <v>8.199999999999999</v>
@@ -12854,7 +12863,7 @@
         <v>20</v>
       </c>
       <c r="AW49">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX49">
         <v>8.4</v>
@@ -12866,7 +12875,7 @@
         <v>19</v>
       </c>
       <c r="BA49">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB49">
         <v>12.5</v>
@@ -12878,13 +12887,13 @@
         <v>30</v>
       </c>
       <c r="BE49">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF49">
         <v>7.8</v>
       </c>
       <c r="BG49">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -12947,7 +12956,7 @@
         <v>1.01</v>
       </c>
       <c r="CB49" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:80">
@@ -12955,31 +12964,31 @@
         <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F50">
+        <v>1.49</v>
+      </c>
+      <c r="G50">
         <v>1.5</v>
-      </c>
-      <c r="G50">
-        <v>1.51</v>
       </c>
       <c r="H50">
         <v>7.6</v>
       </c>
       <c r="I50">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J50">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K50">
         <v>5</v>
@@ -12997,7 +13006,7 @@
         <v>1.3</v>
       </c>
       <c r="P50">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q50">
         <v>1.86</v>
@@ -13006,7 +13015,7 @@
         <v>1.41</v>
       </c>
       <c r="S50">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T50">
         <v>2.06</v>
@@ -13039,10 +13048,10 @@
         <v>11</v>
       </c>
       <c r="AD50">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE50">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF50">
         <v>8.6</v>
@@ -13096,7 +13105,7 @@
         <v>24</v>
       </c>
       <c r="AW50">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX50">
         <v>7.8</v>
@@ -13189,7 +13198,7 @@
         <v>0</v>
       </c>
       <c r="CB50" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:80">
@@ -13197,16 +13206,16 @@
         <v>87</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E51" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F51">
         <v>1.98</v>
@@ -13239,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -13431,7 +13440,7 @@
         <v>0</v>
       </c>
       <c r="CB51" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:80">
@@ -13439,34 +13448,34 @@
         <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E52" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G52">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H52">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I52">
         <v>4.5</v>
       </c>
       <c r="J52">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K52">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -13481,10 +13490,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q52">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -13673,7 +13682,7 @@
         <v>0</v>
       </c>
       <c r="CB52" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:80">
@@ -13681,16 +13690,16 @@
         <v>94</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E53" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F53">
         <v>1.1</v>
@@ -13708,7 +13717,7 @@
         <v>1.1</v>
       </c>
       <c r="K53">
-        <v>100</v>
+        <v>910</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -13915,7 +13924,7 @@
         <v>0</v>
       </c>
       <c r="CB53" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:80">
@@ -13923,16 +13932,16 @@
         <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F54">
         <v>1.1</v>
@@ -13950,7 +13959,7 @@
         <v>1.1</v>
       </c>
       <c r="K54">
-        <v>100</v>
+        <v>930</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -14157,7 +14166,7 @@
         <v>0</v>
       </c>
       <c r="CB54" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:80">
@@ -14165,16 +14174,16 @@
         <v>95</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F55">
         <v>1.91</v>
@@ -14399,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="CB55" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:80">
@@ -14407,16 +14416,16 @@
         <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E56" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F56">
         <v>1.99</v>
@@ -14641,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="CB56" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:80">
@@ -14649,34 +14658,34 @@
         <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E57" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F57">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="G57">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H57">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="I57">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J57">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K57">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -14691,10 +14700,10 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="Q57">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -14883,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="CB57" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:80">
@@ -14891,19 +14900,19 @@
         <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F58">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G58">
         <v>1.93</v>
@@ -14933,10 +14942,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q58">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -15125,7 +15134,7 @@
         <v>0</v>
       </c>
       <c r="CB58" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:80">
@@ -15133,19 +15142,19 @@
         <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E59" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F59">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G59">
         <v>1.44</v>
@@ -15154,7 +15163,7 @@
         <v>8</v>
       </c>
       <c r="I59">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J59">
         <v>5.5</v>
@@ -15295,7 +15304,7 @@
         <v>12.5</v>
       </c>
       <c r="BD59">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BE59">
         <v>11.5</v>
@@ -15367,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="CB59" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="1:80">
@@ -15375,16 +15384,16 @@
         <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F60">
         <v>3.15</v>
@@ -15399,7 +15408,7 @@
         <v>2.56</v>
       </c>
       <c r="J60">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K60">
         <v>3.5</v>
@@ -15408,10 +15417,10 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N60">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O60">
         <v>1.39</v>
@@ -15429,10 +15438,10 @@
         <v>3.85</v>
       </c>
       <c r="T60">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U60">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -15609,7 +15618,7 @@
         <v>1.01</v>
       </c>
       <c r="CB60" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:80">
@@ -15617,16 +15626,16 @@
         <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E61" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F61">
         <v>2.56</v>
@@ -15659,22 +15668,22 @@
         <v>1.17</v>
       </c>
       <c r="P61">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q61">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R61">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="S61">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T61">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U61">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -15683,19 +15692,19 @@
         <v>0</v>
       </c>
       <c r="X61">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y61">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z61">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA61">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB61">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC61">
         <v>10</v>
@@ -15734,19 +15743,19 @@
         <v>12.5</v>
       </c>
       <c r="AO61">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP61">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ61">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR61">
         <v>19</v>
       </c>
       <c r="AS61">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT61">
         <v>15.5</v>
@@ -15767,28 +15776,28 @@
         <v>11</v>
       </c>
       <c r="AZ61">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA61">
+        <v>7.6</v>
+      </c>
+      <c r="BB61">
         <v>8</v>
-      </c>
-      <c r="BB61">
-        <v>8.4</v>
       </c>
       <c r="BC61">
         <v>19.5</v>
       </c>
       <c r="BD61">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE61">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF61">
         <v>10.5</v>
       </c>
       <c r="BG61">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH61">
         <v>1000</v>
@@ -15851,42 +15860,42 @@
         <v>0</v>
       </c>
       <c r="CB61" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:80">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E62" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -15901,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="Q62">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -16093,42 +16102,42 @@
         <v>0</v>
       </c>
       <c r="CB62" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:80">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E63" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F63">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -16143,10 +16152,10 @@
         <v>0</v>
       </c>
       <c r="P63">
-        <v>1.92</v>
+        <v>1.05</v>
       </c>
       <c r="Q63">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -16335,42 +16344,42 @@
         <v>0</v>
       </c>
       <c r="CB63" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="1:80">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E64" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F64">
-        <v>2.08</v>
+        <v>1.34</v>
       </c>
       <c r="G64">
-        <v>2.22</v>
+        <v>1.53</v>
       </c>
       <c r="H64">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="I64">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="J64">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="K64">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -16385,10 +16394,10 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="Q64">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -16577,42 +16586,42 @@
         <v>0</v>
       </c>
       <c r="CB64" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:80">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s">
         <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F65">
-        <v>1.1</v>
+        <v>2.08</v>
       </c>
       <c r="G65">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H65">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="I65">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J65">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="K65">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -16627,10 +16636,10 @@
         <v>0</v>
       </c>
       <c r="P65">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="Q65">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -16819,7 +16828,249 @@
         <v>0</v>
       </c>
       <c r="CB65" t="s">
-        <v>247</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" spans="1:80">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" t="s">
+        <v>249</v>
+      </c>
+      <c r="F66">
+        <v>2.44</v>
+      </c>
+      <c r="G66">
+        <v>2.96</v>
+      </c>
+      <c r="H66">
+        <v>3.25</v>
+      </c>
+      <c r="I66">
+        <v>5</v>
+      </c>
+      <c r="J66">
+        <v>2.58</v>
+      </c>
+      <c r="K66">
+        <v>3.55</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>1.42</v>
+      </c>
+      <c r="Q66">
+        <v>2.5</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66">
+        <v>0</v>
+      </c>
+      <c r="AI66">
+        <v>0</v>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>0</v>
+      </c>
+      <c r="AN66">
+        <v>0</v>
+      </c>
+      <c r="AO66">
+        <v>0</v>
+      </c>
+      <c r="AP66">
+        <v>0</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66">
+        <v>0</v>
+      </c>
+      <c r="AV66">
+        <v>0</v>
+      </c>
+      <c r="AW66">
+        <v>0</v>
+      </c>
+      <c r="AX66">
+        <v>0</v>
+      </c>
+      <c r="AY66">
+        <v>0</v>
+      </c>
+      <c r="AZ66">
+        <v>0</v>
+      </c>
+      <c r="BA66">
+        <v>0</v>
+      </c>
+      <c r="BB66">
+        <v>0</v>
+      </c>
+      <c r="BC66">
+        <v>0</v>
+      </c>
+      <c r="BD66">
+        <v>0</v>
+      </c>
+      <c r="BE66">
+        <v>0</v>
+      </c>
+      <c r="BF66">
+        <v>0</v>
+      </c>
+      <c r="BG66">
+        <v>0</v>
+      </c>
+      <c r="BH66">
+        <v>0</v>
+      </c>
+      <c r="BI66">
+        <v>0</v>
+      </c>
+      <c r="BJ66">
+        <v>0</v>
+      </c>
+      <c r="BK66">
+        <v>0</v>
+      </c>
+      <c r="BL66">
+        <v>0</v>
+      </c>
+      <c r="BM66">
+        <v>0</v>
+      </c>
+      <c r="BN66">
+        <v>0</v>
+      </c>
+      <c r="BO66">
+        <v>0</v>
+      </c>
+      <c r="BP66">
+        <v>0</v>
+      </c>
+      <c r="BQ66">
+        <v>0</v>
+      </c>
+      <c r="BR66">
+        <v>0</v>
+      </c>
+      <c r="BS66">
+        <v>0</v>
+      </c>
+      <c r="BT66">
+        <v>0</v>
+      </c>
+      <c r="BU66">
+        <v>0</v>
+      </c>
+      <c r="BV66">
+        <v>0</v>
+      </c>
+      <c r="BW66">
+        <v>0</v>
+      </c>
+      <c r="BX66">
+        <v>0</v>
+      </c>
+      <c r="BY66">
+        <v>0</v>
+      </c>
+      <c r="BZ66">
+        <v>0</v>
+      </c>
+      <c r="CA66">
+        <v>0</v>
+      </c>
+      <c r="CB66" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -553,15 +553,15 @@
     <t>Juventud De Las Piedras</t>
   </si>
   <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
     <t>Germany</t>
   </si>
   <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
     <t>Cerrito</t>
   </si>
   <si>
@@ -751,15 +751,15 @@
     <t>Cerro</t>
   </si>
   <si>
+    <t>Republic of Ireland</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
     <t>Greece</t>
   </si>
   <si>
-    <t>Republic of Ireland</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
     <t>La Luz FC</t>
   </si>
   <si>
@@ -775,7 +775,7 @@
     <t>HUSA Agadir</t>
   </si>
   <si>
-    <t>2026-09-25 13:21:39</t>
+    <t>2026-09-25 15:43:10</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1378,7 @@
         <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1393,7 +1393,7 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O2">
         <v>1.19</v>
@@ -1405,7 +1405,7 @@
         <v>1.59</v>
       </c>
       <c r="R2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S2">
         <v>2.46</v>
@@ -1417,13 +1417,13 @@
         <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
         <v>1.74</v>
       </c>
       <c r="X2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2">
         <v>18</v>
@@ -1435,7 +1435,7 @@
         <v>50</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC2">
         <v>9.6</v>
@@ -1447,7 +1447,7 @@
         <v>30</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1465,7 +1465,7 @@
         <v>22</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AM2">
         <v>55</v>
@@ -1474,10 +1474,10 @@
         <v>12</v>
       </c>
       <c r="AO2">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1489,7 +1489,7 @@
         <v>28</v>
       </c>
       <c r="AT2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU2">
         <v>8.800000000000001</v>
@@ -1498,7 +1498,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX2">
         <v>16</v>
@@ -1614,7 +1614,7 @@
         <v>1.48</v>
       </c>
       <c r="G3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1623,10 +1623,10 @@
         <v>7.4</v>
       </c>
       <c r="J3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1791,7 +1791,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
         <v>3.6</v>
@@ -1859,7 +1859,7 @@
         <v>2.42</v>
       </c>
       <c r="H4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>3.15</v>
@@ -1883,7 +1883,7 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
         <v>1.66</v>
@@ -1895,7 +1895,7 @@
         <v>2.66</v>
       </c>
       <c r="T4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U4">
         <v>2.62</v>
@@ -1916,10 +1916,10 @@
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
         <v>9.199999999999999</v>
@@ -2018,7 +2018,7 @@
         <v>4.1</v>
       </c>
       <c r="BI4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ4">
         <v>8.6</v>
@@ -2039,7 +2039,7 @@
         <v>5</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
         <v>13.5</v>
@@ -2048,7 +2048,7 @@
         <v>27</v>
       </c>
       <c r="BS4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
@@ -2069,10 +2069,10 @@
         <v>22</v>
       </c>
       <c r="BZ4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>253</v>
@@ -2095,49 +2095,49 @@
         <v>190</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G5">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
         <v>5</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U5">
         <v>2.18</v>
@@ -2146,16 +2146,16 @@
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -2167,28 +2167,28 @@
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL5">
         <v>32</v>
@@ -2197,37 +2197,37 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AS5">
         <v>44</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AW5">
         <v>34</v>
       </c>
       <c r="AX5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -2236,43 +2236,43 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD5">
         <v>19.5</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>1.61</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>2.14</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN5">
         <v>5.4</v>
@@ -2284,13 +2284,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>12</v>
+        <v>1.56</v>
       </c>
       <c r="BT5">
         <v>1000</v>
@@ -2302,19 +2302,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="CB5" t="s">
         <v>253</v>
@@ -2337,13 +2337,13 @@
         <v>191</v>
       </c>
       <c r="F6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H6">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
         <v>2.94</v>
@@ -2367,7 +2367,7 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
         <v>1.64</v>
@@ -2499,64 +2499,64 @@
         <v>15.5</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BL6">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>253</v>
@@ -2585,7 +2585,7 @@
         <v>2.34</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
         <v>4.2</v>
@@ -2594,13 +2594,13 @@
         <v>3.35</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
         <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
         <v>3.4</v>
@@ -2854,7 +2854,7 @@
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R8">
         <v>1.4</v>
@@ -2866,7 +2866,7 @@
         <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
         <v>1.4</v>
@@ -2923,7 +2923,7 @@
         <v>110</v>
       </c>
       <c r="AN8">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO8">
         <v>42</v>
@@ -2938,7 +2938,7 @@
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT8">
         <v>9.6</v>
@@ -2950,7 +2950,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX8">
         <v>13</v>
@@ -2962,25 +2962,25 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB8">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BC8">
         <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE8">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF8">
         <v>15</v>
       </c>
       <c r="BG8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3063,19 +3063,19 @@
         <v>194</v>
       </c>
       <c r="F9">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G9">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H9">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I9">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.1</v>
@@ -3108,16 +3108,16 @@
         <v>1.56</v>
       </c>
       <c r="U9">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
         <v>1.54</v>
       </c>
       <c r="X9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y9">
         <v>15.5</v>
@@ -3129,61 +3129,61 @@
         <v>38</v>
       </c>
       <c r="AB9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI9">
+        <v>30</v>
+      </c>
+      <c r="AJ9">
+        <v>42</v>
+      </c>
+      <c r="AK9">
+        <v>28</v>
+      </c>
+      <c r="AL9">
         <v>32</v>
       </c>
-      <c r="AJ9">
-        <v>46</v>
-      </c>
-      <c r="AK9">
-        <v>26</v>
-      </c>
-      <c r="AL9">
-        <v>36</v>
-      </c>
       <c r="AM9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="AN9">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ9">
         <v>14</v>
       </c>
       <c r="AR9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AT9">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU9">
         <v>8.6</v>
@@ -3195,34 +3195,34 @@
         <v>21</v>
       </c>
       <c r="AX9">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY9">
         <v>12</v>
       </c>
       <c r="AZ9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB9">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BC9">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BD9">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE9">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BF9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH9">
         <v>5.5</v>
@@ -3252,7 +3252,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -3261,10 +3261,10 @@
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3425,7 +3425,7 @@
         <v>28</v>
       </c>
       <c r="AT10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU10">
         <v>8.800000000000001</v>
@@ -3547,7 +3547,7 @@
         <v>196</v>
       </c>
       <c r="F11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G11">
         <v>1.3</v>
@@ -3559,7 +3559,7 @@
         <v>12</v>
       </c>
       <c r="J11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K11">
         <v>7.4</v>
@@ -3568,22 +3568,22 @@
         <v>1.24</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S11">
         <v>2.16</v>
@@ -3616,10 +3616,10 @@
         <v>13</v>
       </c>
       <c r="AC11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE11">
         <v>1000</v>
@@ -3649,13 +3649,13 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AQ11">
         <v>25</v>
@@ -3667,7 +3667,7 @@
         <v>55</v>
       </c>
       <c r="AT11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU11">
         <v>14</v>
@@ -3697,7 +3697,7 @@
         <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE11">
         <v>40</v>
@@ -3742,7 +3742,7 @@
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT11">
         <v>1000</v>
@@ -3801,7 +3801,7 @@
         <v>3.7</v>
       </c>
       <c r="J12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3828,7 +3828,7 @@
         <v>1.83</v>
       </c>
       <c r="S12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T12">
         <v>1.45</v>
@@ -3867,10 +3867,10 @@
         <v>36</v>
       </c>
       <c r="AF12">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12">
         <v>14</v>
@@ -3879,7 +3879,7 @@
         <v>34</v>
       </c>
       <c r="AJ12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK12">
         <v>18.5</v>
@@ -3912,7 +3912,7 @@
         <v>15.5</v>
       </c>
       <c r="AU12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12">
         <v>14</v>
@@ -3921,7 +3921,7 @@
         <v>24</v>
       </c>
       <c r="AX12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3948,7 +3948,7 @@
         <v>7.6</v>
       </c>
       <c r="BG12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4040,7 +4040,7 @@
         <v>2.16</v>
       </c>
       <c r="I13">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J13">
         <v>3.85</v>
@@ -4064,7 +4064,7 @@
         <v>2.46</v>
       </c>
       <c r="Q13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R13">
         <v>1.59</v>
@@ -4073,13 +4073,13 @@
         <v>2.54</v>
       </c>
       <c r="T13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U13">
         <v>2.58</v>
       </c>
       <c r="V13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
         <v>1.4</v>
@@ -4273,10 +4273,10 @@
         <v>199</v>
       </c>
       <c r="F14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G14">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H14">
         <v>5.6</v>
@@ -4303,7 +4303,7 @@
         <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q14">
         <v>1.73</v>
@@ -4312,19 +4312,19 @@
         <v>1.49</v>
       </c>
       <c r="S14">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T14">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U14">
         <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X14">
         <v>25</v>
@@ -4339,7 +4339,7 @@
         <v>170</v>
       </c>
       <c r="AB14">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
@@ -4384,13 +4384,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ14">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AR14">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS14">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AT14">
         <v>8.6</v>
@@ -4399,10 +4399,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AW14">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4411,28 +4411,28 @@
         <v>9</v>
       </c>
       <c r="AZ14">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BA14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB14">
         <v>13.5</v>
       </c>
       <c r="BC14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD14">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BF14">
         <v>7</v>
       </c>
       <c r="BG14">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -5271,22 +5271,22 @@
         <v>1.49</v>
       </c>
       <c r="P18">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q18">
         <v>2.56</v>
       </c>
       <c r="R18">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S18">
         <v>5.1</v>
       </c>
       <c r="T18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V18">
         <v>1.41</v>
@@ -5740,16 +5740,16 @@
         <v>3.4</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O20">
         <v>1.01</v>
@@ -5776,7 +5776,7 @@
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5967,40 +5967,40 @@
         <v>206</v>
       </c>
       <c r="F21">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="G21">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="H21">
+        <v>3.05</v>
+      </c>
+      <c r="I21">
         <v>3.2</v>
       </c>
-      <c r="I21">
-        <v>3.45</v>
-      </c>
       <c r="J21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K21">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21">
         <v>1.35</v>
       </c>
       <c r="M21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N21">
         <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R21">
         <v>1.38</v>
@@ -6015,142 +6015,142 @@
         <v>2.22</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W21">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y21">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z21">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA21">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE21">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF21">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM21">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN21">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP21">
         <v>13</v>
       </c>
       <c r="AQ21">
+        <v>11</v>
+      </c>
+      <c r="AR21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS21">
+        <v>44</v>
+      </c>
+      <c r="AT21">
+        <v>10</v>
+      </c>
+      <c r="AU21">
+        <v>7.2</v>
+      </c>
+      <c r="AV21">
         <v>12</v>
       </c>
-      <c r="AR21">
-        <v>20</v>
-      </c>
-      <c r="AS21">
-        <v>8.6</v>
-      </c>
-      <c r="AT21">
-        <v>9.6</v>
-      </c>
-      <c r="AU21">
-        <v>7.4</v>
-      </c>
-      <c r="AV21">
+      <c r="AW21">
+        <v>29</v>
+      </c>
+      <c r="AX21">
+        <v>14.5</v>
+      </c>
+      <c r="AY21">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21">
+        <v>15</v>
+      </c>
+      <c r="BA21">
+        <v>36</v>
+      </c>
+      <c r="BB21">
+        <v>30</v>
+      </c>
+      <c r="BC21">
+        <v>23</v>
+      </c>
+      <c r="BD21">
+        <v>32</v>
+      </c>
+      <c r="BE21">
         <v>12.5</v>
       </c>
-      <c r="AW21">
-        <v>8</v>
-      </c>
-      <c r="AX21">
-        <v>13.5</v>
-      </c>
-      <c r="AY21">
-        <v>10</v>
-      </c>
-      <c r="AZ21">
-        <v>14.5</v>
-      </c>
-      <c r="BA21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB21">
-        <v>7.6</v>
-      </c>
-      <c r="BC21">
-        <v>22</v>
-      </c>
-      <c r="BD21">
-        <v>8</v>
-      </c>
-      <c r="BE21">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF21">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BG21">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="BP21">
         <v>1000</v>
@@ -6162,7 +6162,7 @@
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BT21">
         <v>1000</v>
@@ -6174,19 +6174,19 @@
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CB21" t="s">
         <v>253</v>
@@ -6460,7 +6460,7 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J23">
         <v>4.4</v>
@@ -6478,7 +6478,7 @@
         <v>7.6</v>
       </c>
       <c r="O23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P23">
         <v>3.9</v>
@@ -6487,10 +6487,10 @@
         <v>1.3</v>
       </c>
       <c r="R23">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T23">
         <v>1.3</v>
@@ -6499,7 +6499,7 @@
         <v>3.15</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
         <v>1.86</v>
@@ -6526,7 +6526,7 @@
         <v>25</v>
       </c>
       <c r="AE23">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF23">
         <v>36</v>
@@ -6559,16 +6559,16 @@
         <v>15</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AQ23">
         <v>19</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AT23">
         <v>16</v>
@@ -6583,7 +6583,7 @@
         <v>16.5</v>
       </c>
       <c r="AX23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY23">
         <v>10</v>
@@ -6604,13 +6604,13 @@
         <v>15</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BF23">
         <v>5.2</v>
       </c>
       <c r="BG23">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6983,7 +6983,7 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25">
         <v>1.02</v>
@@ -7225,7 +7225,7 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W26">
         <v>1.02</v>
@@ -7452,7 +7452,7 @@
         <v>1.1</v>
       </c>
       <c r="Q27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R27">
         <v>1.05</v>
@@ -7664,10 +7664,10 @@
         <v>2.52</v>
       </c>
       <c r="G28">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I28">
         <v>3.5</v>
@@ -7682,22 +7682,22 @@
         <v>1.57</v>
       </c>
       <c r="M28">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N28">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="O28">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="P28">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S28">
         <v>5</v>
@@ -7727,7 +7727,7 @@
         <v>75</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28">
         <v>7.4</v>
@@ -7736,7 +7736,7 @@
         <v>16</v>
       </c>
       <c r="AE28">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF28">
         <v>16</v>
@@ -7763,7 +7763,7 @@
         <v>200</v>
       </c>
       <c r="AN28">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO28">
         <v>80</v>
@@ -7772,13 +7772,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR28">
         <v>18.5</v>
       </c>
       <c r="AS28">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT28">
         <v>6.8</v>
@@ -7799,13 +7799,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC28">
         <v>8</v>
@@ -7814,10 +7814,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE28">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BG28">
         <v>9</v>
@@ -7912,7 +7912,7 @@
         <v>1.1</v>
       </c>
       <c r="I29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J29">
         <v>1.1</v>
@@ -7951,10 +7951,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -8154,7 +8154,7 @@
         <v>1.1</v>
       </c>
       <c r="I30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J30">
         <v>1.1</v>
@@ -8193,10 +8193,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8435,7 +8435,7 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W31">
         <v>1.02</v>
@@ -8677,7 +8677,7 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32">
         <v>1.01</v>
@@ -8919,7 +8919,7 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33">
         <v>1.02</v>
@@ -8979,52 +8979,52 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF33">
         <v>1.01</v>
@@ -9137,7 +9137,7 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="O34">
         <v>1.02</v>
@@ -9221,52 +9221,52 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF34">
         <v>1.01</v>
@@ -9355,28 +9355,28 @@
         <v>220</v>
       </c>
       <c r="F35">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G35">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H35">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I35">
         <v>2.08</v>
       </c>
       <c r="J35">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K35">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L35">
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N35">
         <v>2.94</v>
@@ -9385,22 +9385,22 @@
         <v>1.41</v>
       </c>
       <c r="P35">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q35">
         <v>2.18</v>
       </c>
       <c r="R35">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T35">
         <v>1.92</v>
       </c>
       <c r="U35">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V35">
         <v>1.92</v>
@@ -9412,10 +9412,10 @@
         <v>22</v>
       </c>
       <c r="Y35">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z35">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA35">
         <v>1000</v>
@@ -9424,10 +9424,10 @@
         <v>34</v>
       </c>
       <c r="AC35">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD35">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE35">
         <v>1000</v>
@@ -9463,58 +9463,58 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="AQ35">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AR35">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AU35">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AV35">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AX35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AY35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AZ35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BA35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BB35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BC35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BD35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BE35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9947,52 +9947,52 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF37">
         <v>1.01</v>
@@ -10081,16 +10081,16 @@
         <v>223</v>
       </c>
       <c r="F38">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="G38">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H38">
         <v>5.5</v>
       </c>
       <c r="I38">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J38">
         <v>3.75</v>
@@ -10108,7 +10108,7 @@
         <v>3.3</v>
       </c>
       <c r="O38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P38">
         <v>1.76</v>
@@ -10123,16 +10123,16 @@
         <v>3.6</v>
       </c>
       <c r="T38">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U38">
         <v>1.76</v>
       </c>
       <c r="V38">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W38">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X38">
         <v>29</v>
@@ -10147,10 +10147,10 @@
         <v>1000</v>
       </c>
       <c r="AB38">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC38">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD38">
         <v>1000</v>
@@ -10159,10 +10159,10 @@
         <v>1000</v>
       </c>
       <c r="AF38">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG38">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH38">
         <v>1000</v>
@@ -10183,22 +10183,22 @@
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AO38">
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>8.800000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="AQ38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AS38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AT38">
         <v>5.8</v>
@@ -10207,10 +10207,10 @@
         <v>6.4</v>
       </c>
       <c r="AV38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AW38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AX38">
         <v>6.6</v>
@@ -10219,28 +10219,28 @@
         <v>7.2</v>
       </c>
       <c r="AZ38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BA38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BB38">
-        <v>10.5</v>
+        <v>1.59</v>
       </c>
       <c r="BC38">
-        <v>11.5</v>
+        <v>1.59</v>
       </c>
       <c r="BD38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BE38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF38">
         <v>6.8</v>
       </c>
       <c r="BG38">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10252,55 +10252,55 @@
         <v>1000</v>
       </c>
       <c r="BK38">
-        <v>6.4</v>
+        <v>1.26</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BN38">
         <v>1000</v>
       </c>
       <c r="BO38">
-        <v>3.55</v>
+        <v>1.41</v>
       </c>
       <c r="BP38">
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BT38">
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>5.6</v>
+        <v>1.26</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="CB38" t="s">
         <v>253</v>
@@ -10371,7 +10371,7 @@
         <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39">
         <v>1.01</v>
@@ -10431,52 +10431,52 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
@@ -10673,52 +10673,52 @@
         <v>1000</v>
       </c>
       <c r="AP40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40">
         <v>1.01</v>
@@ -10855,7 +10855,7 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W41">
         <v>1.02</v>
@@ -10915,52 +10915,52 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41">
         <v>1.01</v>
@@ -11157,52 +11157,52 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42">
         <v>1.01</v>
@@ -11315,7 +11315,7 @@
         <v>1.07</v>
       </c>
       <c r="N43">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O43">
         <v>1.33</v>
@@ -11324,7 +11324,7 @@
         <v>1.96</v>
       </c>
       <c r="Q43">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R43">
         <v>1.37</v>
@@ -11342,10 +11342,10 @@
         <v>1.33</v>
       </c>
       <c r="W43">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X43">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y43">
         <v>15</v>
@@ -11390,13 +11390,13 @@
         <v>38</v>
       </c>
       <c r="AM43">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN43">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO43">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP43">
         <v>12.5</v>
@@ -11408,7 +11408,7 @@
         <v>21</v>
       </c>
       <c r="AS43">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AT43">
         <v>8.800000000000001</v>
@@ -11429,13 +11429,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ43">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA43">
         <v>42</v>
       </c>
       <c r="BB43">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC43">
         <v>20</v>
@@ -11444,7 +11444,7 @@
         <v>29</v>
       </c>
       <c r="BE43">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF43">
         <v>14</v>
@@ -11542,7 +11542,7 @@
         <v>1.12</v>
       </c>
       <c r="I44">
-        <v>9.4</v>
+        <v>190</v>
       </c>
       <c r="J44">
         <v>1.13</v>
@@ -11557,7 +11557,7 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="O44">
         <v>1.29</v>
@@ -11572,7 +11572,7 @@
         <v>1.07</v>
       </c>
       <c r="S44">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
         <v>1.01</v>
@@ -12292,7 +12292,7 @@
         <v>1.1</v>
       </c>
       <c r="Q47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R47">
         <v>1.05</v>
@@ -12510,22 +12510,22 @@
         <v>2.52</v>
       </c>
       <c r="I48">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J48">
         <v>2.86</v>
       </c>
       <c r="K48">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="L48">
         <v>1.65</v>
       </c>
       <c r="M48">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="N48">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O48">
         <v>1.83</v>
@@ -12534,31 +12534,31 @@
         <v>1.37</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R48">
         <v>1.12</v>
       </c>
       <c r="S48">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="T48">
         <v>2.66</v>
       </c>
       <c r="U48">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V48">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W48">
         <v>1.34</v>
       </c>
       <c r="X48">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Y48">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z48">
         <v>14</v>
@@ -12567,16 +12567,16 @@
         <v>42</v>
       </c>
       <c r="AB48">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC48">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD48">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE48">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF48">
         <v>26</v>
@@ -12585,16 +12585,16 @@
         <v>20</v>
       </c>
       <c r="AH48">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI48">
         <v>110</v>
       </c>
       <c r="AJ48">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK48">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL48">
         <v>150</v>
@@ -12609,7 +12609,7 @@
         <v>65</v>
       </c>
       <c r="AP48">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ48">
         <v>5.9</v>
@@ -12636,31 +12636,31 @@
         <v>21</v>
       </c>
       <c r="AY48">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ48">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB48">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC48">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD48">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE48">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF48">
         <v>11</v>
       </c>
       <c r="BG48">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12743,13 +12743,13 @@
         <v>234</v>
       </c>
       <c r="F49">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G49">
         <v>1.64</v>
       </c>
       <c r="H49">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I49">
         <v>6.6</v>
@@ -12758,7 +12758,7 @@
         <v>4.3</v>
       </c>
       <c r="K49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L49">
         <v>1.33</v>
@@ -12776,7 +12776,7 @@
         <v>2.04</v>
       </c>
       <c r="Q49">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R49">
         <v>1.4</v>
@@ -12785,13 +12785,13 @@
         <v>3.25</v>
       </c>
       <c r="T49">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U49">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W49">
         <v>2.56</v>
@@ -12800,10 +12800,10 @@
         <v>16.5</v>
       </c>
       <c r="Y49">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z49">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA49">
         <v>190</v>
@@ -12815,7 +12815,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD49">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE49">
         <v>100</v>
@@ -12845,10 +12845,10 @@
         <v>130</v>
       </c>
       <c r="AN49">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO49">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP49">
         <v>14</v>
@@ -12860,7 +12860,7 @@
         <v>44</v>
       </c>
       <c r="AS49">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT49">
         <v>8.199999999999999</v>
@@ -12872,10 +12872,10 @@
         <v>21</v>
       </c>
       <c r="AW49">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX49">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY49">
         <v>9.4</v>
@@ -12884,7 +12884,7 @@
         <v>19.5</v>
       </c>
       <c r="BA49">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="BB49">
         <v>13</v>
@@ -12896,13 +12896,13 @@
         <v>30</v>
       </c>
       <c r="BE49">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF49">
         <v>8</v>
       </c>
       <c r="BG49">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -12985,73 +12985,73 @@
         <v>235</v>
       </c>
       <c r="F50">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="G50">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="I50">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K50">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L50">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M50">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N50">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O50">
         <v>1.23</v>
       </c>
       <c r="P50">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q50">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R50">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S50">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T50">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V50">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y50">
+        <v>10</v>
+      </c>
+      <c r="Z50">
         <v>9.6</v>
       </c>
-      <c r="Z50">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AA50">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB50">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC50">
         <v>11.5</v>
@@ -13063,31 +13063,31 @@
         <v>14.5</v>
       </c>
       <c r="AF50">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AG50">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AH50">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI50">
         <v>34</v>
       </c>
       <c r="AJ50">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AK50">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AL50">
         <v>100</v>
       </c>
       <c r="AM50">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN50">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO50">
         <v>6.2</v>
@@ -13096,13 +13096,13 @@
         <v>19</v>
       </c>
       <c r="AQ50">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR50">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS50">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT50">
         <v>27</v>
@@ -13111,100 +13111,100 @@
         <v>10.5</v>
       </c>
       <c r="AV50">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW50">
         <v>13</v>
       </c>
       <c r="AX50">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AY50">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ50">
         <v>20</v>
       </c>
       <c r="BA50">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB50">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC50">
+        <v>13.5</v>
+      </c>
+      <c r="BD50">
+        <v>14.5</v>
+      </c>
+      <c r="BE50">
         <v>14</v>
-      </c>
-      <c r="BD50">
-        <v>80</v>
-      </c>
-      <c r="BE50">
-        <v>14.5</v>
       </c>
       <c r="BF50">
         <v>16.5</v>
       </c>
       <c r="BG50">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH50">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI50">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="BJ50">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK50">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BL50">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM50">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN50">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO50">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BP50">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BR50">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS50">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BT50">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BU50">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BV50">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BW50">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX50">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY50">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA50">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="s">
         <v>253</v>
@@ -13284,7 +13284,7 @@
         <v>17</v>
       </c>
       <c r="Y51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z51">
         <v>70</v>
@@ -13293,7 +13293,7 @@
         <v>270</v>
       </c>
       <c r="AB51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC51">
         <v>10.5</v>
@@ -13308,7 +13308,7 @@
         <v>8.6</v>
       </c>
       <c r="AG51">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH51">
         <v>26</v>
@@ -13320,7 +13320,7 @@
         <v>13</v>
       </c>
       <c r="AK51">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL51">
         <v>38</v>
@@ -13344,19 +13344,19 @@
         <v>60</v>
       </c>
       <c r="AS51">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT51">
         <v>7.4</v>
       </c>
       <c r="AU51">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV51">
         <v>26</v>
       </c>
       <c r="AW51">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AX51">
         <v>7.8</v>
@@ -13368,7 +13368,7 @@
         <v>23</v>
       </c>
       <c r="BA51">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB51">
         <v>11.5</v>
@@ -13380,13 +13380,13 @@
         <v>32</v>
       </c>
       <c r="BE51">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF51">
         <v>7</v>
       </c>
       <c r="BG51">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13469,226 +13469,226 @@
         <v>237</v>
       </c>
       <c r="F52">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H52">
         <v>4.4</v>
       </c>
       <c r="I52">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J52">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K52">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P52">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q52">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI52">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL52">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM52">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN52">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO52">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP52">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU52">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV52">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW52">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AX52">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY52">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ52">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA52">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BB52">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC52">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD52">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE52">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BF52">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG52">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BJ52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BL52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BN52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BP52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ52">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BR52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BT52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU52">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BV52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BX52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BZ52">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="CB52" t="s">
         <v>253</v>
@@ -13714,7 +13714,7 @@
         <v>2.04</v>
       </c>
       <c r="G53">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H53">
         <v>4.1</v>
@@ -13726,211 +13726,211 @@
         <v>3.5</v>
       </c>
       <c r="K53">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P53">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q53">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH53">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI53">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL53">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM53">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN53">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AO53">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP53">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU53">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV53">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW53">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX53">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY53">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ53">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA53">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB53">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC53">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD53">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE53">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF53">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG53">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BJ53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK53">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BN53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO53">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BP53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ53">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BR53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BT53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BV53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BX53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BZ53">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="CB53" t="s">
         <v>253</v>
@@ -13971,208 +13971,208 @@
         <v>910</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M54">
         <v>1.01</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P54">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Q54">
         <v>1.02</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ54">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB54" t="s">
         <v>253</v>
@@ -14213,208 +14213,208 @@
         <v>930</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M55">
         <v>1.01</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P55">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Q55">
         <v>1.02</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ55">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB55" t="s">
         <v>253</v>
@@ -14446,7 +14446,7 @@
         <v>2.84</v>
       </c>
       <c r="I56">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J56">
         <v>3.75</v>
@@ -14455,16 +14455,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P56">
         <v>2.2</v>
@@ -14473,190 +14473,190 @@
         <v>1.43</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ56">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB56" t="s">
         <v>253</v>
@@ -14679,226 +14679,226 @@
         <v>242</v>
       </c>
       <c r="F57">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G57">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H57">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I57">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J57">
         <v>3.75</v>
       </c>
       <c r="K57">
+        <v>4.1</v>
+      </c>
+      <c r="L57">
+        <v>1.32</v>
+      </c>
+      <c r="M57">
+        <v>1.05</v>
+      </c>
+      <c r="N57">
+        <v>4.3</v>
+      </c>
+      <c r="O57">
+        <v>1.26</v>
+      </c>
+      <c r="P57">
+        <v>2.18</v>
+      </c>
+      <c r="Q57">
+        <v>1.78</v>
+      </c>
+      <c r="R57">
+        <v>1.4</v>
+      </c>
+      <c r="S57">
+        <v>2.88</v>
+      </c>
+      <c r="T57">
+        <v>1.61</v>
+      </c>
+      <c r="U57">
+        <v>2.14</v>
+      </c>
+      <c r="V57">
+        <v>1.33</v>
+      </c>
+      <c r="W57">
+        <v>1.9</v>
+      </c>
+      <c r="X57">
+        <v>1000</v>
+      </c>
+      <c r="Y57">
+        <v>21</v>
+      </c>
+      <c r="Z57">
+        <v>38</v>
+      </c>
+      <c r="AA57">
+        <v>95</v>
+      </c>
+      <c r="AB57">
+        <v>13</v>
+      </c>
+      <c r="AC57">
+        <v>10</v>
+      </c>
+      <c r="AD57">
+        <v>21</v>
+      </c>
+      <c r="AE57">
+        <v>55</v>
+      </c>
+      <c r="AF57">
+        <v>17</v>
+      </c>
+      <c r="AG57">
+        <v>12.5</v>
+      </c>
+      <c r="AH57">
+        <v>21</v>
+      </c>
+      <c r="AI57">
+        <v>60</v>
+      </c>
+      <c r="AJ57">
+        <v>32</v>
+      </c>
+      <c r="AK57">
+        <v>27</v>
+      </c>
+      <c r="AL57">
+        <v>42</v>
+      </c>
+      <c r="AM57">
+        <v>100</v>
+      </c>
+      <c r="AN57">
+        <v>15</v>
+      </c>
+      <c r="AO57">
+        <v>50</v>
+      </c>
+      <c r="AP57">
+        <v>11</v>
+      </c>
+      <c r="AQ57">
+        <v>13</v>
+      </c>
+      <c r="AR57">
+        <v>19</v>
+      </c>
+      <c r="AS57">
+        <v>3.65</v>
+      </c>
+      <c r="AT57">
+        <v>9.4</v>
+      </c>
+      <c r="AU57">
+        <v>7.2</v>
+      </c>
+      <c r="AV57">
+        <v>13</v>
+      </c>
+      <c r="AW57">
+        <v>3.55</v>
+      </c>
+      <c r="AX57">
+        <v>11</v>
+      </c>
+      <c r="AY57">
+        <v>9</v>
+      </c>
+      <c r="AZ57">
+        <v>14</v>
+      </c>
+      <c r="BA57">
+        <v>3.55</v>
+      </c>
+      <c r="BB57">
+        <v>3.35</v>
+      </c>
+      <c r="BC57">
+        <v>15.5</v>
+      </c>
+      <c r="BD57">
+        <v>21</v>
+      </c>
+      <c r="BE57">
+        <v>3.65</v>
+      </c>
+      <c r="BF57">
+        <v>9.4</v>
+      </c>
+      <c r="BG57">
+        <v>24</v>
+      </c>
+      <c r="BH57">
+        <v>1000</v>
+      </c>
+      <c r="BI57">
+        <v>3.15</v>
+      </c>
+      <c r="BJ57">
+        <v>12</v>
+      </c>
+      <c r="BK57">
+        <v>6.8</v>
+      </c>
+      <c r="BL57">
+        <v>1000</v>
+      </c>
+      <c r="BM57">
+        <v>22</v>
+      </c>
+      <c r="BN57">
+        <v>5.7</v>
+      </c>
+      <c r="BO57">
         <v>4</v>
       </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>2.16</v>
-      </c>
-      <c r="Q57">
-        <v>1.77</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
-      <c r="U57">
-        <v>0</v>
-      </c>
-      <c r="V57">
-        <v>0</v>
-      </c>
-      <c r="W57">
-        <v>0</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
-      </c>
-      <c r="Y57">
-        <v>0</v>
-      </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-      <c r="AA57">
-        <v>0</v>
-      </c>
-      <c r="AB57">
-        <v>0</v>
-      </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <v>0</v>
-      </c>
-      <c r="AE57">
-        <v>0</v>
-      </c>
-      <c r="AF57">
-        <v>0</v>
-      </c>
-      <c r="AG57">
-        <v>0</v>
-      </c>
-      <c r="AH57">
-        <v>0</v>
-      </c>
-      <c r="AI57">
-        <v>0</v>
-      </c>
-      <c r="AJ57">
-        <v>0</v>
-      </c>
-      <c r="AK57">
-        <v>0</v>
-      </c>
-      <c r="AL57">
-        <v>0</v>
-      </c>
-      <c r="AM57">
-        <v>0</v>
-      </c>
-      <c r="AN57">
-        <v>0</v>
-      </c>
-      <c r="AO57">
-        <v>0</v>
-      </c>
-      <c r="AP57">
-        <v>0</v>
-      </c>
-      <c r="AQ57">
-        <v>0</v>
-      </c>
-      <c r="AR57">
-        <v>0</v>
-      </c>
-      <c r="AS57">
-        <v>0</v>
-      </c>
-      <c r="AT57">
-        <v>0</v>
-      </c>
-      <c r="AU57">
-        <v>0</v>
-      </c>
-      <c r="AV57">
-        <v>0</v>
-      </c>
-      <c r="AW57">
-        <v>0</v>
-      </c>
-      <c r="AX57">
-        <v>0</v>
-      </c>
-      <c r="AY57">
-        <v>0</v>
-      </c>
-      <c r="AZ57">
-        <v>0</v>
-      </c>
-      <c r="BA57">
-        <v>0</v>
-      </c>
-      <c r="BB57">
-        <v>0</v>
-      </c>
-      <c r="BC57">
-        <v>0</v>
-      </c>
-      <c r="BD57">
-        <v>0</v>
-      </c>
-      <c r="BE57">
-        <v>0</v>
-      </c>
-      <c r="BF57">
-        <v>0</v>
-      </c>
-      <c r="BG57">
-        <v>0</v>
-      </c>
-      <c r="BH57">
-        <v>0</v>
-      </c>
-      <c r="BI57">
-        <v>0</v>
-      </c>
-      <c r="BJ57">
-        <v>0</v>
-      </c>
-      <c r="BK57">
-        <v>0</v>
-      </c>
-      <c r="BL57">
-        <v>0</v>
-      </c>
-      <c r="BM57">
-        <v>0</v>
-      </c>
-      <c r="BN57">
-        <v>0</v>
-      </c>
-      <c r="BO57">
-        <v>0</v>
-      </c>
       <c r="BP57">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR57">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS57">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT57">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BU57">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV57">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW57">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BX57">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ57">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA57">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CB57" t="s">
         <v>253</v>
@@ -14921,16 +14921,16 @@
         <v>243</v>
       </c>
       <c r="F58">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="G58">
         <v>2.24</v>
       </c>
       <c r="H58">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I58">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="J58">
         <v>3.05</v>
@@ -14939,16 +14939,16 @@
         <v>3.45</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P58">
         <v>1.39</v>
@@ -14957,190 +14957,190 @@
         <v>2.16</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB58" t="s">
         <v>253</v>
@@ -15166,223 +15166,223 @@
         <v>1.74</v>
       </c>
       <c r="G59">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H59">
         <v>5.3</v>
       </c>
       <c r="I59">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J59">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K59">
         <v>3.95</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P59">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q59">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN59">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU59">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY59">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD59">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE59">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF59">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG59">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BH59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB59" t="s">
         <v>253</v>
@@ -15405,52 +15405,52 @@
         <v>245</v>
       </c>
       <c r="F60">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="G60">
-        <v>1.45</v>
+        <v>3.25</v>
       </c>
       <c r="H60">
-        <v>8</v>
+        <v>2.52</v>
       </c>
       <c r="I60">
-        <v>8.4</v>
+        <v>2.56</v>
       </c>
       <c r="J60">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="K60">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N60">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="O60">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="P60">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="Q60">
-        <v>1.51</v>
+        <v>2.14</v>
       </c>
       <c r="R60">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="S60">
-        <v>2.28</v>
+        <v>3.95</v>
       </c>
       <c r="T60">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U60">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -15459,161 +15459,161 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="Y60">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z60">
-        <v>75</v>
+        <v>16.5</v>
       </c>
       <c r="AA60">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="AB60">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC60">
+        <v>7.6</v>
+      </c>
+      <c r="AD60">
+        <v>12.5</v>
+      </c>
+      <c r="AE60">
+        <v>32</v>
+      </c>
+      <c r="AF60">
+        <v>22</v>
+      </c>
+      <c r="AG60">
+        <v>14.5</v>
+      </c>
+      <c r="AH60">
+        <v>19.5</v>
+      </c>
+      <c r="AI60">
+        <v>46</v>
+      </c>
+      <c r="AJ60">
+        <v>65</v>
+      </c>
+      <c r="AK60">
+        <v>42</v>
+      </c>
+      <c r="AL60">
+        <v>55</v>
+      </c>
+      <c r="AM60">
+        <v>120</v>
+      </c>
+      <c r="AN60">
+        <v>38</v>
+      </c>
+      <c r="AO60">
+        <v>26</v>
+      </c>
+      <c r="AP60">
+        <v>10.5</v>
+      </c>
+      <c r="AQ60">
+        <v>8.6</v>
+      </c>
+      <c r="AR60">
         <v>13.5</v>
       </c>
-      <c r="AD60">
+      <c r="AS60">
         <v>30</v>
-      </c>
-      <c r="AE60">
-        <v>110</v>
-      </c>
-      <c r="AF60">
-        <v>11</v>
-      </c>
-      <c r="AG60">
-        <v>10</v>
-      </c>
-      <c r="AH60">
-        <v>22</v>
-      </c>
-      <c r="AI60">
-        <v>80</v>
-      </c>
-      <c r="AJ60">
-        <v>13.5</v>
-      </c>
-      <c r="AK60">
-        <v>14.5</v>
-      </c>
-      <c r="AL60">
-        <v>27</v>
-      </c>
-      <c r="AM60">
-        <v>90</v>
-      </c>
-      <c r="AN60">
-        <v>5</v>
-      </c>
-      <c r="AO60">
-        <v>90</v>
-      </c>
-      <c r="AP60">
-        <v>9.6</v>
-      </c>
-      <c r="AQ60">
-        <v>27</v>
-      </c>
-      <c r="AR60">
-        <v>11</v>
-      </c>
-      <c r="AS60">
-        <v>12.5</v>
       </c>
       <c r="AT60">
         <v>10</v>
       </c>
       <c r="AU60">
+        <v>6.8</v>
+      </c>
+      <c r="AV60">
+        <v>10.5</v>
+      </c>
+      <c r="AW60">
+        <v>21</v>
+      </c>
+      <c r="AX60">
+        <v>18</v>
+      </c>
+      <c r="AY60">
+        <v>12</v>
+      </c>
+      <c r="AZ60">
+        <v>17</v>
+      </c>
+      <c r="BA60">
+        <v>9.4</v>
+      </c>
+      <c r="BB60">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC60">
+        <v>30</v>
+      </c>
+      <c r="BD60">
+        <v>9.6</v>
+      </c>
+      <c r="BE60">
+        <v>10.5</v>
+      </c>
+      <c r="BF60">
+        <v>9</v>
+      </c>
+      <c r="BG60">
+        <v>21</v>
+      </c>
+      <c r="BH60">
+        <v>3.55</v>
+      </c>
+      <c r="BI60">
+        <v>2.76</v>
+      </c>
+      <c r="BJ60">
+        <v>1000</v>
+      </c>
+      <c r="BK60">
+        <v>7</v>
+      </c>
+      <c r="BL60">
+        <v>1000</v>
+      </c>
+      <c r="BM60">
+        <v>1.01</v>
+      </c>
+      <c r="BN60">
+        <v>1000</v>
+      </c>
+      <c r="BO60">
+        <v>4.9</v>
+      </c>
+      <c r="BP60">
+        <v>1000</v>
+      </c>
+      <c r="BQ60">
+        <v>1.01</v>
+      </c>
+      <c r="BR60">
+        <v>1000</v>
+      </c>
+      <c r="BS60">
+        <v>1.01</v>
+      </c>
+      <c r="BT60">
+        <v>1000</v>
+      </c>
+      <c r="BU60">
+        <v>4.3</v>
+      </c>
+      <c r="BV60">
+        <v>1000</v>
+      </c>
+      <c r="BW60">
         <v>11.5</v>
       </c>
-      <c r="AV60">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW60">
-        <v>11.5</v>
-      </c>
-      <c r="AX60">
-        <v>9.6</v>
-      </c>
-      <c r="AY60">
-        <v>9</v>
-      </c>
-      <c r="AZ60">
-        <v>18.5</v>
-      </c>
-      <c r="BA60">
-        <v>11.5</v>
-      </c>
-      <c r="BB60">
-        <v>12</v>
-      </c>
-      <c r="BC60">
-        <v>12.5</v>
-      </c>
-      <c r="BD60">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE60">
-        <v>11.5</v>
-      </c>
-      <c r="BF60">
-        <v>4.5</v>
-      </c>
-      <c r="BG60">
-        <v>11.5</v>
-      </c>
-      <c r="BH60">
-        <v>1000</v>
-      </c>
-      <c r="BI60">
-        <v>3.75</v>
-      </c>
-      <c r="BJ60">
-        <v>1000</v>
-      </c>
-      <c r="BK60">
-        <v>7.2</v>
-      </c>
-      <c r="BL60">
-        <v>1000</v>
-      </c>
-      <c r="BM60">
-        <v>1.01</v>
-      </c>
-      <c r="BN60">
-        <v>1000</v>
-      </c>
-      <c r="BO60">
-        <v>3.4</v>
-      </c>
-      <c r="BP60">
-        <v>1000</v>
-      </c>
-      <c r="BQ60">
-        <v>6.2</v>
-      </c>
-      <c r="BR60">
-        <v>1000</v>
-      </c>
-      <c r="BS60">
-        <v>1.01</v>
-      </c>
-      <c r="BT60">
-        <v>1000</v>
-      </c>
-      <c r="BU60">
-        <v>7.8</v>
-      </c>
-      <c r="BV60">
-        <v>1000</v>
-      </c>
-      <c r="BW60">
-        <v>1.01</v>
-      </c>
       <c r="BX60">
         <v>1000</v>
       </c>
@@ -15621,10 +15621,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ60">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB60" t="s">
         <v>253</v>
@@ -15647,52 +15647,52 @@
         <v>246</v>
       </c>
       <c r="F61">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="G61">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="H61">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="I61">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="J61">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K61">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N61">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="O61">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="P61">
-        <v>1.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q61">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="R61">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="S61">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="T61">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="U61">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -15701,143 +15701,143 @@
         <v>0</v>
       </c>
       <c r="X61">
+        <v>32</v>
+      </c>
+      <c r="Y61">
+        <v>21</v>
+      </c>
+      <c r="Z61">
+        <v>25</v>
+      </c>
+      <c r="AA61">
+        <v>46</v>
+      </c>
+      <c r="AB61">
+        <v>21</v>
+      </c>
+      <c r="AC61">
+        <v>10</v>
+      </c>
+      <c r="AD61">
+        <v>14</v>
+      </c>
+      <c r="AE61">
+        <v>26</v>
+      </c>
+      <c r="AF61">
+        <v>24</v>
+      </c>
+      <c r="AG61">
+        <v>13</v>
+      </c>
+      <c r="AH61">
+        <v>14</v>
+      </c>
+      <c r="AI61">
+        <v>30</v>
+      </c>
+      <c r="AJ61">
+        <v>38</v>
+      </c>
+      <c r="AK61">
+        <v>23</v>
+      </c>
+      <c r="AL61">
+        <v>29</v>
+      </c>
+      <c r="AM61">
+        <v>55</v>
+      </c>
+      <c r="AN61">
         <v>12.5</v>
       </c>
-      <c r="Y61">
-        <v>9.6</v>
-      </c>
-      <c r="Z61">
-        <v>16.5</v>
-      </c>
-      <c r="AA61">
-        <v>40</v>
-      </c>
-      <c r="AB61">
+      <c r="AO61">
+        <v>14</v>
+      </c>
+      <c r="AP61">
+        <v>20</v>
+      </c>
+      <c r="AQ61">
+        <v>17.5</v>
+      </c>
+      <c r="AR61">
+        <v>19</v>
+      </c>
+      <c r="AS61">
+        <v>34</v>
+      </c>
+      <c r="AT61">
+        <v>15.5</v>
+      </c>
+      <c r="AU61">
+        <v>8.6</v>
+      </c>
+      <c r="AV61">
         <v>11.5</v>
       </c>
-      <c r="AC61">
-        <v>7.8</v>
-      </c>
-      <c r="AD61">
-        <v>12.5</v>
-      </c>
-      <c r="AE61">
-        <v>32</v>
-      </c>
-      <c r="AF61">
-        <v>23</v>
-      </c>
-      <c r="AG61">
-        <v>14.5</v>
-      </c>
-      <c r="AH61">
+      <c r="AW61">
+        <v>20</v>
+      </c>
+      <c r="AX61">
+        <v>18.5</v>
+      </c>
+      <c r="AY61">
+        <v>11</v>
+      </c>
+      <c r="AZ61">
+        <v>11.5</v>
+      </c>
+      <c r="BA61">
+        <v>7.6</v>
+      </c>
+      <c r="BB61">
+        <v>30</v>
+      </c>
+      <c r="BC61">
+        <v>18.5</v>
+      </c>
+      <c r="BD61">
         <v>19.5</v>
       </c>
-      <c r="AI61">
-        <v>55</v>
-      </c>
-      <c r="AJ61">
-        <v>65</v>
-      </c>
-      <c r="AK61">
-        <v>42</v>
-      </c>
-      <c r="AL61">
-        <v>55</v>
-      </c>
-      <c r="AM61">
-        <v>120</v>
-      </c>
-      <c r="AN61">
+      <c r="BE61">
         <v>38</v>
       </c>
-      <c r="AO61">
-        <v>26</v>
-      </c>
-      <c r="AP61">
+      <c r="BF61">
         <v>10.5</v>
       </c>
-      <c r="AQ61">
-        <v>8.4</v>
-      </c>
-      <c r="AR61">
-        <v>13.5</v>
-      </c>
-      <c r="AS61">
-        <v>30</v>
-      </c>
-      <c r="AT61">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU61">
-        <v>6.8</v>
-      </c>
-      <c r="AV61">
+      <c r="BG61">
+        <v>12</v>
+      </c>
+      <c r="BH61">
+        <v>1000</v>
+      </c>
+      <c r="BI61">
+        <v>3.6</v>
+      </c>
+      <c r="BJ61">
+        <v>1000</v>
+      </c>
+      <c r="BK61">
+        <v>5.9</v>
+      </c>
+      <c r="BL61">
+        <v>1000</v>
+      </c>
+      <c r="BM61">
+        <v>1.01</v>
+      </c>
+      <c r="BN61">
+        <v>1000</v>
+      </c>
+      <c r="BO61">
+        <v>4.8</v>
+      </c>
+      <c r="BP61">
+        <v>1000</v>
+      </c>
+      <c r="BQ61">
         <v>10.5</v>
       </c>
-      <c r="AW61">
-        <v>21</v>
-      </c>
-      <c r="AX61">
-        <v>18</v>
-      </c>
-      <c r="AY61">
-        <v>12.5</v>
-      </c>
-      <c r="AZ61">
-        <v>17</v>
-      </c>
-      <c r="BA61">
-        <v>9</v>
-      </c>
-      <c r="BB61">
-        <v>9.6</v>
-      </c>
-      <c r="BC61">
-        <v>30</v>
-      </c>
-      <c r="BD61">
-        <v>9.4</v>
-      </c>
-      <c r="BE61">
-        <v>10</v>
-      </c>
-      <c r="BF61">
-        <v>8.6</v>
-      </c>
-      <c r="BG61">
-        <v>21</v>
-      </c>
-      <c r="BH61">
-        <v>3.55</v>
-      </c>
-      <c r="BI61">
-        <v>2.76</v>
-      </c>
-      <c r="BJ61">
-        <v>1000</v>
-      </c>
-      <c r="BK61">
-        <v>7</v>
-      </c>
-      <c r="BL61">
-        <v>1000</v>
-      </c>
-      <c r="BM61">
-        <v>1.01</v>
-      </c>
-      <c r="BN61">
-        <v>1000</v>
-      </c>
-      <c r="BO61">
-        <v>4.9</v>
-      </c>
-      <c r="BP61">
-        <v>1000</v>
-      </c>
-      <c r="BQ61">
-        <v>1.01</v>
-      </c>
       <c r="BR61">
         <v>1000</v>
       </c>
@@ -15848,13 +15848,13 @@
         <v>1000</v>
       </c>
       <c r="BU61">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV61">
         <v>1000</v>
       </c>
       <c r="BW61">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX61">
         <v>1000</v>
@@ -15863,10 +15863,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ61">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA61">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB61" t="s">
         <v>253</v>
@@ -15889,22 +15889,22 @@
         <v>247</v>
       </c>
       <c r="F62">
-        <v>2.58</v>
+        <v>1.43</v>
       </c>
       <c r="G62">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="H62">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I62">
-        <v>2.82</v>
+        <v>8.4</v>
       </c>
       <c r="J62">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="K62">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -15913,28 +15913,28 @@
         <v>1.03</v>
       </c>
       <c r="N62">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O62">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P62">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q62">
         <v>1.51</v>
       </c>
       <c r="R62">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="S62">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T62">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="U62">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -15946,106 +15946,106 @@
         <v>32</v>
       </c>
       <c r="Y62">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Z62">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AA62">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="AB62">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AC62">
+        <v>13</v>
+      </c>
+      <c r="AD62">
+        <v>30</v>
+      </c>
+      <c r="AE62">
+        <v>110</v>
+      </c>
+      <c r="AF62">
+        <v>11</v>
+      </c>
+      <c r="AG62">
         <v>10</v>
       </c>
-      <c r="AD62">
-        <v>14</v>
-      </c>
-      <c r="AE62">
-        <v>26</v>
-      </c>
-      <c r="AF62">
-        <v>24</v>
-      </c>
-      <c r="AG62">
+      <c r="AH62">
+        <v>22</v>
+      </c>
+      <c r="AI62">
+        <v>80</v>
+      </c>
+      <c r="AJ62">
+        <v>13.5</v>
+      </c>
+      <c r="AK62">
+        <v>14.5</v>
+      </c>
+      <c r="AL62">
+        <v>27</v>
+      </c>
+      <c r="AM62">
+        <v>90</v>
+      </c>
+      <c r="AN62">
+        <v>5</v>
+      </c>
+      <c r="AO62">
+        <v>90</v>
+      </c>
+      <c r="AP62">
+        <v>23</v>
+      </c>
+      <c r="AQ62">
+        <v>27</v>
+      </c>
+      <c r="AR62">
+        <v>11.5</v>
+      </c>
+      <c r="AS62">
         <v>13</v>
       </c>
-      <c r="AH62">
-        <v>14</v>
-      </c>
-      <c r="AI62">
-        <v>30</v>
-      </c>
-      <c r="AJ62">
-        <v>38</v>
-      </c>
-      <c r="AK62">
+      <c r="AT62">
+        <v>10</v>
+      </c>
+      <c r="AU62">
+        <v>11.5</v>
+      </c>
+      <c r="AV62">
         <v>23</v>
       </c>
-      <c r="AL62">
-        <v>29</v>
-      </c>
-      <c r="AM62">
-        <v>60</v>
-      </c>
-      <c r="AN62">
+      <c r="AW62">
+        <v>12</v>
+      </c>
+      <c r="AX62">
+        <v>9.6</v>
+      </c>
+      <c r="AY62">
+        <v>9</v>
+      </c>
+      <c r="AZ62">
+        <v>18.5</v>
+      </c>
+      <c r="BA62">
+        <v>11.5</v>
+      </c>
+      <c r="BB62">
+        <v>12</v>
+      </c>
+      <c r="BC62">
         <v>12.5</v>
       </c>
-      <c r="AO62">
-        <v>14</v>
-      </c>
-      <c r="AP62">
-        <v>20</v>
-      </c>
-      <c r="AQ62">
-        <v>17.5</v>
-      </c>
-      <c r="AR62">
-        <v>19</v>
-      </c>
-      <c r="AS62">
-        <v>34</v>
-      </c>
-      <c r="AT62">
-        <v>15.5</v>
-      </c>
-      <c r="AU62">
-        <v>8.6</v>
-      </c>
-      <c r="AV62">
-        <v>11.5</v>
-      </c>
-      <c r="AW62">
-        <v>20</v>
-      </c>
-      <c r="AX62">
-        <v>18.5</v>
-      </c>
-      <c r="AY62">
-        <v>11</v>
-      </c>
-      <c r="AZ62">
-        <v>11.5</v>
-      </c>
-      <c r="BA62">
-        <v>7.6</v>
-      </c>
-      <c r="BB62">
-        <v>30</v>
-      </c>
-      <c r="BC62">
-        <v>18.5</v>
-      </c>
       <c r="BD62">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE62">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="BF62">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG62">
         <v>12</v>
@@ -16054,13 +16054,13 @@
         <v>1000</v>
       </c>
       <c r="BI62">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BJ62">
         <v>1000</v>
       </c>
       <c r="BK62">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BL62">
         <v>1000</v>
@@ -16072,13 +16072,13 @@
         <v>1000</v>
       </c>
       <c r="BO62">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="BP62">
         <v>1000</v>
       </c>
       <c r="BQ62">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR62">
         <v>1000</v>
@@ -16090,13 +16090,13 @@
         <v>1000</v>
       </c>
       <c r="BU62">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BV62">
         <v>1000</v>
       </c>
       <c r="BW62">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX62">
         <v>1000</v>
@@ -16618,7 +16618,7 @@
         <v>1.34</v>
       </c>
       <c r="G65">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H65">
         <v>8.6</v>
@@ -16857,22 +16857,22 @@
         <v>251</v>
       </c>
       <c r="F66">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G66">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H66">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J66">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K66">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -16890,7 +16890,7 @@
         <v>1.59</v>
       </c>
       <c r="Q66">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R66">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -787,7 +787,7 @@
     <t>HUSA Agadir</t>
   </si>
   <si>
-    <t>2026-09-25 18:06:44</t>
+    <t>2026-09-25 20:27:22</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1381,7 @@
         <v>190</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
         <v>2.36</v>
@@ -1402,7 +1402,7 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
         <v>5.8</v>
@@ -1423,7 +1423,7 @@
         <v>2.46</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U2">
         <v>2.72</v>
@@ -1432,7 +1432,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
         <v>25</v>
@@ -1489,7 +1489,7 @@
         <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1623,10 +1623,10 @@
         <v>191</v>
       </c>
       <c r="F3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1638,7 +1638,7 @@
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1674,16 +1674,16 @@
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y3">
         <v>34</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1695,19 +1695,19 @@
         <v>12.5</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF3">
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3">
         <v>1000</v>
@@ -1716,28 +1716,28 @@
         <v>14.5</v>
       </c>
       <c r="AK3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3">
         <v>5.3</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AQ3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AS3">
         <v>46</v>
@@ -1749,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="AV3">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AW3">
         <v>34</v>
@@ -1764,22 +1764,22 @@
         <v>18</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB3">
+        <v>13</v>
+      </c>
+      <c r="BC3">
         <v>12.5</v>
       </c>
-      <c r="BC3">
-        <v>12</v>
-      </c>
       <c r="BD3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE3">
         <v>34</v>
       </c>
       <c r="BF3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG3">
         <v>34</v>
@@ -1865,16 +1865,16 @@
         <v>192</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
         <v>3.8</v>
@@ -1892,7 +1892,7 @@
         <v>5.3</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
         <v>2.42</v>
@@ -1910,13 +1910,13 @@
         <v>1.58</v>
       </c>
       <c r="U4">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1928,7 +1928,7 @@
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB4">
         <v>14.5</v>
@@ -1937,7 +1937,7 @@
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
         <v>32</v>
@@ -1946,7 +1946,7 @@
         <v>18.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>15.5</v>
@@ -1982,19 +1982,19 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
         <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX4">
         <v>15.5</v>
@@ -2006,7 +2006,7 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB4">
         <v>21</v>
@@ -2015,7 +2015,7 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE4">
         <v>29</v>
@@ -2024,67 +2024,67 @@
         <v>12</v>
       </c>
       <c r="BG4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI4">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN4">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>257</v>
@@ -2110,10 +2110,10 @@
         <v>1.55</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6.8</v>
@@ -2125,46 +2125,46 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z5">
         <v>55</v>
@@ -2197,7 +2197,7 @@
         <v>70</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK5">
         <v>16</v>
@@ -2212,7 +2212,7 @@
         <v>6.6</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>20</v>
@@ -2221,13 +2221,13 @@
         <v>19</v>
       </c>
       <c r="AR5">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AS5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
         <v>9.800000000000001</v>
@@ -2239,7 +2239,7 @@
         <v>34</v>
       </c>
       <c r="AX5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -2251,7 +2251,7 @@
         <v>44</v>
       </c>
       <c r="BB5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC5">
         <v>14</v>
@@ -2260,10 +2260,10 @@
         <v>19</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG5">
         <v>48</v>
@@ -2349,7 +2349,7 @@
         <v>194</v>
       </c>
       <c r="F6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
         <v>2.6</v>
@@ -2400,7 +2400,7 @@
         <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X6">
         <v>23</v>
@@ -2418,7 +2418,7 @@
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6">
         <v>13.5</v>
@@ -2511,64 +2511,64 @@
         <v>15.5</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="s">
         <v>257</v>
@@ -2600,7 +2600,7 @@
         <v>3.25</v>
       </c>
       <c r="I7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
         <v>3.4</v>
@@ -2702,7 +2702,7 @@
         <v>1.34</v>
       </c>
       <c r="AQ7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7">
         <v>1.39</v>
@@ -2711,7 +2711,7 @@
         <v>1.39</v>
       </c>
       <c r="AT7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>5.9</v>
@@ -2726,7 +2726,7 @@
         <v>1.34</v>
       </c>
       <c r="AY7">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7">
         <v>9.6</v>
@@ -2792,7 +2792,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2842,7 +2842,7 @@
         <v>3.3</v>
       </c>
       <c r="I8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2914,7 +2914,7 @@
         <v>19</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH8">
         <v>21</v>
@@ -2950,7 +2950,7 @@
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT8">
         <v>9.6</v>
@@ -2962,7 +2962,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX8">
         <v>13</v>
@@ -2974,25 +2974,25 @@
         <v>15</v>
       </c>
       <c r="BA8">
+        <v>5.4</v>
+      </c>
+      <c r="BB8">
         <v>5.1</v>
-      </c>
-      <c r="BB8">
-        <v>4.9</v>
       </c>
       <c r="BC8">
         <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE8">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF8">
         <v>15</v>
       </c>
       <c r="BG8">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3075,16 +3075,16 @@
         <v>197</v>
       </c>
       <c r="F9">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G9">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H9">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I9">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J9">
         <v>3.9</v>
@@ -3105,7 +3105,7 @@
         <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q9">
         <v>1.62</v>
@@ -3123,10 +3123,10 @@
         <v>2.68</v>
       </c>
       <c r="V9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X9">
         <v>23</v>
@@ -3147,7 +3147,7 @@
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE9">
         <v>24</v>
@@ -3162,13 +3162,13 @@
         <v>14.5</v>
       </c>
       <c r="AI9">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ9">
         <v>42</v>
       </c>
       <c r="AK9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL9">
         <v>32</v>
@@ -3177,7 +3177,7 @@
         <v>60</v>
       </c>
       <c r="AN9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO9">
         <v>14.5</v>
@@ -3195,7 +3195,7 @@
         <v>34</v>
       </c>
       <c r="AT9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU9">
         <v>8.6</v>
@@ -3216,7 +3216,7 @@
         <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="BB9">
         <v>36</v>
@@ -3228,10 +3228,10 @@
         <v>28</v>
       </c>
       <c r="BE9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG9">
         <v>12.5</v>
@@ -3326,7 +3326,7 @@
         <v>2.1</v>
       </c>
       <c r="I10">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J10">
         <v>3.2</v>
@@ -3344,7 +3344,7 @@
         <v>3.6</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P10">
         <v>1.94</v>
@@ -3365,7 +3365,7 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W10">
         <v>1.31</v>
@@ -3562,13 +3562,13 @@
         <v>2.28</v>
       </c>
       <c r="G11">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H11">
         <v>3</v>
       </c>
       <c r="I11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3589,28 +3589,28 @@
         <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
         <v>1.59</v>
       </c>
       <c r="R11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S11">
         <v>2.48</v>
       </c>
       <c r="T11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U11">
         <v>2.68</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3816,7 +3816,7 @@
         <v>6.8</v>
       </c>
       <c r="K12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L12">
         <v>1.24</v>
@@ -3828,28 +3828,28 @@
         <v>7.2</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
         <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R12">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T12">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W12">
         <v>4.3</v>
@@ -3864,10 +3864,10 @@
         <v>1000</v>
       </c>
       <c r="AA12">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AB12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC12">
         <v>16.5</v>
@@ -3903,16 +3903,16 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ12">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AR12">
         <v>38</v>
@@ -3927,10 +3927,10 @@
         <v>14</v>
       </c>
       <c r="AV12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX12">
         <v>8.800000000000001</v>
@@ -3942,7 +3942,7 @@
         <v>19</v>
       </c>
       <c r="BA12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB12">
         <v>9.4</v>
@@ -3960,13 +3960,13 @@
         <v>3.55</v>
       </c>
       <c r="BG12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3984,7 +3984,7 @@
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP12">
         <v>1000</v>
@@ -4043,22 +4043,22 @@
         <v>201</v>
       </c>
       <c r="F13">
+        <v>2.06</v>
+      </c>
+      <c r="G13">
         <v>2.1</v>
       </c>
-      <c r="G13">
-        <v>2.12</v>
-      </c>
       <c r="H13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J13">
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
         <v>1.25</v>
@@ -4082,7 +4082,7 @@
         <v>1.81</v>
       </c>
       <c r="S13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T13">
         <v>1.45</v>
@@ -4094,7 +4094,7 @@
         <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X13">
         <v>32</v>
@@ -4148,7 +4148,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP13">
         <v>21</v>
@@ -4157,7 +4157,7 @@
         <v>21</v>
       </c>
       <c r="AR13">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AS13">
         <v>32</v>
@@ -4199,10 +4199,10 @@
         <v>29</v>
       </c>
       <c r="BF13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4285,16 +4285,16 @@
         <v>202</v>
       </c>
       <c r="F14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G14">
         <v>3.45</v>
       </c>
       <c r="H14">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J14">
         <v>3.85</v>
@@ -4318,25 +4318,25 @@
         <v>2.48</v>
       </c>
       <c r="Q14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R14">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S14">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T14">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U14">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V14">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X14">
         <v>27</v>
@@ -4384,10 +4384,10 @@
         <v>40</v>
       </c>
       <c r="AM14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14">
         <v>11.5</v>
@@ -4402,7 +4402,7 @@
         <v>14.5</v>
       </c>
       <c r="AS14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
         <v>15.5</v>
@@ -4441,7 +4441,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF14">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG14">
         <v>10</v>
@@ -4450,37 +4450,37 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.45</v>
+        <v>1.48</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>5.3</v>
+        <v>1.88</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>5.3</v>
+        <v>1.74</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BT14">
         <v>1000</v>
@@ -4492,19 +4492,19 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>8</v>
+        <v>2.14</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="CB14" t="s">
         <v>257</v>
@@ -4527,7 +4527,7 @@
         <v>203</v>
       </c>
       <c r="F15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G15">
         <v>1.65</v>
@@ -4557,13 +4557,13 @@
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q15">
         <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S15">
         <v>2.88</v>
@@ -4784,7 +4784,7 @@
         <v>3.65</v>
       </c>
       <c r="K16">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4820,7 +4820,7 @@
         <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5498,19 +5498,19 @@
         <v>2.48</v>
       </c>
       <c r="G19">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I19">
         <v>3.45</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L19">
         <v>1.52</v>
@@ -5519,7 +5519,7 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O19">
         <v>1.5</v>
@@ -5528,7 +5528,7 @@
         <v>1.58</v>
       </c>
       <c r="Q19">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R19">
         <v>1.21</v>
@@ -5537,16 +5537,16 @@
         <v>5.2</v>
       </c>
       <c r="T19">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V19">
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X19">
         <v>9.199999999999999</v>
@@ -5570,7 +5570,7 @@
         <v>16.5</v>
       </c>
       <c r="AE19">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF19">
         <v>14.5</v>
@@ -5624,10 +5624,10 @@
         <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY19">
         <v>11.5</v>
@@ -5642,19 +5642,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC19">
+        <v>9</v>
+      </c>
+      <c r="BD19">
+        <v>10</v>
+      </c>
+      <c r="BE19">
+        <v>11</v>
+      </c>
+      <c r="BF19">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE19">
-        <v>10.5</v>
-      </c>
-      <c r="BF19">
-        <v>8.6</v>
-      </c>
       <c r="BG19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5743,7 +5743,7 @@
         <v>4.5</v>
       </c>
       <c r="H20">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I20">
         <v>2.28</v>
@@ -5764,7 +5764,7 @@
         <v>2.3</v>
       </c>
       <c r="O20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
         <v>2.3</v>
@@ -6221,16 +6221,16 @@
         <v>210</v>
       </c>
       <c r="F22">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G22">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I22">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J22">
         <v>3.55</v>
@@ -6242,10 +6242,10 @@
         <v>1.35</v>
       </c>
       <c r="M22">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O22">
         <v>1.31</v>
@@ -6254,13 +6254,13 @@
         <v>2</v>
       </c>
       <c r="Q22">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R22">
         <v>1.38</v>
       </c>
       <c r="S22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T22">
         <v>1.72</v>
@@ -6269,13 +6269,13 @@
         <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y22">
         <v>12.5</v>
@@ -6299,10 +6299,10 @@
         <v>36</v>
       </c>
       <c r="AF22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH22">
         <v>17.5</v>
@@ -6323,7 +6323,7 @@
         <v>85</v>
       </c>
       <c r="AN22">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO22">
         <v>30</v>
@@ -6335,10 +6335,10 @@
         <v>12</v>
       </c>
       <c r="AR22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT22">
         <v>10</v>
@@ -6356,7 +6356,7 @@
         <v>15</v>
       </c>
       <c r="AY22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22">
         <v>15</v>
@@ -6371,13 +6371,13 @@
         <v>23</v>
       </c>
       <c r="BD22">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BE22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BG22">
         <v>24</v>
@@ -6729,13 +6729,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O24">
         <v>1.07</v>
       </c>
       <c r="P24">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q24">
         <v>1.3</v>
@@ -6753,7 +6753,7 @@
         <v>3.2</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
         <v>1.86</v>
@@ -6780,7 +6780,7 @@
         <v>25</v>
       </c>
       <c r="AE24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF24">
         <v>36</v>
@@ -6837,10 +6837,10 @@
         <v>16.5</v>
       </c>
       <c r="AX24">
-        <v>2.68</v>
+        <v>15.5</v>
       </c>
       <c r="AY24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
         <v>10</v>
@@ -6861,7 +6861,7 @@
         <v>2.76</v>
       </c>
       <c r="BF24">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG24">
         <v>9.199999999999999</v>
@@ -7918,7 +7918,7 @@
         <v>2.52</v>
       </c>
       <c r="G29">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H29">
         <v>3.25</v>
@@ -7930,7 +7930,7 @@
         <v>3.15</v>
       </c>
       <c r="K29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L29">
         <v>1.57</v>
@@ -7945,16 +7945,16 @@
         <v>1.52</v>
       </c>
       <c r="P29">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q29">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R29">
         <v>1.22</v>
       </c>
       <c r="S29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
         <v>2.06</v>
@@ -7966,7 +7966,7 @@
         <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X29">
         <v>9.199999999999999</v>
@@ -7978,7 +7978,7 @@
         <v>23</v>
       </c>
       <c r="AA29">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB29">
         <v>8.199999999999999</v>
@@ -8032,7 +8032,7 @@
         <v>18.5</v>
       </c>
       <c r="AS29">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29">
         <v>7</v>
@@ -8044,7 +8044,7 @@
         <v>13</v>
       </c>
       <c r="AW29">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX29">
         <v>13</v>
@@ -8068,10 +8068,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE29">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF29">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG29">
         <v>8.800000000000001</v>
@@ -8163,7 +8163,7 @@
         <v>1000</v>
       </c>
       <c r="H30">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I30">
         <v>110</v>
@@ -9609,7 +9609,7 @@
         <v>224</v>
       </c>
       <c r="F36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G36">
         <v>5.6</v>
@@ -9618,13 +9618,13 @@
         <v>1.9</v>
       </c>
       <c r="I36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J36">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K36">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9633,34 +9633,34 @@
         <v>1.09</v>
       </c>
       <c r="N36">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="O36">
         <v>1.41</v>
       </c>
       <c r="P36">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
       </c>
       <c r="R36">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S36">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T36">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U36">
         <v>1.79</v>
       </c>
       <c r="V36">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W36">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X36">
         <v>21</v>
@@ -10338,10 +10338,10 @@
         <v>1.64</v>
       </c>
       <c r="G39">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H39">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I39">
         <v>6.8</v>
@@ -10359,13 +10359,13 @@
         <v>1.08</v>
       </c>
       <c r="N39">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O39">
         <v>1.37</v>
       </c>
       <c r="P39">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="Q39">
         <v>2.04</v>
@@ -10377,16 +10377,16 @@
         <v>3.6</v>
       </c>
       <c r="T39">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="U39">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V39">
         <v>1.17</v>
       </c>
       <c r="W39">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X39">
         <v>30</v>
@@ -10506,13 +10506,13 @@
         <v>1000</v>
       </c>
       <c r="BK39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BN39">
         <v>1000</v>
@@ -10530,31 +10530,31 @@
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BT39">
         <v>1000</v>
       </c>
       <c r="BU39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BV39">
         <v>1000</v>
       </c>
       <c r="BW39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="s">
         <v>257</v>
@@ -11551,7 +11551,7 @@
         <v>2.2</v>
       </c>
       <c r="H44">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I44">
         <v>4.1</v>
@@ -11569,7 +11569,7 @@
         <v>1.07</v>
       </c>
       <c r="N44">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O44">
         <v>1.32</v>
@@ -11578,40 +11578,40 @@
         <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="R44">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S44">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T44">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U44">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W44">
         <v>1.83</v>
       </c>
       <c r="X44">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y44">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z44">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA44">
         <v>85</v>
       </c>
       <c r="AB44">
-        <v>32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC44">
         <v>7.8</v>
@@ -11632,28 +11632,28 @@
         <v>17.5</v>
       </c>
       <c r="AI44">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ44">
         <v>27</v>
       </c>
       <c r="AK44">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL44">
         <v>38</v>
       </c>
       <c r="AM44">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN44">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO44">
         <v>60</v>
       </c>
       <c r="AP44">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ44">
         <v>13</v>
@@ -11662,10 +11662,10 @@
         <v>21</v>
       </c>
       <c r="AS44">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AT44">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU44">
         <v>7.2</v>
@@ -11674,7 +11674,7 @@
         <v>14</v>
       </c>
       <c r="AW44">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="AX44">
         <v>12</v>
@@ -11683,28 +11683,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ44">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA44">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BB44">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BC44">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD44">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BE44">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BF44">
         <v>14</v>
       </c>
       <c r="BG44">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -12755,19 +12755,19 @@
         <v>237</v>
       </c>
       <c r="F49">
+        <v>3.85</v>
+      </c>
+      <c r="G49">
         <v>3.95</v>
       </c>
-      <c r="G49">
-        <v>4.1</v>
-      </c>
       <c r="H49">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I49">
         <v>2.52</v>
       </c>
       <c r="J49">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K49">
         <v>2.92</v>
@@ -12782,7 +12782,7 @@
         <v>2.06</v>
       </c>
       <c r="O49">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="P49">
         <v>1.38</v>
@@ -12791,7 +12791,7 @@
         <v>3.5</v>
       </c>
       <c r="R49">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="S49">
         <v>8.4</v>
@@ -12800,13 +12800,13 @@
         <v>2.66</v>
       </c>
       <c r="U49">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V49">
         <v>1.66</v>
       </c>
       <c r="W49">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X49">
         <v>6.4</v>
@@ -12854,7 +12854,7 @@
         <v>160</v>
       </c>
       <c r="AM49">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AN49">
         <v>160</v>
@@ -12872,7 +12872,7 @@
         <v>12</v>
       </c>
       <c r="AS49">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="AT49">
         <v>7.6</v>
@@ -12890,7 +12890,7 @@
         <v>22</v>
       </c>
       <c r="AY49">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AZ49">
         <v>29</v>
@@ -12902,7 +12902,7 @@
         <v>12.5</v>
       </c>
       <c r="BC49">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD49">
         <v>11</v>
@@ -12914,7 +12914,7 @@
         <v>11.5</v>
       </c>
       <c r="BG49">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -12956,7 +12956,7 @@
         <v>1000</v>
       </c>
       <c r="BU49">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BV49">
         <v>1000</v>
@@ -13036,16 +13036,16 @@
         <v>1.41</v>
       </c>
       <c r="S50">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T50">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U50">
         <v>1.96</v>
       </c>
       <c r="V50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W50">
         <v>2.56</v>
@@ -13057,7 +13057,7 @@
         <v>21</v>
       </c>
       <c r="Z50">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA50">
         <v>190</v>
@@ -13069,10 +13069,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD50">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE50">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF50">
         <v>9.6</v>
@@ -13099,7 +13099,7 @@
         <v>130</v>
       </c>
       <c r="AN50">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO50">
         <v>110</v>
@@ -13126,19 +13126,19 @@
         <v>21</v>
       </c>
       <c r="AW50">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX50">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY50">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ50">
         <v>19.5</v>
       </c>
       <c r="BA50">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BB50">
         <v>13</v>
@@ -13156,7 +13156,7 @@
         <v>8</v>
       </c>
       <c r="BG50">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -13239,25 +13239,25 @@
         <v>239</v>
       </c>
       <c r="F51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G51">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H51">
         <v>1.46</v>
       </c>
       <c r="I51">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J51">
         <v>5</v>
       </c>
       <c r="K51">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L51">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M51">
         <v>1.04</v>
@@ -13272,22 +13272,22 @@
         <v>2.44</v>
       </c>
       <c r="Q51">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R51">
         <v>1.56</v>
       </c>
       <c r="S51">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T51">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U51">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V51">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="W51">
         <v>1.13</v>
@@ -13320,7 +13320,7 @@
         <v>70</v>
       </c>
       <c r="AG51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH51">
         <v>23</v>
@@ -13329,7 +13329,7 @@
         <v>34</v>
       </c>
       <c r="AJ51">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AK51">
         <v>110</v>
@@ -13344,7 +13344,7 @@
         <v>120</v>
       </c>
       <c r="AO51">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP51">
         <v>19</v>
@@ -13383,34 +13383,34 @@
         <v>27</v>
       </c>
       <c r="BB51">
+        <v>18</v>
+      </c>
+      <c r="BC51">
+        <v>17</v>
+      </c>
+      <c r="BD51">
+        <v>17</v>
+      </c>
+      <c r="BE51">
         <v>16.5</v>
       </c>
-      <c r="BC51">
-        <v>15.5</v>
-      </c>
-      <c r="BD51">
-        <v>16</v>
-      </c>
-      <c r="BE51">
-        <v>15.5</v>
-      </c>
       <c r="BF51">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG51">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH51">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI51">
         <v>3.7</v>
       </c>
       <c r="BJ51">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK51">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL51">
         <v>130</v>
@@ -13437,10 +13437,10 @@
         <v>21</v>
       </c>
       <c r="BT51">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BU51">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV51">
         <v>9</v>
@@ -13458,7 +13458,7 @@
         <v>14</v>
       </c>
       <c r="CA51">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB51" t="s">
         <v>257</v>
@@ -13490,16 +13490,16 @@
         <v>7.8</v>
       </c>
       <c r="I52">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J52">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K52">
         <v>4.9</v>
       </c>
       <c r="L52">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M52">
         <v>1.06</v>
@@ -13535,10 +13535,10 @@
         <v>2.96</v>
       </c>
       <c r="X52">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z52">
         <v>70</v>
@@ -13586,7 +13586,7 @@
         <v>7.8</v>
       </c>
       <c r="AO52">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP52">
         <v>15.5</v>
@@ -13598,7 +13598,7 @@
         <v>60</v>
       </c>
       <c r="AS52">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT52">
         <v>7.4</v>
@@ -13607,10 +13607,10 @@
         <v>9.6</v>
       </c>
       <c r="AV52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW52">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX52">
         <v>7.8</v>
@@ -13622,7 +13622,7 @@
         <v>22</v>
       </c>
       <c r="BA52">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB52">
         <v>12</v>
@@ -13634,13 +13634,13 @@
         <v>32</v>
       </c>
       <c r="BE52">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF52">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG52">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13729,7 +13729,7 @@
         <v>2.04</v>
       </c>
       <c r="H53">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I53">
         <v>4.7</v>
@@ -13747,10 +13747,10 @@
         <v>1.09</v>
       </c>
       <c r="N53">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O53">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P53">
         <v>1.78</v>
@@ -13765,10 +13765,10 @@
         <v>4.1</v>
       </c>
       <c r="T53">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U53">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V53">
         <v>1.27</v>
@@ -13777,7 +13777,7 @@
         <v>1.96</v>
       </c>
       <c r="X53">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y53">
         <v>14.5</v>
@@ -13789,7 +13789,7 @@
         <v>110</v>
       </c>
       <c r="AB53">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC53">
         <v>7.8</v>
@@ -13831,16 +13831,16 @@
         <v>80</v>
       </c>
       <c r="AP53">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ53">
         <v>13</v>
       </c>
       <c r="AR53">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AS53">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT53">
         <v>7.4</v>
@@ -13861,7 +13861,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ53">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA53">
         <v>60</v>
@@ -13876,13 +13876,13 @@
         <v>11</v>
       </c>
       <c r="BE53">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF53">
         <v>15</v>
       </c>
       <c r="BG53">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13977,25 +13977,25 @@
         <v>4.4</v>
       </c>
       <c r="J54">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K54">
         <v>3.65</v>
       </c>
       <c r="L54">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M54">
         <v>1.07</v>
       </c>
       <c r="N54">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O54">
         <v>1.34</v>
       </c>
       <c r="P54">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q54">
         <v>2</v>
@@ -14028,7 +14028,7 @@
         <v>36</v>
       </c>
       <c r="AA54">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB54">
         <v>9.6</v>
@@ -14049,13 +14049,13 @@
         <v>11</v>
       </c>
       <c r="AH54">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI54">
         <v>65</v>
       </c>
       <c r="AJ54">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK54">
         <v>24</v>
@@ -14064,13 +14064,13 @@
         <v>44</v>
       </c>
       <c r="AM54">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN54">
         <v>14.5</v>
       </c>
       <c r="AO54">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP54">
         <v>12</v>
@@ -14103,7 +14103,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ54">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA54">
         <v>10</v>
@@ -14112,7 +14112,7 @@
         <v>8.4</v>
       </c>
       <c r="BC54">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BD54">
         <v>9</v>
@@ -14799,52 +14799,52 @@
         <v>1000</v>
       </c>
       <c r="AP57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF57">
         <v>1.01</v>
@@ -14933,31 +14933,31 @@
         <v>246</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G58">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H58">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I58">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K58">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M58">
         <v>1.05</v>
       </c>
       <c r="N58">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O58">
         <v>1.26</v>
@@ -14981,118 +14981,118 @@
         <v>2.3</v>
       </c>
       <c r="V58">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W58">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X58">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y58">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z58">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA58">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB58">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC58">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD58">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AE58">
         <v>55</v>
       </c>
       <c r="AF58">
+        <v>14.5</v>
+      </c>
+      <c r="AG58">
+        <v>11</v>
+      </c>
+      <c r="AH58">
         <v>17</v>
-      </c>
-      <c r="AG58">
-        <v>12.5</v>
-      </c>
-      <c r="AH58">
-        <v>21</v>
       </c>
       <c r="AI58">
         <v>60</v>
       </c>
       <c r="AJ58">
+        <v>25</v>
+      </c>
+      <c r="AK58">
+        <v>21</v>
+      </c>
+      <c r="AL58">
+        <v>36</v>
+      </c>
+      <c r="AM58">
+        <v>90</v>
+      </c>
+      <c r="AN58">
+        <v>12.5</v>
+      </c>
+      <c r="AO58">
+        <v>44</v>
+      </c>
+      <c r="AP58">
+        <v>16</v>
+      </c>
+      <c r="AQ58">
+        <v>14.5</v>
+      </c>
+      <c r="AR58">
+        <v>25</v>
+      </c>
+      <c r="AS58">
+        <v>10</v>
+      </c>
+      <c r="AT58">
+        <v>10</v>
+      </c>
+      <c r="AU58">
+        <v>8</v>
+      </c>
+      <c r="AV58">
+        <v>14</v>
+      </c>
+      <c r="AW58">
+        <v>36</v>
+      </c>
+      <c r="AX58">
+        <v>12</v>
+      </c>
+      <c r="AY58">
+        <v>9.4</v>
+      </c>
+      <c r="AZ58">
+        <v>14.5</v>
+      </c>
+      <c r="BA58">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB58">
+        <v>7.8</v>
+      </c>
+      <c r="BC58">
+        <v>17.5</v>
+      </c>
+      <c r="BD58">
+        <v>8.4</v>
+      </c>
+      <c r="BE58">
+        <v>10</v>
+      </c>
+      <c r="BF58">
+        <v>10.5</v>
+      </c>
+      <c r="BG58">
         <v>32</v>
-      </c>
-      <c r="AK58">
-        <v>27</v>
-      </c>
-      <c r="AL58">
-        <v>42</v>
-      </c>
-      <c r="AM58">
-        <v>100</v>
-      </c>
-      <c r="AN58">
-        <v>15</v>
-      </c>
-      <c r="AO58">
-        <v>1000</v>
-      </c>
-      <c r="AP58">
-        <v>11</v>
-      </c>
-      <c r="AQ58">
-        <v>13</v>
-      </c>
-      <c r="AR58">
-        <v>19</v>
-      </c>
-      <c r="AS58">
-        <v>3.4</v>
-      </c>
-      <c r="AT58">
-        <v>8.6</v>
-      </c>
-      <c r="AU58">
-        <v>7.2</v>
-      </c>
-      <c r="AV58">
-        <v>12.5</v>
-      </c>
-      <c r="AW58">
-        <v>3.3</v>
-      </c>
-      <c r="AX58">
-        <v>9</v>
-      </c>
-      <c r="AY58">
-        <v>8.4</v>
-      </c>
-      <c r="AZ58">
-        <v>13</v>
-      </c>
-      <c r="BA58">
-        <v>3.3</v>
-      </c>
-      <c r="BB58">
-        <v>3.15</v>
-      </c>
-      <c r="BC58">
-        <v>15.5</v>
-      </c>
-      <c r="BD58">
-        <v>3.2</v>
-      </c>
-      <c r="BE58">
-        <v>3.4</v>
-      </c>
-      <c r="BF58">
-        <v>9.4</v>
-      </c>
-      <c r="BG58">
-        <v>24</v>
       </c>
       <c r="BH58">
         <v>1000</v>
@@ -15122,7 +15122,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ58">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR58">
         <v>32</v>
@@ -15140,7 +15140,7 @@
         <v>38</v>
       </c>
       <c r="BW58">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX58">
         <v>48</v>
@@ -15283,52 +15283,52 @@
         <v>1000</v>
       </c>
       <c r="AP59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF59">
         <v>1.01</v>
@@ -15420,61 +15420,61 @@
         <v>1.73</v>
       </c>
       <c r="G60">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H60">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I60">
         <v>6.6</v>
       </c>
       <c r="J60">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K60">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L60">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M60">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N60">
-        <v>1.67</v>
+        <v>2.84</v>
       </c>
       <c r="O60">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P60">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q60">
         <v>2.24</v>
       </c>
       <c r="R60">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S60">
-        <v>2.24</v>
+        <v>3.9</v>
       </c>
       <c r="T60">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U60">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V60">
         <v>1.18</v>
       </c>
       <c r="W60">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X60">
         <v>1000</v>
       </c>
       <c r="Y60">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z60">
         <v>1000</v>
@@ -15486,19 +15486,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC60">
+        <v>12.5</v>
+      </c>
+      <c r="AD60">
+        <v>1000</v>
+      </c>
+      <c r="AE60">
+        <v>1000</v>
+      </c>
+      <c r="AF60">
         <v>10.5</v>
       </c>
-      <c r="AD60">
-        <v>1000</v>
-      </c>
-      <c r="AE60">
-        <v>1000</v>
-      </c>
-      <c r="AF60">
-        <v>1000</v>
-      </c>
       <c r="AG60">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH60">
         <v>1000</v>
@@ -15519,64 +15519,64 @@
         <v>1000</v>
       </c>
       <c r="AN60">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO60">
         <v>1000</v>
       </c>
       <c r="AP60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AQ60">
-        <v>11</v>
+        <v>1.74</v>
       </c>
       <c r="AR60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AS60">
-        <v>95</v>
+        <v>1.74</v>
       </c>
       <c r="AT60">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AU60">
-        <v>5.9</v>
+        <v>1.53</v>
       </c>
       <c r="AV60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AW60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AX60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY60">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ60">
         <v>16</v>
       </c>
       <c r="BA60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BB60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BC60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BD60">
-        <v>32</v>
+        <v>1.74</v>
       </c>
       <c r="BE60">
-        <v>95</v>
+        <v>1.74</v>
       </c>
       <c r="BF60">
-        <v>11</v>
+        <v>1.6</v>
       </c>
       <c r="BG60">
-        <v>95</v>
+        <v>1.74</v>
       </c>
       <c r="BH60">
         <v>1000</v>
@@ -15665,7 +15665,7 @@
         <v>3.25</v>
       </c>
       <c r="H61">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I61">
         <v>2.54</v>
@@ -15677,7 +15677,7 @@
         <v>3.45</v>
       </c>
       <c r="L61">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M61">
         <v>1.08</v>
@@ -15692,7 +15692,7 @@
         <v>1.82</v>
       </c>
       <c r="Q61">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R61">
         <v>1.32</v>
@@ -15761,16 +15761,16 @@
         <v>110</v>
       </c>
       <c r="AN61">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO61">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP61">
         <v>11</v>
       </c>
       <c r="AQ61">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR61">
         <v>14</v>
@@ -15791,7 +15791,7 @@
         <v>26</v>
       </c>
       <c r="AX61">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY61">
         <v>12.5</v>
@@ -15803,7 +15803,7 @@
         <v>40</v>
       </c>
       <c r="BB61">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BC61">
         <v>34</v>
@@ -15815,7 +15815,7 @@
         <v>13.5</v>
       </c>
       <c r="BF61">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG61">
         <v>21</v>
@@ -15901,10 +15901,10 @@
         <v>250</v>
       </c>
       <c r="F62">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G62">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H62">
         <v>2.78</v>
@@ -15919,10 +15919,10 @@
         <v>3.95</v>
       </c>
       <c r="L62">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M62">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N62">
         <v>6.4</v>
@@ -15931,13 +15931,13 @@
         <v>1.17</v>
       </c>
       <c r="P62">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q62">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R62">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S62">
         <v>2.28</v>
@@ -15949,7 +15949,7 @@
         <v>2.96</v>
       </c>
       <c r="V62">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W62">
         <v>1.62</v>
@@ -15961,13 +15961,13 @@
         <v>20</v>
       </c>
       <c r="Z62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA62">
         <v>44</v>
       </c>
       <c r="AB62">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC62">
         <v>9.800000000000001</v>
@@ -16021,7 +16021,7 @@
         <v>36</v>
       </c>
       <c r="AT62">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU62">
         <v>8.800000000000001</v>
@@ -16146,7 +16146,7 @@
         <v>1.44</v>
       </c>
       <c r="G63">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H63">
         <v>8</v>
@@ -16155,10 +16155,10 @@
         <v>8.4</v>
       </c>
       <c r="J63">
+        <v>5.2</v>
+      </c>
+      <c r="K63">
         <v>5.4</v>
-      </c>
-      <c r="K63">
-        <v>5.5</v>
       </c>
       <c r="L63">
         <v>1.26</v>
@@ -16173,7 +16173,7 @@
         <v>1.17</v>
       </c>
       <c r="P63">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="Q63">
         <v>1.52</v>
@@ -16194,7 +16194,7 @@
         <v>1.13</v>
       </c>
       <c r="W63">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X63">
         <v>30</v>
@@ -16206,7 +16206,7 @@
         <v>75</v>
       </c>
       <c r="AA63">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB63">
         <v>12</v>
@@ -16218,7 +16218,7 @@
         <v>30</v>
       </c>
       <c r="AE63">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF63">
         <v>11</v>
@@ -16230,7 +16230,7 @@
         <v>22</v>
       </c>
       <c r="AI63">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ63">
         <v>14</v>
@@ -16239,7 +16239,7 @@
         <v>14</v>
       </c>
       <c r="AL63">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM63">
         <v>90</v>
@@ -16251,7 +16251,7 @@
         <v>85</v>
       </c>
       <c r="AP63">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AQ63">
         <v>32</v>
@@ -16260,7 +16260,7 @@
         <v>60</v>
       </c>
       <c r="AS63">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT63">
         <v>11</v>
@@ -16272,19 +16272,19 @@
         <v>26</v>
       </c>
       <c r="AW63">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX63">
         <v>9.800000000000001</v>
       </c>
       <c r="AY63">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ63">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA63">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB63">
         <v>12</v>
@@ -16296,13 +16296,13 @@
         <v>23</v>
       </c>
       <c r="BE63">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF63">
         <v>4.7</v>
       </c>
       <c r="BG63">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BH63">
         <v>1000</v>
@@ -16394,10 +16394,10 @@
         <v>2.72</v>
       </c>
       <c r="I64">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J64">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="K64">
         <v>6</v>
@@ -16409,10 +16409,10 @@
         <v>1.01</v>
       </c>
       <c r="N64">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="O64">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P64">
         <v>1.5</v>
@@ -16493,52 +16493,52 @@
         <v>1000</v>
       </c>
       <c r="AP64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF64">
         <v>1.01</v>
@@ -16636,13 +16636,13 @@
         <v>4.4</v>
       </c>
       <c r="I65">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J65">
         <v>3.35</v>
       </c>
       <c r="K65">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L65">
         <v>1.47</v>
@@ -16654,7 +16654,7 @@
         <v>3.2</v>
       </c>
       <c r="O65">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P65">
         <v>1.74</v>
@@ -16669,13 +16669,13 @@
         <v>4</v>
       </c>
       <c r="T65">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U65">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V65">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W65">
         <v>1.93</v>
@@ -16714,7 +16714,7 @@
         <v>24</v>
       </c>
       <c r="AI65">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ65">
         <v>29</v>
@@ -16741,7 +16741,7 @@
         <v>12</v>
       </c>
       <c r="AR65">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS65">
         <v>8.800000000000001</v>
@@ -16750,13 +16750,13 @@
         <v>6.8</v>
       </c>
       <c r="AU65">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV65">
         <v>16</v>
       </c>
       <c r="AW65">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX65">
         <v>10</v>
@@ -16774,7 +16774,7 @@
         <v>20</v>
       </c>
       <c r="BC65">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD65">
         <v>8.199999999999999</v>
@@ -16783,10 +16783,10 @@
         <v>9</v>
       </c>
       <c r="BF65">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BG65">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16884,13 +16884,13 @@
         <v>4.4</v>
       </c>
       <c r="K66">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="L66">
         <v>1.01</v>
       </c>
       <c r="M66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N66">
         <v>3.3</v>
@@ -16902,7 +16902,7 @@
         <v>1.87</v>
       </c>
       <c r="Q66">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R66">
         <v>1.3</v>
@@ -16917,7 +16917,7 @@
         <v>1.01</v>
       </c>
       <c r="V66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W66">
         <v>3.05</v>
@@ -16977,58 +16977,58 @@
         <v>1000</v>
       </c>
       <c r="AP66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ66">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AR66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS66">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="AT66">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU66">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW66">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="AX66">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY66">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA66">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="BB66">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD66">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE66">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="BF66">
         <v>1.01</v>
       </c>
       <c r="BG66">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -17111,19 +17111,19 @@
         <v>255</v>
       </c>
       <c r="F67">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G67">
         <v>2.28</v>
       </c>
       <c r="H67">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I67">
         <v>4.5</v>
       </c>
       <c r="J67">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K67">
         <v>3.35</v>
@@ -17132,7 +17132,7 @@
         <v>1.51</v>
       </c>
       <c r="M67">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N67">
         <v>2.78</v>
@@ -17153,10 +17153,10 @@
         <v>4.8</v>
       </c>
       <c r="T67">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U67">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V67">
         <v>1.29</v>
@@ -17297,7 +17297,7 @@
         <v>3.55</v>
       </c>
       <c r="BP67">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ67">
         <v>12.5</v>
@@ -17312,7 +17312,7 @@
         <v>9</v>
       </c>
       <c r="BU67">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV67">
         <v>1000</v>
@@ -17389,7 +17389,7 @@
         <v>2.56</v>
       </c>
       <c r="R68">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S68">
         <v>3.2</v>
@@ -17461,52 +17461,52 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF68">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -787,7 +787,7 @@
     <t>HUSA Agadir</t>
   </si>
   <si>
-    <t>2026-09-25 20:27:22</t>
+    <t>2026-09-25 22:46:49</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1381,7 @@
         <v>190</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
         <v>2.36</v>
@@ -1396,13 +1396,13 @@
         <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>5.8</v>
@@ -1417,13 +1417,13 @@
         <v>1.59</v>
       </c>
       <c r="R2">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S2">
         <v>2.46</v>
       </c>
       <c r="T2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U2">
         <v>2.72</v>
@@ -1462,13 +1462,13 @@
         <v>18.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>15</v>
       </c>
       <c r="AI2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ2">
         <v>32</v>
@@ -1489,7 +1489,7 @@
         <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1510,7 +1510,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AX2">
         <v>16</v>
@@ -1531,7 +1531,7 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BE2">
         <v>28</v>
@@ -1540,7 +1540,7 @@
         <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1638,7 +1638,7 @@
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1647,25 +1647,25 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U3">
         <v>2.3</v>
@@ -1689,10 +1689,10 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD3">
         <v>27</v>
@@ -1704,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
         <v>21</v>
@@ -1719,7 +1719,7 @@
         <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM3">
         <v>85</v>
@@ -1731,7 +1731,7 @@
         <v>70</v>
       </c>
       <c r="AP3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ3">
         <v>27</v>
@@ -1779,7 +1779,7 @@
         <v>34</v>
       </c>
       <c r="BF3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG3">
         <v>34</v>
@@ -1874,7 +1874,7 @@
         <v>3.05</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J4">
         <v>3.8</v>
@@ -1928,7 +1928,7 @@
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB4">
         <v>14.5</v>
@@ -1952,19 +1952,19 @@
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ4">
         <v>36</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>30</v>
       </c>
       <c r="AM4">
-        <v>65</v>
+        <v>530</v>
       </c>
       <c r="AN4">
         <v>13</v>
@@ -1982,7 +1982,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT4">
         <v>12.5</v>
@@ -1994,13 +1994,13 @@
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AX4">
         <v>15.5</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>13</v>
@@ -2009,10 +2009,10 @@
         <v>22</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD4">
         <v>19</v>
@@ -2024,7 +2024,7 @@
         <v>12</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH4">
         <v>4.1</v>
@@ -2060,7 +2060,7 @@
         <v>27</v>
       </c>
       <c r="BS4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
@@ -2069,22 +2069,22 @@
         <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BX4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BZ4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CB4" t="s">
         <v>257</v>
@@ -2107,13 +2107,13 @@
         <v>193</v>
       </c>
       <c r="F5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
         <v>1.58</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>6.8</v>
@@ -2149,16 +2149,16 @@
         <v>2.62</v>
       </c>
       <c r="T5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X5">
         <v>25</v>
@@ -2173,7 +2173,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>11</v>
@@ -2206,13 +2206,13 @@
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN5">
         <v>6.6</v>
       </c>
       <c r="AO5">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP5">
         <v>20</v>
@@ -2221,7 +2221,7 @@
         <v>19</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AS5">
         <v>44</v>
@@ -2272,19 +2272,19 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BN5">
         <v>5.4</v>
@@ -2302,7 +2302,7 @@
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BT5">
         <v>1000</v>
@@ -2314,19 +2314,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CB5" t="s">
         <v>257</v>
@@ -2352,10 +2352,10 @@
         <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
         <v>2.94</v>
@@ -2373,7 +2373,7 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -2391,16 +2391,16 @@
         <v>2.6</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U6">
         <v>2.66</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X6">
         <v>23</v>
@@ -2412,13 +2412,13 @@
         <v>23</v>
       </c>
       <c r="AA6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB6">
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6">
         <v>13.5</v>
@@ -2430,7 +2430,7 @@
         <v>20</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
         <v>15</v>
@@ -2478,7 +2478,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX6">
         <v>17</v>
@@ -2502,10 +2502,10 @@
         <v>19.5</v>
       </c>
       <c r="BE6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
@@ -2523,13 +2523,13 @@
         <v>7.4</v>
       </c>
       <c r="BL6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BM6">
         <v>21</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
         <v>5.3</v>
@@ -2544,19 +2544,19 @@
         <v>29</v>
       </c>
       <c r="BS6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BT6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
         <v>23</v>
       </c>
       <c r="BW6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BX6">
         <v>32</v>
@@ -2565,7 +2565,7 @@
         <v>20</v>
       </c>
       <c r="BZ6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="CA6">
         <v>13</v>
@@ -2591,31 +2591,31 @@
         <v>195</v>
       </c>
       <c r="F7">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="G7">
         <v>2.34</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
         <v>1.32</v>
@@ -2627,22 +2627,22 @@
         <v>1.93</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
         <v>3.3</v>
       </c>
       <c r="T7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X7">
         <v>38</v>
@@ -2651,7 +2651,7 @@
         <v>40</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2660,7 +2660,7 @@
         <v>970</v>
       </c>
       <c r="AC7">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7">
         <v>65</v>
@@ -2672,10 +2672,10 @@
         <v>38</v>
       </c>
       <c r="AG7">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI7">
         <v>1000</v>
@@ -2699,58 +2699,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR7">
-        <v>1.39</v>
+        <v>15</v>
       </c>
       <c r="AS7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU7">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>8.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AX7">
-        <v>1.34</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7">
         <v>9.6</v>
       </c>
       <c r="BA7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="BB7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="BC7">
-        <v>1.39</v>
+        <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="BE7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="BF7">
         <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2842,7 +2842,7 @@
         <v>3.3</v>
       </c>
       <c r="I8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2860,22 +2860,22 @@
         <v>3.9</v>
       </c>
       <c r="O8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
         <v>2.22</v>
@@ -2893,7 +2893,7 @@
         <v>17</v>
       </c>
       <c r="Z8">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA8">
         <v>75</v>
@@ -2914,10 +2914,10 @@
         <v>19</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
         <v>60</v>
@@ -2950,7 +2950,7 @@
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT8">
         <v>9.6</v>
@@ -2962,7 +2962,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX8">
         <v>13</v>
@@ -2974,25 +2974,25 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB8">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC8">
         <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF8">
         <v>15</v>
       </c>
       <c r="BG8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3075,10 +3075,10 @@
         <v>197</v>
       </c>
       <c r="F9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G9">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H9">
         <v>2.52</v>
@@ -3093,13 +3093,13 @@
         <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
         <v>1.2</v>
@@ -3114,13 +3114,13 @@
         <v>1.61</v>
       </c>
       <c r="S9">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T9">
         <v>1.56</v>
       </c>
       <c r="U9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V9">
         <v>1.64</v>
@@ -3168,7 +3168,7 @@
         <v>42</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL9">
         <v>32</v>
@@ -3210,13 +3210,13 @@
         <v>20</v>
       </c>
       <c r="AY9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
         <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BB9">
         <v>36</v>
@@ -3335,7 +3335,7 @@
         <v>4.8</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10">
         <v>1.01</v>
@@ -3562,10 +3562,10 @@
         <v>2.28</v>
       </c>
       <c r="G11">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I11">
         <v>3.15</v>
@@ -3598,19 +3598,19 @@
         <v>1.63</v>
       </c>
       <c r="S11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T11">
         <v>1.54</v>
       </c>
       <c r="U11">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
         <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3652,7 +3652,7 @@
         <v>34</v>
       </c>
       <c r="AK11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL11">
         <v>29</v>
@@ -3810,19 +3810,19 @@
         <v>11</v>
       </c>
       <c r="I12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L12">
         <v>1.24</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>7.2</v>
@@ -3834,22 +3834,22 @@
         <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S12">
         <v>2.16</v>
       </c>
       <c r="T12">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W12">
         <v>4.3</v>
@@ -3891,7 +3891,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK12">
         <v>14</v>
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="AV12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW12">
         <v>44</v>
@@ -4073,7 +4073,7 @@
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q13">
         <v>1.47</v>
@@ -4091,7 +4091,7 @@
         <v>3.05</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
         <v>1.9</v>
@@ -4145,7 +4145,7 @@
         <v>44</v>
       </c>
       <c r="AN13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO13">
         <v>20</v>
@@ -4214,7 +4214,7 @@
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -4223,7 +4223,7 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO13">
         <v>3.9</v>
@@ -4232,7 +4232,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
@@ -4241,10 +4241,10 @@
         <v>11</v>
       </c>
       <c r="BT13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -4285,16 +4285,16 @@
         <v>202</v>
       </c>
       <c r="F14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H14">
         <v>2.18</v>
       </c>
       <c r="I14">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J14">
         <v>3.85</v>
@@ -4321,22 +4321,22 @@
         <v>1.61</v>
       </c>
       <c r="R14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S14">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T14">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U14">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V14">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W14">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X14">
         <v>27</v>
@@ -4450,19 +4450,19 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BN14">
         <v>1000</v>
@@ -4474,13 +4474,13 @@
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BT14">
         <v>1000</v>
@@ -4492,19 +4492,19 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CB14" t="s">
         <v>257</v>
@@ -4527,10 +4527,10 @@
         <v>203</v>
       </c>
       <c r="F15">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H15">
         <v>5.7</v>
@@ -4557,7 +4557,7 @@
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
         <v>1.73</v>
@@ -4572,13 +4572,13 @@
         <v>1.84</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
         <v>1.19</v>
       </c>
       <c r="W15">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -5020,7 +5020,7 @@
         <v>2.44</v>
       </c>
       <c r="I17">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -5059,7 +5059,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
         <v>1.44</v>
@@ -5268,7 +5268,7 @@
         <v>2.78</v>
       </c>
       <c r="K18">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5495,10 +5495,10 @@
         <v>207</v>
       </c>
       <c r="F19">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G19">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H19">
         <v>3.25</v>
@@ -5507,7 +5507,7 @@
         <v>3.45</v>
       </c>
       <c r="J19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K19">
         <v>3.35</v>
@@ -5522,10 +5522,10 @@
         <v>2.72</v>
       </c>
       <c r="O19">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P19">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q19">
         <v>2.56</v>
@@ -5546,7 +5546,7 @@
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X19">
         <v>9.199999999999999</v>
@@ -5558,7 +5558,7 @@
         <v>21</v>
       </c>
       <c r="AA19">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -5567,7 +5567,7 @@
         <v>7.6</v>
       </c>
       <c r="AD19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE19">
         <v>65</v>
@@ -5579,7 +5579,7 @@
         <v>13</v>
       </c>
       <c r="AH19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI19">
         <v>80</v>
@@ -5606,7 +5606,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19">
         <v>17</v>
@@ -5624,10 +5624,10 @@
         <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY19">
         <v>11.5</v>
@@ -5636,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="BA19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB19">
+        <v>9.4</v>
+      </c>
+      <c r="BC19">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC19">
-        <v>9</v>
       </c>
       <c r="BD19">
         <v>10</v>
@@ -5651,7 +5651,7 @@
         <v>11</v>
       </c>
       <c r="BF19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG19">
         <v>10</v>
@@ -5743,7 +5743,7 @@
         <v>4.5</v>
       </c>
       <c r="H20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I20">
         <v>2.28</v>
@@ -6003,7 +6003,7 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="O21">
         <v>1.01</v>
@@ -6015,7 +6015,7 @@
         <v>1.8</v>
       </c>
       <c r="R21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S21">
         <v>2.76</v>
@@ -6221,10 +6221,10 @@
         <v>210</v>
       </c>
       <c r="F22">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G22">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H22">
         <v>3.1</v>
@@ -6236,7 +6236,7 @@
         <v>3.55</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22">
         <v>1.35</v>
@@ -6254,28 +6254,28 @@
         <v>2</v>
       </c>
       <c r="Q22">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S22">
         <v>3.25</v>
       </c>
       <c r="T22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V22">
         <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y22">
         <v>12.5</v>
@@ -6290,7 +6290,7 @@
         <v>11.5</v>
       </c>
       <c r="AC22">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>13.5</v>
@@ -6305,7 +6305,7 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI22">
         <v>44</v>
@@ -6353,7 +6353,7 @@
         <v>29</v>
       </c>
       <c r="AX22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
         <v>11</v>
@@ -6377,7 +6377,7 @@
         <v>14</v>
       </c>
       <c r="BF22">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG22">
         <v>24</v>
@@ -6475,7 +6475,7 @@
         <v>110</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K23">
         <v>930</v>
@@ -6511,10 +6511,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6708,7 +6708,7 @@
         <v>2.04</v>
       </c>
       <c r="G24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H24">
         <v>3</v>
@@ -6717,7 +6717,7 @@
         <v>3.3</v>
       </c>
       <c r="J24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K24">
         <v>5.1</v>
@@ -6729,13 +6729,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O24">
         <v>1.07</v>
       </c>
       <c r="P24">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q24">
         <v>1.3</v>
@@ -6756,7 +6756,7 @@
         <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6780,7 +6780,7 @@
         <v>25</v>
       </c>
       <c r="AE24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF24">
         <v>36</v>
@@ -6837,7 +6837,7 @@
         <v>16.5</v>
       </c>
       <c r="AX24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY24">
         <v>11</v>
@@ -6864,7 +6864,7 @@
         <v>4.7</v>
       </c>
       <c r="BG24">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -7960,7 +7960,7 @@
         <v>2.06</v>
       </c>
       <c r="U29">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V29">
         <v>1.4</v>
@@ -7972,7 +7972,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z29">
         <v>23</v>
@@ -8023,16 +8023,16 @@
         <v>70</v>
       </c>
       <c r="AP29">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ29">
         <v>8.199999999999999</v>
       </c>
       <c r="AR29">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT29">
         <v>7</v>
@@ -8044,37 +8044,37 @@
         <v>13</v>
       </c>
       <c r="AW29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX29">
         <v>13</v>
       </c>
       <c r="AY29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ29">
         <v>19</v>
       </c>
       <c r="BA29">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB29">
         <v>8.199999999999999</v>
       </c>
       <c r="BC29">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE29">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF29">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8160,7 +8160,7 @@
         <v>1.1</v>
       </c>
       <c r="G30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H30">
         <v>1.12</v>
@@ -8205,7 +8205,7 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W30">
         <v>1.02</v>
@@ -8447,7 +8447,7 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W31">
         <v>1.02</v>
@@ -9609,13 +9609,13 @@
         <v>224</v>
       </c>
       <c r="F36">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G36">
         <v>5.6</v>
       </c>
       <c r="H36">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I36">
         <v>2.1</v>
@@ -9639,19 +9639,19 @@
         <v>1.41</v>
       </c>
       <c r="P36">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
       </c>
       <c r="R36">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S36">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T36">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U36">
         <v>1.79</v>
@@ -10341,7 +10341,7 @@
         <v>1.75</v>
       </c>
       <c r="H39">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I39">
         <v>6.8</v>
@@ -10350,7 +10350,7 @@
         <v>3.75</v>
       </c>
       <c r="K39">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L39">
         <v>1.42</v>
@@ -10359,19 +10359,19 @@
         <v>1.08</v>
       </c>
       <c r="N39">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O39">
         <v>1.37</v>
       </c>
       <c r="P39">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q39">
         <v>2.04</v>
       </c>
       <c r="R39">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S39">
         <v>3.6</v>
@@ -10386,7 +10386,7 @@
         <v>1.17</v>
       </c>
       <c r="W39">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X39">
         <v>30</v>
@@ -11569,16 +11569,16 @@
         <v>1.07</v>
       </c>
       <c r="N44">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O44">
         <v>1.32</v>
       </c>
       <c r="P44">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q44">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="R44">
         <v>1.37</v>
@@ -11587,10 +11587,10 @@
         <v>3.45</v>
       </c>
       <c r="T44">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U44">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V44">
         <v>1.32</v>
@@ -11632,7 +11632,7 @@
         <v>17.5</v>
       </c>
       <c r="AI44">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ44">
         <v>27</v>
@@ -11644,7 +11644,7 @@
         <v>38</v>
       </c>
       <c r="AM44">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN44">
         <v>16.5</v>
@@ -11683,7 +11683,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ44">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA44">
         <v>11</v>
@@ -11692,10 +11692,10 @@
         <v>20</v>
       </c>
       <c r="BC44">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE44">
         <v>12</v>
@@ -12080,7 +12080,7 @@
         <v>1.01</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12755,10 +12755,10 @@
         <v>237</v>
       </c>
       <c r="F49">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G49">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>2.5</v>
@@ -12767,28 +12767,28 @@
         <v>2.52</v>
       </c>
       <c r="J49">
+        <v>2.88</v>
+      </c>
+      <c r="K49">
         <v>2.9</v>
       </c>
-      <c r="K49">
-        <v>2.92</v>
-      </c>
       <c r="L49">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M49">
         <v>1.19</v>
       </c>
       <c r="N49">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="O49">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="P49">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q49">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R49">
         <v>1.12</v>
@@ -12803,10 +12803,10 @@
         <v>1.56</v>
       </c>
       <c r="V49">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W49">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X49">
         <v>6.4</v>
@@ -12815,7 +12815,7 @@
         <v>6.4</v>
       </c>
       <c r="Z49">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA49">
         <v>42</v>
@@ -12824,10 +12824,10 @@
         <v>9</v>
       </c>
       <c r="AC49">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD49">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE49">
         <v>48</v>
@@ -12851,7 +12851,7 @@
         <v>90</v>
       </c>
       <c r="AL49">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM49">
         <v>350</v>
@@ -12863,19 +12863,19 @@
         <v>65</v>
       </c>
       <c r="AP49">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ49">
         <v>5.9</v>
       </c>
       <c r="AR49">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS49">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT49">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU49">
         <v>6.6</v>
@@ -12887,7 +12887,7 @@
         <v>40</v>
       </c>
       <c r="AX49">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY49">
         <v>18</v>
@@ -12896,85 +12896,85 @@
         <v>29</v>
       </c>
       <c r="BA49">
+        <v>13</v>
+      </c>
+      <c r="BB49">
+        <v>14</v>
+      </c>
+      <c r="BC49">
+        <v>14</v>
+      </c>
+      <c r="BD49">
+        <v>13</v>
+      </c>
+      <c r="BE49">
         <v>12</v>
       </c>
-      <c r="BB49">
-        <v>12.5</v>
-      </c>
-      <c r="BC49">
-        <v>12.5</v>
-      </c>
-      <c r="BD49">
-        <v>11</v>
-      </c>
-      <c r="BE49">
-        <v>11</v>
-      </c>
       <c r="BF49">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG49">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BH49">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="BI49">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ49">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK49">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN49">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO49">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP49">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ49">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BR49">
         <v>1000</v>
       </c>
       <c r="BS49">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT49">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU49">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV49">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW49">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BX49">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY49">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ49">
         <v>1000</v>
       </c>
       <c r="CA49">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB49" t="s">
         <v>257</v>
@@ -13006,7 +13006,7 @@
         <v>6</v>
       </c>
       <c r="I50">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J50">
         <v>4.3</v>
@@ -13027,25 +13027,25 @@
         <v>1.3</v>
       </c>
       <c r="P50">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q50">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R50">
         <v>1.41</v>
       </c>
       <c r="S50">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T50">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U50">
         <v>1.96</v>
       </c>
       <c r="V50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W50">
         <v>2.56</v>
@@ -13072,7 +13072,7 @@
         <v>24</v>
       </c>
       <c r="AE50">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF50">
         <v>9.6</v>
@@ -13114,7 +13114,7 @@
         <v>44</v>
       </c>
       <c r="AS50">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT50">
         <v>8.199999999999999</v>
@@ -13129,10 +13129,10 @@
         <v>13.5</v>
       </c>
       <c r="AX50">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY50">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ50">
         <v>19.5</v>
@@ -13150,7 +13150,7 @@
         <v>30</v>
       </c>
       <c r="BE50">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF50">
         <v>8</v>
@@ -13329,7 +13329,7 @@
         <v>34</v>
       </c>
       <c r="AJ51">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AK51">
         <v>110</v>
@@ -13410,7 +13410,7 @@
         <v>10.5</v>
       </c>
       <c r="BK51">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL51">
         <v>130</v>
@@ -13484,58 +13484,58 @@
         <v>1.5</v>
       </c>
       <c r="G52">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H52">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I52">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J52">
         <v>4.7</v>
       </c>
       <c r="K52">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L52">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M52">
         <v>1.06</v>
       </c>
       <c r="N52">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O52">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P52">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q52">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R52">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S52">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T52">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U52">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V52">
         <v>1.14</v>
       </c>
       <c r="W52">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X52">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y52">
         <v>25</v>
@@ -13544,31 +13544,31 @@
         <v>70</v>
       </c>
       <c r="AA52">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB52">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC52">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD52">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE52">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF52">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG52">
         <v>9.800000000000001</v>
       </c>
       <c r="AH52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI52">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ52">
         <v>13</v>
@@ -13580,28 +13580,28 @@
         <v>38</v>
       </c>
       <c r="AM52">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN52">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO52">
         <v>160</v>
       </c>
       <c r="AP52">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ52">
         <v>22</v>
       </c>
       <c r="AR52">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS52">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT52">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU52">
         <v>9.6</v>
@@ -13610,7 +13610,7 @@
         <v>26</v>
       </c>
       <c r="AW52">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX52">
         <v>7.8</v>
@@ -13622,7 +13622,7 @@
         <v>22</v>
       </c>
       <c r="BA52">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB52">
         <v>12</v>
@@ -13634,13 +13634,13 @@
         <v>32</v>
       </c>
       <c r="BE52">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF52">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG52">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13729,10 +13729,10 @@
         <v>2.04</v>
       </c>
       <c r="H53">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I53">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J53">
         <v>3.5</v>
@@ -13750,10 +13750,10 @@
         <v>3.3</v>
       </c>
       <c r="O53">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P53">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q53">
         <v>2.14</v>
@@ -13765,10 +13765,10 @@
         <v>4.1</v>
       </c>
       <c r="T53">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U53">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V53">
         <v>1.27</v>
@@ -13861,7 +13861,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ53">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA53">
         <v>60</v>
@@ -13873,7 +13873,7 @@
         <v>20</v>
       </c>
       <c r="BD53">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BE53">
         <v>13.5</v>
@@ -13968,19 +13968,19 @@
         <v>2.04</v>
       </c>
       <c r="G54">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H54">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I54">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J54">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K54">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L54">
         <v>1.41</v>
@@ -14007,10 +14007,10 @@
         <v>3.45</v>
       </c>
       <c r="T54">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U54">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V54">
         <v>1.29</v>
@@ -14025,7 +14025,7 @@
         <v>16</v>
       </c>
       <c r="Z54">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA54">
         <v>110</v>
@@ -14043,7 +14043,7 @@
         <v>65</v>
       </c>
       <c r="AF54">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG54">
         <v>11</v>
@@ -14055,7 +14055,7 @@
         <v>65</v>
       </c>
       <c r="AJ54">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK54">
         <v>24</v>
@@ -14067,7 +14067,7 @@
         <v>90</v>
       </c>
       <c r="AN54">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO54">
         <v>60</v>
@@ -14079,10 +14079,10 @@
         <v>13.5</v>
       </c>
       <c r="AR54">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS54">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT54">
         <v>8.4</v>
@@ -14094,7 +14094,7 @@
         <v>15</v>
       </c>
       <c r="AW54">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX54">
         <v>11</v>
@@ -14103,28 +14103,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ54">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA54">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB54">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC54">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD54">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE54">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF54">
         <v>12</v>
       </c>
       <c r="BG54">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14724,7 +14724,7 @@
         <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R57">
         <v>1.5</v>
@@ -14951,13 +14951,13 @@
         <v>3.9</v>
       </c>
       <c r="L58">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M58">
         <v>1.05</v>
       </c>
       <c r="N58">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O58">
         <v>1.26</v>
@@ -15002,7 +15002,7 @@
         <v>11.5</v>
       </c>
       <c r="AC58">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD58">
         <v>16.5</v>
@@ -15023,13 +15023,13 @@
         <v>60</v>
       </c>
       <c r="AJ58">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK58">
         <v>21</v>
       </c>
       <c r="AL58">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM58">
         <v>90</v>
@@ -15050,7 +15050,7 @@
         <v>25</v>
       </c>
       <c r="AS58">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT58">
         <v>10</v>
@@ -15074,19 +15074,19 @@
         <v>14.5</v>
       </c>
       <c r="BA58">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB58">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC58">
         <v>17.5</v>
       </c>
       <c r="BD58">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE58">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF58">
         <v>10.5</v>
@@ -15140,7 +15140,7 @@
         <v>38</v>
       </c>
       <c r="BW58">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BX58">
         <v>48</v>
@@ -15417,19 +15417,19 @@
         <v>248</v>
       </c>
       <c r="F60">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G60">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H60">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I60">
         <v>6.6</v>
       </c>
       <c r="J60">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K60">
         <v>3.8</v>
@@ -15438,10 +15438,10 @@
         <v>1.01</v>
       </c>
       <c r="M60">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N60">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O60">
         <v>1.43</v>
@@ -15450,25 +15450,25 @@
         <v>1.68</v>
       </c>
       <c r="Q60">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R60">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S60">
         <v>3.9</v>
       </c>
       <c r="T60">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U60">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="V60">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W60">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -15483,10 +15483,10 @@
         <v>1000</v>
       </c>
       <c r="AB60">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC60">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD60">
         <v>1000</v>
@@ -15495,7 +15495,7 @@
         <v>1000</v>
       </c>
       <c r="AF60">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG60">
         <v>11.5</v>
@@ -15507,7 +15507,7 @@
         <v>1000</v>
       </c>
       <c r="AJ60">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK60">
         <v>1000</v>
@@ -15525,58 +15525,58 @@
         <v>1000</v>
       </c>
       <c r="AP60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AQ60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AR60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AS60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AT60">
-        <v>5.9</v>
+        <v>1.49</v>
       </c>
       <c r="AU60">
+        <v>1.54</v>
+      </c>
+      <c r="AV60">
+        <v>1.76</v>
+      </c>
+      <c r="AW60">
+        <v>1.76</v>
+      </c>
+      <c r="AX60">
+        <v>1.58</v>
+      </c>
+      <c r="AY60">
         <v>1.53</v>
-      </c>
-      <c r="AV60">
-        <v>1.74</v>
-      </c>
-      <c r="AW60">
-        <v>1.74</v>
-      </c>
-      <c r="AX60">
-        <v>8</v>
-      </c>
-      <c r="AY60">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ60">
         <v>16</v>
       </c>
       <c r="BA60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BB60">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="BC60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BD60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BE60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BF60">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BG60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BH60">
         <v>1000</v>
@@ -15665,7 +15665,7 @@
         <v>3.25</v>
       </c>
       <c r="H61">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I61">
         <v>2.54</v>
@@ -15683,7 +15683,7 @@
         <v>1.08</v>
       </c>
       <c r="N61">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O61">
         <v>1.38</v>
@@ -15692,7 +15692,7 @@
         <v>1.82</v>
       </c>
       <c r="Q61">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R61">
         <v>1.32</v>
@@ -15710,10 +15710,10 @@
         <v>1.64</v>
       </c>
       <c r="W61">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X61">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y61">
         <v>9.800000000000001</v>
@@ -15767,10 +15767,10 @@
         <v>25</v>
       </c>
       <c r="AP61">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ61">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR61">
         <v>14</v>
@@ -15797,7 +15797,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ61">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA61">
         <v>40</v>
@@ -15809,7 +15809,7 @@
         <v>34</v>
       </c>
       <c r="BD61">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE61">
         <v>13.5</v>
@@ -15901,19 +15901,19 @@
         <v>250</v>
       </c>
       <c r="F62">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G62">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H62">
         <v>2.78</v>
       </c>
       <c r="I62">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J62">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K62">
         <v>3.95</v>
@@ -15928,7 +15928,7 @@
         <v>6.4</v>
       </c>
       <c r="O62">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P62">
         <v>2.78</v>
@@ -15946,13 +15946,13 @@
         <v>1.47</v>
       </c>
       <c r="U62">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V62">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W62">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X62">
         <v>28</v>
@@ -15961,7 +15961,7 @@
         <v>20</v>
       </c>
       <c r="Z62">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA62">
         <v>44</v>
@@ -15994,7 +15994,7 @@
         <v>38</v>
       </c>
       <c r="AK62">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL62">
         <v>28</v>
@@ -16152,7 +16152,7 @@
         <v>8</v>
       </c>
       <c r="I63">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J63">
         <v>5.2</v>
@@ -16173,7 +16173,7 @@
         <v>1.17</v>
       </c>
       <c r="P63">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q63">
         <v>1.52</v>
@@ -16206,7 +16206,7 @@
         <v>75</v>
       </c>
       <c r="AA63">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB63">
         <v>12</v>
@@ -16215,7 +16215,7 @@
         <v>12.5</v>
       </c>
       <c r="AD63">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE63">
         <v>95</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="AM63">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN63">
         <v>5</v>
@@ -16260,34 +16260,34 @@
         <v>60</v>
       </c>
       <c r="AS63">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT63">
         <v>11</v>
       </c>
       <c r="AU63">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV63">
         <v>26</v>
       </c>
       <c r="AW63">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX63">
         <v>9.800000000000001</v>
       </c>
       <c r="AY63">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ63">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA63">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB63">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC63">
         <v>12.5</v>
@@ -16338,7 +16338,7 @@
         <v>1000</v>
       </c>
       <c r="BS63">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BT63">
         <v>1000</v>
@@ -16394,7 +16394,7 @@
         <v>2.72</v>
       </c>
       <c r="I64">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J64">
         <v>2.7</v>
@@ -16433,7 +16433,7 @@
         <v>1.01</v>
       </c>
       <c r="V64">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W64">
         <v>1.64</v>
@@ -16627,22 +16627,22 @@
         <v>253</v>
       </c>
       <c r="F65">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="G65">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H65">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I65">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J65">
         <v>3.35</v>
       </c>
       <c r="K65">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L65">
         <v>1.47</v>
@@ -16654,31 +16654,31 @@
         <v>3.2</v>
       </c>
       <c r="O65">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P65">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q65">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R65">
         <v>1.28</v>
       </c>
       <c r="S65">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T65">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U65">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V65">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W65">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X65">
         <v>12</v>
@@ -16693,7 +16693,7 @@
         <v>120</v>
       </c>
       <c r="AB65">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC65">
         <v>8</v>
@@ -16741,13 +16741,13 @@
         <v>12</v>
       </c>
       <c r="AR65">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS65">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT65">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU65">
         <v>7</v>
@@ -16756,7 +16756,7 @@
         <v>16</v>
       </c>
       <c r="AW65">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX65">
         <v>10</v>
@@ -16768,25 +16768,25 @@
         <v>18</v>
       </c>
       <c r="BA65">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB65">
         <v>20</v>
       </c>
       <c r="BC65">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD65">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE65">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF65">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BG65">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16869,118 +16869,118 @@
         <v>254</v>
       </c>
       <c r="F66">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G66">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H66">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I66">
+        <v>13</v>
+      </c>
+      <c r="J66">
+        <v>4.5</v>
+      </c>
+      <c r="K66">
+        <v>5.8</v>
+      </c>
+      <c r="L66">
+        <v>1.01</v>
+      </c>
+      <c r="M66">
+        <v>1.07</v>
+      </c>
+      <c r="N66">
+        <v>3.6</v>
+      </c>
+      <c r="O66">
+        <v>1.29</v>
+      </c>
+      <c r="P66">
+        <v>1.9</v>
+      </c>
+      <c r="Q66">
+        <v>1.91</v>
+      </c>
+      <c r="R66">
+        <v>1.33</v>
+      </c>
+      <c r="S66">
+        <v>3.35</v>
+      </c>
+      <c r="T66">
+        <v>2.06</v>
+      </c>
+      <c r="U66">
+        <v>1.68</v>
+      </c>
+      <c r="V66">
+        <v>1.08</v>
+      </c>
+      <c r="W66">
+        <v>3.1</v>
+      </c>
+      <c r="X66">
+        <v>17.5</v>
+      </c>
+      <c r="Y66">
+        <v>29</v>
+      </c>
+      <c r="Z66">
         <v>110</v>
       </c>
-      <c r="J66">
-        <v>4.4</v>
-      </c>
-      <c r="K66">
+      <c r="AA66">
+        <v>520</v>
+      </c>
+      <c r="AB66">
         <v>7.4</v>
       </c>
-      <c r="L66">
-        <v>1.01</v>
-      </c>
-      <c r="M66">
-        <v>1.05</v>
-      </c>
-      <c r="N66">
-        <v>3.3</v>
-      </c>
-      <c r="O66">
-        <v>1.28</v>
-      </c>
-      <c r="P66">
-        <v>1.87</v>
-      </c>
-      <c r="Q66">
-        <v>1.89</v>
-      </c>
-      <c r="R66">
-        <v>1.3</v>
-      </c>
-      <c r="S66">
-        <v>3</v>
-      </c>
-      <c r="T66">
-        <v>1.01</v>
-      </c>
-      <c r="U66">
-        <v>1.01</v>
-      </c>
-      <c r="V66">
-        <v>1.04</v>
-      </c>
-      <c r="W66">
-        <v>3.05</v>
-      </c>
-      <c r="X66">
-        <v>1000</v>
-      </c>
-      <c r="Y66">
-        <v>36</v>
-      </c>
-      <c r="Z66">
-        <v>1000</v>
-      </c>
-      <c r="AA66">
-        <v>1000</v>
-      </c>
-      <c r="AB66">
-        <v>8.6</v>
-      </c>
       <c r="AC66">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD66">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE66">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF66">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG66">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH66">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI66">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ66">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK66">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL66">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM66">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN66">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO66">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP66">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ66">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR66">
         <v>1.03</v>
@@ -16989,7 +16989,7 @@
         <v>1.03</v>
       </c>
       <c r="AT66">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU66">
         <v>1.03</v>
@@ -17001,10 +17001,10 @@
         <v>1.03</v>
       </c>
       <c r="AX66">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY66">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ66">
         <v>1.03</v>
@@ -17013,19 +17013,19 @@
         <v>1.03</v>
       </c>
       <c r="BB66">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BC66">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD66">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE66">
         <v>1.03</v>
       </c>
       <c r="BF66">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG66">
         <v>1.01</v>
@@ -17114,16 +17114,16 @@
         <v>2.16</v>
       </c>
       <c r="G67">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I67">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J67">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K67">
         <v>3.35</v>
@@ -17153,16 +17153,16 @@
         <v>4.8</v>
       </c>
       <c r="T67">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U67">
         <v>1.83</v>
       </c>
       <c r="V67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X67">
         <v>9.4</v>
@@ -17183,7 +17183,7 @@
         <v>7.6</v>
       </c>
       <c r="AD67">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE67">
         <v>80</v>
@@ -17255,7 +17255,7 @@
         <v>9</v>
       </c>
       <c r="BB67">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BC67">
         <v>7.4</v>
@@ -17267,7 +17267,7 @@
         <v>9.4</v>
       </c>
       <c r="BF67">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BG67">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>2.44</v>
       </c>
       <c r="G68">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="H68">
         <v>3.25</v>
@@ -17404,7 +17404,7 @@
         <v>1.25</v>
       </c>
       <c r="W68">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X68">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -853,7 +853,7 @@
     <t>Tolima</t>
   </si>
   <si>
-    <t>2026-09-26 01:07:34</t>
+    <t>2026-09-26 03:27:52</t>
   </si>
 </sst>
 </file>
@@ -1447,16 +1447,16 @@
         <v>204</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
         <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1465,7 +1465,7 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1486,7 +1486,7 @@
         <v>1.64</v>
       </c>
       <c r="S2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T2">
         <v>1.54</v>
@@ -1495,7 +1495,7 @@
         <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
         <v>1.73</v>
@@ -1507,7 +1507,7 @@
         <v>18</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2">
         <v>50</v>
@@ -1522,7 +1522,7 @@
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF2">
         <v>18.5</v>
@@ -1531,7 +1531,7 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI2">
         <v>32</v>
@@ -1561,10 +1561,10 @@
         <v>16</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AT2">
         <v>13.5</v>
@@ -1588,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="BA2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB2">
         <v>21</v>
@@ -1600,7 +1600,7 @@
         <v>23</v>
       </c>
       <c r="BE2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
@@ -1609,13 +1609,13 @@
         <v>16</v>
       </c>
       <c r="BH2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2">
         <v>7.4</v>
@@ -1645,22 +1645,22 @@
         <v>17.5</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
         <v>24</v>
       </c>
       <c r="BW2">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BZ2">
         <v>18</v>
@@ -1689,22 +1689,22 @@
         <v>205</v>
       </c>
       <c r="F3">
+        <v>1.47</v>
+      </c>
+      <c r="G3">
         <v>1.49</v>
       </c>
-      <c r="G3">
-        <v>1.51</v>
-      </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1713,34 +1713,34 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O3">
         <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R3">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S3">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3">
         <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X3">
         <v>30</v>
@@ -1758,19 +1758,19 @@
         <v>12.5</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD3">
         <v>27</v>
       </c>
       <c r="AE3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3">
         <v>21</v>
@@ -1791,13 +1791,13 @@
         <v>85</v>
       </c>
       <c r="AN3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO3">
         <v>70</v>
       </c>
       <c r="AP3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3">
         <v>27</v>
@@ -1818,7 +1818,7 @@
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AX3">
         <v>9.800000000000001</v>
@@ -1830,10 +1830,10 @@
         <v>18</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC3">
         <v>12.5</v>
@@ -1842,25 +1842,25 @@
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BF3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG3">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BH3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1869,19 +1869,19 @@
         <v>21</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS3">
         <v>9.6</v>
@@ -1890,10 +1890,10 @@
         <v>11</v>
       </c>
       <c r="BU3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW3">
         <v>21</v>
@@ -1905,10 +1905,10 @@
         <v>21</v>
       </c>
       <c r="BZ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA3">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
         <v>279</v>
@@ -1931,7 +1931,7 @@
         <v>206</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
         <v>2.4</v>
@@ -1946,10 +1946,10 @@
         <v>3.8</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4">
         <v>1.04</v>
@@ -1961,19 +1961,19 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S4">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U4">
         <v>2.6</v>
@@ -1985,13 +1985,13 @@
         <v>1.72</v>
       </c>
       <c r="X4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4">
         <v>16.5</v>
       </c>
       <c r="Z4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4">
         <v>55</v>
@@ -2000,7 +2000,7 @@
         <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>14</v>
@@ -2018,7 +2018,7 @@
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ4">
         <v>36</v>
@@ -2030,25 +2030,25 @@
         <v>30</v>
       </c>
       <c r="AM4">
-        <v>530</v>
+        <v>650</v>
       </c>
       <c r="AN4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4">
         <v>21</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT4">
         <v>12.5</v>
@@ -2069,7 +2069,7 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
         <v>22</v>
@@ -2081,7 +2081,7 @@
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE4">
         <v>29</v>
@@ -2093,16 +2093,16 @@
         <v>17.5</v>
       </c>
       <c r="BH4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI4">
         <v>3.7</v>
       </c>
       <c r="BJ4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -2111,13 +2111,13 @@
         <v>21</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
         <v>13.5</v>
@@ -2126,31 +2126,31 @@
         <v>27</v>
       </c>
       <c r="BS4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BX4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY4">
         <v>22</v>
       </c>
       <c r="BZ4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>279</v>
@@ -2173,22 +2173,22 @@
         <v>207</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="H5">
+        <v>5.7</v>
+      </c>
+      <c r="I5">
         <v>6.2</v>
       </c>
-      <c r="I5">
-        <v>6.8</v>
-      </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -2200,40 +2200,40 @@
         <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
         <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="X5">
+        <v>24</v>
+      </c>
+      <c r="Y5">
         <v>25</v>
       </c>
-      <c r="Y5">
-        <v>26</v>
-      </c>
       <c r="Z5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -2245,79 +2245,79 @@
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK5">
         <v>16</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AO5">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AP5">
         <v>20</v>
       </c>
       <c r="AQ5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5">
         <v>40</v>
       </c>
       <c r="AS5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU5">
         <v>9.6</v>
       </c>
-      <c r="AU5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AV5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AX5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY5">
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC5">
         <v>14</v>
@@ -2329,10 +2329,10 @@
         <v>36</v>
       </c>
       <c r="BF5">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2344,13 +2344,13 @@
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BN5">
         <v>5.4</v>
@@ -2362,13 +2362,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>1000</v>
@@ -2380,19 +2380,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CB5" t="s">
         <v>279</v>
@@ -2421,7 +2421,7 @@
         <v>2.56</v>
       </c>
       <c r="H6">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I6">
         <v>2.94</v>
@@ -2433,28 +2433,28 @@
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
         <v>1.65</v>
       </c>
       <c r="R6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T6">
         <v>1.57</v>
@@ -2484,10 +2484,10 @@
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
         <v>29</v>
@@ -2532,7 +2532,7 @@
         <v>19</v>
       </c>
       <c r="AS6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AT6">
         <v>13.5</v>
@@ -2544,7 +2544,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AX6">
         <v>17</v>
@@ -2559,13 +2559,13 @@
         <v>21</v>
       </c>
       <c r="BB6">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BE6">
         <v>28</v>
@@ -2577,61 +2577,61 @@
         <v>15.5</v>
       </c>
       <c r="BH6">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN6">
         <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BR6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BS6">
         <v>19</v>
       </c>
       <c r="BT6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BW6">
         <v>16</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BY6">
         <v>20</v>
       </c>
       <c r="BZ6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CA6">
         <v>13</v>
@@ -2669,13 +2669,13 @@
         <v>3.8</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
         <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
         <v>1.07</v>
@@ -2684,7 +2684,7 @@
         <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
         <v>1.92</v>
@@ -2771,10 +2771,10 @@
         <v>12</v>
       </c>
       <c r="AR7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT7">
         <v>8.6</v>
@@ -2798,19 +2798,19 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC7">
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF7">
         <v>15.5</v>
@@ -2899,40 +2899,40 @@
         <v>210</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I8">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
         <v>4</v>
       </c>
       <c r="O8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P8">
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
         <v>1.4</v>
@@ -2941,28 +2941,28 @@
         <v>3.3</v>
       </c>
       <c r="T8">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X8">
         <v>18.5</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB8">
         <v>11.5</v>
@@ -2971,13 +2971,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE8">
         <v>40</v>
       </c>
       <c r="AF8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG8">
         <v>12</v>
@@ -2986,7 +2986,7 @@
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
         <v>38</v>
@@ -2998,13 +2998,13 @@
         <v>44</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP8">
         <v>13.5</v>
@@ -3016,10 +3016,10 @@
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8">
         <v>7.4</v>
@@ -3028,19 +3028,19 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY8">
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB8">
         <v>22</v>
@@ -3052,13 +3052,13 @@
         <v>26</v>
       </c>
       <c r="BE8">
+        <v>7</v>
+      </c>
+      <c r="BF8">
+        <v>16</v>
+      </c>
+      <c r="BG8">
         <v>6.2</v>
-      </c>
-      <c r="BF8">
-        <v>15</v>
-      </c>
-      <c r="BG8">
-        <v>5.7</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3141,31 +3141,31 @@
         <v>211</v>
       </c>
       <c r="F9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G9">
+        <v>2.64</v>
+      </c>
+      <c r="H9">
+        <v>2.64</v>
+      </c>
+      <c r="I9">
         <v>2.68</v>
       </c>
-      <c r="H9">
-        <v>2.58</v>
-      </c>
-      <c r="I9">
-        <v>2.64</v>
-      </c>
       <c r="J9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O9">
         <v>1.2</v>
@@ -3180,19 +3180,19 @@
         <v>1.62</v>
       </c>
       <c r="S9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
         <v>1.56</v>
       </c>
       <c r="U9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V9">
+        <v>1.59</v>
+      </c>
+      <c r="W9">
         <v>1.6</v>
-      </c>
-      <c r="W9">
-        <v>1.59</v>
       </c>
       <c r="X9">
         <v>23</v>
@@ -3210,7 +3210,7 @@
         <v>16</v>
       </c>
       <c r="AC9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD9">
         <v>12.5</v>
@@ -3222,7 +3222,7 @@
         <v>21</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
         <v>15</v>
@@ -3234,7 +3234,7 @@
         <v>38</v>
       </c>
       <c r="AK9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL9">
         <v>30</v>
@@ -3264,7 +3264,7 @@
         <v>14.5</v>
       </c>
       <c r="AU9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
         <v>11</v>
@@ -3300,13 +3300,13 @@
         <v>13</v>
       </c>
       <c r="BG9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH9">
         <v>5.5</v>
       </c>
       <c r="BI9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3330,7 +3330,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -3342,7 +3342,7 @@
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3383,178 +3383,178 @@
         <v>212</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G10">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="H10">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="I10">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
         <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S10">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U10">
         <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W10">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y10">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10">
         <v>13</v>
       </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW10">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3563,40 +3563,40 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>213</v>
       </c>
       <c r="F11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G11">
         <v>1.3</v>
@@ -3637,22 +3637,22 @@
         <v>12.5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L11">
         <v>1.24</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
         <v>7.2</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
         <v>3.1</v>
@@ -3661,10 +3661,10 @@
         <v>1.45</v>
       </c>
       <c r="R11">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S11">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T11">
         <v>1.92</v>
@@ -3679,7 +3679,7 @@
         <v>4.3</v>
       </c>
       <c r="X11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y11">
         <v>48</v>
@@ -3703,16 +3703,16 @@
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
         <v>30</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ11">
         <v>10</v>
@@ -3724,22 +3724,22 @@
         <v>32</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AO11">
         <v>180</v>
       </c>
       <c r="AP11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AQ11">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AR11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AS11">
         <v>55</v>
@@ -3748,10 +3748,10 @@
         <v>11.5</v>
       </c>
       <c r="AU11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AW11">
         <v>44</v>
@@ -3778,7 +3778,7 @@
         <v>26</v>
       </c>
       <c r="BE11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF11">
         <v>3.55</v>
@@ -3796,7 +3796,7 @@
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3808,25 +3808,25 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3867,67 +3867,67 @@
         <v>214</v>
       </c>
       <c r="F12">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
         <v>3.6</v>
       </c>
       <c r="I12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R12">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="S12">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U12">
         <v>3.05</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA12">
         <v>80</v>
@@ -3939,13 +3939,13 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
         <v>36</v>
       </c>
       <c r="AF12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG12">
         <v>11.5</v>
@@ -3966,10 +3966,10 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO12">
         <v>20</v>
@@ -3987,10 +3987,10 @@
         <v>32</v>
       </c>
       <c r="AT12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
         <v>14.5</v>
@@ -4023,16 +4023,16 @@
         <v>29</v>
       </c>
       <c r="BF12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH12">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BI12">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ12">
         <v>8.4</v>
@@ -4044,7 +4044,7 @@
         <v>65</v>
       </c>
       <c r="BM12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BN12">
         <v>5.6</v>
@@ -4056,19 +4056,19 @@
         <v>13</v>
       </c>
       <c r="BQ12">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BS12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BT12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
         <v>24</v>
@@ -4080,13 +4080,13 @@
         <v>27</v>
       </c>
       <c r="BY12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BZ12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
         <v>279</v>
@@ -4109,22 +4109,22 @@
         <v>215</v>
       </c>
       <c r="F13">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I13">
         <v>3.15</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.3</v>
@@ -4133,10 +4133,10 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P13">
         <v>2.6</v>
@@ -4148,121 +4148,121 @@
         <v>1.63</v>
       </c>
       <c r="S13">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T13">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U13">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
         <v>1.46</v>
       </c>
       <c r="W13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y13">
         <v>19</v>
       </c>
       <c r="Z13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA13">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="AB13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI13">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM13">
         <v>60</v>
       </c>
       <c r="AN13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO13">
         <v>19.5</v>
       </c>
       <c r="AP13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS13">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AT13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AX13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY13">
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BC13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD13">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE13">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BF13">
         <v>10.5</v>
@@ -4280,7 +4280,7 @@
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -4316,7 +4316,7 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX13">
         <v>1000</v>
@@ -4357,7 +4357,7 @@
         <v>3.4</v>
       </c>
       <c r="H14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I14">
         <v>2.26</v>
@@ -4375,22 +4375,22 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P14">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R14">
         <v>1.6</v>
       </c>
       <c r="S14">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
         <v>1.57</v>
@@ -4402,10 +4402,10 @@
         <v>1.79</v>
       </c>
       <c r="W14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y14">
         <v>14.5</v>
@@ -4462,7 +4462,7 @@
         <v>19</v>
       </c>
       <c r="AQ14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR14">
         <v>14.5</v>
@@ -4492,19 +4492,19 @@
         <v>13</v>
       </c>
       <c r="BA14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC14">
         <v>7.6</v>
       </c>
       <c r="BD14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF14">
         <v>17.5</v>
@@ -4516,37 +4516,37 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="BT14">
         <v>1000</v>
@@ -4558,19 +4558,19 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="CB14" t="s">
         <v>279</v>
@@ -4593,7 +4593,7 @@
         <v>217</v>
       </c>
       <c r="F15">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G15">
         <v>1.65</v>
@@ -4602,16 +4602,16 @@
         <v>5.6</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K15">
         <v>4.7</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M15">
         <v>1.05</v>
@@ -4623,19 +4623,19 @@
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R15">
         <v>1.49</v>
       </c>
       <c r="S15">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T15">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U15">
         <v>2.12</v>
@@ -4647,7 +4647,7 @@
         <v>2.52</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y15">
         <v>22</v>
@@ -4659,7 +4659,7 @@
         <v>170</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15">
         <v>10.5</v>
@@ -4668,7 +4668,7 @@
         <v>22</v>
       </c>
       <c r="AE15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF15">
         <v>10.5</v>
@@ -4683,19 +4683,19 @@
         <v>80</v>
       </c>
       <c r="AJ15">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AK15">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM15">
         <v>120</v>
       </c>
       <c r="AN15">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AO15">
         <v>80</v>
@@ -4704,25 +4704,25 @@
         <v>17.5</v>
       </c>
       <c r="AQ15">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="AR15">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AS15">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AT15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>3.95</v>
+        <v>19</v>
       </c>
       <c r="AW15">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AX15">
         <v>9.199999999999999</v>
@@ -4731,88 +4731,88 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="BA15">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BB15">
         <v>13.5</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE15">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG15">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI15">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK15">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO15">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU15">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB15" t="s">
         <v>279</v>
@@ -4835,7 +4835,7 @@
         <v>218</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G16">
         <v>2.6</v>
@@ -4844,7 +4844,7 @@
         <v>2.64</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J16">
         <v>3.65</v>
@@ -4859,16 +4859,16 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R16">
         <v>1.51</v>
@@ -4877,13 +4877,13 @@
         <v>2.54</v>
       </c>
       <c r="T16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
         <v>1.62</v>
@@ -4922,7 +4922,7 @@
         <v>17.5</v>
       </c>
       <c r="AI16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ16">
         <v>42</v>
@@ -4943,58 +4943,58 @@
         <v>21</v>
       </c>
       <c r="AP16">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
+        <v>1.03</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>1.03</v>
+      </c>
+      <c r="AU16">
+        <v>1.03</v>
+      </c>
+      <c r="AV16">
+        <v>1.03</v>
+      </c>
+      <c r="AW16">
+        <v>1.03</v>
+      </c>
+      <c r="AX16">
+        <v>1.03</v>
+      </c>
+      <c r="AY16">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16">
+        <v>1.03</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
         <v>11.5</v>
       </c>
-      <c r="AR16">
-        <v>16</v>
-      </c>
-      <c r="AS16">
-        <v>1.03</v>
-      </c>
-      <c r="AT16">
-        <v>11</v>
-      </c>
-      <c r="AU16">
-        <v>7.2</v>
-      </c>
-      <c r="AV16">
-        <v>10</v>
-      </c>
-      <c r="AW16">
-        <v>20</v>
-      </c>
-      <c r="AX16">
-        <v>15</v>
-      </c>
-      <c r="AY16">
-        <v>9.6</v>
-      </c>
-      <c r="AZ16">
-        <v>11.5</v>
-      </c>
-      <c r="BA16">
-        <v>1.03</v>
-      </c>
-      <c r="BB16">
-        <v>1.03</v>
-      </c>
-      <c r="BC16">
-        <v>19</v>
-      </c>
-      <c r="BD16">
-        <v>1.03</v>
-      </c>
-      <c r="BE16">
-        <v>1.03</v>
-      </c>
-      <c r="BF16">
-        <v>12</v>
-      </c>
       <c r="BG16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -5322,19 +5322,19 @@
         <v>2.48</v>
       </c>
       <c r="G18">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H18">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="I18">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J18">
-        <v>2.78</v>
+        <v>3.45</v>
       </c>
       <c r="K18">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5343,7 +5343,7 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
         <v>1.21</v>
@@ -5367,10 +5367,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5564,19 +5564,19 @@
         <v>2.48</v>
       </c>
       <c r="G19">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H19">
         <v>3.25</v>
       </c>
       <c r="I19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J19">
         <v>3.15</v>
       </c>
       <c r="K19">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L19">
         <v>1.52</v>
@@ -5585,16 +5585,16 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O19">
         <v>1.52</v>
       </c>
       <c r="P19">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q19">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
         <v>1.21</v>
@@ -5606,19 +5606,19 @@
         <v>2.14</v>
       </c>
       <c r="U19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V19">
         <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X19">
         <v>9.199999999999999</v>
       </c>
       <c r="Y19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z19">
         <v>21</v>
@@ -5633,7 +5633,7 @@
         <v>7.6</v>
       </c>
       <c r="AD19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE19">
         <v>65</v>
@@ -5645,13 +5645,13 @@
         <v>13</v>
       </c>
       <c r="AH19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI19">
         <v>80</v>
       </c>
       <c r="AJ19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK19">
         <v>38</v>
@@ -5663,7 +5663,7 @@
         <v>200</v>
       </c>
       <c r="AN19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO19">
         <v>70</v>
@@ -5672,13 +5672,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ19">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR19">
         <v>17</v>
       </c>
       <c r="AS19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT19">
         <v>7.2</v>
@@ -5705,28 +5705,28 @@
         <v>10.5</v>
       </c>
       <c r="BB19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC19">
         <v>9.199999999999999</v>
       </c>
       <c r="BD19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI19">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5738,7 +5738,7 @@
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BN19">
         <v>1000</v>
@@ -5750,13 +5750,13 @@
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BT19">
         <v>1000</v>
@@ -5768,19 +5768,19 @@
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="CB19" t="s">
         <v>279</v>
@@ -5827,7 +5827,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
         <v>1.01</v>
@@ -5836,13 +5836,13 @@
         <v>1.98</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="R20">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -6305,13 +6305,13 @@
         <v>3.6</v>
       </c>
       <c r="L22">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M22">
         <v>1.07</v>
       </c>
       <c r="N22">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>1.31</v>
@@ -6323,10 +6323,10 @@
         <v>1.91</v>
       </c>
       <c r="R22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T22">
         <v>1.75</v>
@@ -6344,7 +6344,7 @@
         <v>15.5</v>
       </c>
       <c r="Y22">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z22">
         <v>22</v>
@@ -6356,7 +6356,7 @@
         <v>11.5</v>
       </c>
       <c r="AC22">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22">
         <v>13.5</v>
@@ -6401,10 +6401,10 @@
         <v>12</v>
       </c>
       <c r="AR22">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT22">
         <v>10</v>
@@ -6419,7 +6419,7 @@
         <v>29</v>
       </c>
       <c r="AX22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY22">
         <v>11</v>
@@ -6440,7 +6440,7 @@
         <v>32</v>
       </c>
       <c r="BE22">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BF22">
         <v>16.5</v>
@@ -6452,7 +6452,7 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.5</v>
+        <v>2.92</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
@@ -7013,13 +7013,13 @@
         <v>227</v>
       </c>
       <c r="F25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G25">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I25">
         <v>3.3</v>
@@ -7037,13 +7037,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O25">
         <v>1.07</v>
       </c>
       <c r="P25">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q25">
         <v>1.3</v>
@@ -7055,16 +7055,16 @@
         <v>1.72</v>
       </c>
       <c r="T25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U25">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V25">
         <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -8226,7 +8226,7 @@
         <v>1.1</v>
       </c>
       <c r="G30">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H30">
         <v>1.1</v>
@@ -8710,7 +8710,7 @@
         <v>1.1</v>
       </c>
       <c r="G32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H32">
         <v>1.12</v>
@@ -8952,13 +8952,13 @@
         <v>2.52</v>
       </c>
       <c r="G33">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H33">
         <v>3.25</v>
       </c>
       <c r="I33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J33">
         <v>3.15</v>
@@ -8976,7 +8976,7 @@
         <v>2.72</v>
       </c>
       <c r="O33">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P33">
         <v>1.59</v>
@@ -8988,34 +8988,34 @@
         <v>1.22</v>
       </c>
       <c r="S33">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T33">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U33">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W33">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X33">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9.800000000000001</v>
       </c>
       <c r="Z33">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA33">
         <v>75</v>
       </c>
       <c r="AB33">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>7.4</v>
@@ -9027,13 +9027,13 @@
         <v>55</v>
       </c>
       <c r="AF33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI33">
         <v>85</v>
@@ -9057,28 +9057,28 @@
         <v>70</v>
       </c>
       <c r="AP33">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ33">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR33">
         <v>18</v>
       </c>
       <c r="AS33">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT33">
         <v>7</v>
       </c>
       <c r="AU33">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV33">
         <v>13</v>
       </c>
       <c r="AW33">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX33">
         <v>13</v>
@@ -9087,34 +9087,34 @@
         <v>11</v>
       </c>
       <c r="AZ33">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA33">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB33">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC33">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE33">
+        <v>10.5</v>
+      </c>
+      <c r="BF33">
         <v>9</v>
       </c>
-      <c r="BE33">
-        <v>9.4</v>
-      </c>
-      <c r="BF33">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG33">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH33">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI33">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ33">
         <v>11.5</v>
@@ -9129,10 +9129,10 @@
         <v>21</v>
       </c>
       <c r="BN33">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO33">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP33">
         <v>1000</v>
@@ -9147,10 +9147,10 @@
         <v>34</v>
       </c>
       <c r="BT33">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU33">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV33">
         <v>1000</v>
@@ -9675,61 +9675,61 @@
         <v>238</v>
       </c>
       <c r="F36">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G36">
         <v>5.5</v>
       </c>
       <c r="H36">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="I36">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="J36">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K36">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L36">
         <v>1.44</v>
       </c>
       <c r="M36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N36">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
         <v>1.41</v>
       </c>
       <c r="P36">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
       </c>
       <c r="R36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S36">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T36">
         <v>1.9</v>
       </c>
       <c r="U36">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V36">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y36">
         <v>970</v>
@@ -9741,7 +9741,7 @@
         <v>1000</v>
       </c>
       <c r="AB36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC36">
         <v>970</v>
@@ -9783,64 +9783,64 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AQ36">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR36">
-        <v>1.45</v>
+        <v>7.2</v>
       </c>
       <c r="AS36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AT36">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AU36">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV36">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AW36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AX36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AY36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AZ36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BA36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BB36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BC36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BD36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BE36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BG36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BH36">
         <v>1000</v>
       </c>
       <c r="BI36">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BJ36">
         <v>1000</v>
@@ -10183,7 +10183,7 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O38">
         <v>1.01</v>
@@ -10192,13 +10192,13 @@
         <v>2.08</v>
       </c>
       <c r="Q38">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R38">
         <v>1.41</v>
       </c>
       <c r="S38">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -11127,22 +11127,22 @@
         <v>244</v>
       </c>
       <c r="F42">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G42">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H42">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I42">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K42">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L42">
         <v>1.42</v>
@@ -11151,13 +11151,13 @@
         <v>1.08</v>
       </c>
       <c r="N42">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O42">
         <v>1.36</v>
       </c>
       <c r="P42">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q42">
         <v>2.04</v>
@@ -11166,7 +11166,7 @@
         <v>1.29</v>
       </c>
       <c r="S42">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T42">
         <v>1.98</v>
@@ -11178,10 +11178,10 @@
         <v>1.17</v>
       </c>
       <c r="W42">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X42">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y42">
         <v>1000</v>
@@ -11208,7 +11208,7 @@
         <v>970</v>
       </c>
       <c r="AG42">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AH42">
         <v>1000</v>
@@ -11217,7 +11217,7 @@
         <v>1000</v>
       </c>
       <c r="AJ42">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK42">
         <v>1000</v>
@@ -11235,16 +11235,16 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.51</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ42">
-        <v>1.59</v>
+        <v>10</v>
       </c>
       <c r="AR42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AS42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AT42">
         <v>5.7</v>
@@ -11253,40 +11253,40 @@
         <v>6.2</v>
       </c>
       <c r="AV42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AW42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AX42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY42">
         <v>7.2</v>
       </c>
       <c r="AZ42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BA42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BB42">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BD42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BE42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BF42">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG42">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11304,7 +11304,7 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BN42">
         <v>1000</v>
@@ -11322,7 +11322,7 @@
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BT42">
         <v>1000</v>
@@ -11334,19 +11334,19 @@
         <v>1000</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BZ42">
         <v>1000</v>
       </c>
       <c r="CA42">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="CB42" t="s">
         <v>279</v>
@@ -11372,7 +11372,7 @@
         <v>2.12</v>
       </c>
       <c r="G43">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H43">
         <v>3.85</v>
@@ -11381,7 +11381,7 @@
         <v>4.1</v>
       </c>
       <c r="J43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K43">
         <v>3.6</v>
@@ -11396,37 +11396,37 @@
         <v>3.75</v>
       </c>
       <c r="O43">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P43">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q43">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R43">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T43">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U43">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V43">
         <v>1.32</v>
       </c>
       <c r="W43">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X43">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y43">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z43">
         <v>29</v>
@@ -11453,10 +11453,10 @@
         <v>11</v>
       </c>
       <c r="AH43">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI43">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ43">
         <v>27</v>
@@ -11471,7 +11471,7 @@
         <v>90</v>
       </c>
       <c r="AN43">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO43">
         <v>60</v>
@@ -11486,7 +11486,7 @@
         <v>21</v>
       </c>
       <c r="AS43">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT43">
         <v>8.800000000000001</v>
@@ -11498,7 +11498,7 @@
         <v>14</v>
       </c>
       <c r="AW43">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX43">
         <v>12</v>
@@ -11507,34 +11507,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ43">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA43">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB43">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BC43">
         <v>21</v>
       </c>
       <c r="BD43">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE43">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF43">
         <v>14</v>
       </c>
       <c r="BG43">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH43">
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>1.49</v>
+        <v>2.88</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
@@ -11546,7 +11546,7 @@
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BN43">
         <v>6.8</v>
@@ -11558,13 +11558,13 @@
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BT43">
         <v>1000</v>
@@ -11576,19 +11576,19 @@
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BZ43">
         <v>1000</v>
       </c>
       <c r="CA43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CB43" t="s">
         <v>279</v>
@@ -11611,13 +11611,13 @@
         <v>246</v>
       </c>
       <c r="F44">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G44">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H44">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I44">
         <v>8</v>
@@ -11629,7 +11629,7 @@
         <v>4.9</v>
       </c>
       <c r="L44">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M44">
         <v>1.06</v>
@@ -11644,7 +11644,7 @@
         <v>2.14</v>
       </c>
       <c r="Q44">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R44">
         <v>1.43</v>
@@ -11662,10 +11662,10 @@
         <v>1.14</v>
       </c>
       <c r="W44">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="X44">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y44">
         <v>25</v>
@@ -11677,13 +11677,13 @@
         <v>260</v>
       </c>
       <c r="AB44">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC44">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD44">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE44">
         <v>120</v>
@@ -11728,7 +11728,7 @@
         <v>55</v>
       </c>
       <c r="AS44">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT44">
         <v>7.8</v>
@@ -11764,16 +11764,16 @@
         <v>32</v>
       </c>
       <c r="BE44">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF44">
         <v>6.8</v>
       </c>
       <c r="BG44">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH44">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI44">
         <v>3.35</v>
@@ -11794,7 +11794,7 @@
         <v>3.9</v>
       </c>
       <c r="BO44">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP44">
         <v>9.199999999999999</v>
@@ -11892,7 +11892,7 @@
         <v>1.56</v>
       </c>
       <c r="S45">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T45">
         <v>1.9</v>
@@ -11913,7 +11913,7 @@
         <v>10</v>
       </c>
       <c r="Z45">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA45">
         <v>13</v>
@@ -11931,7 +11931,7 @@
         <v>14.5</v>
       </c>
       <c r="AF45">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AG45">
         <v>30</v>
@@ -12006,7 +12006,7 @@
         <v>17</v>
       </c>
       <c r="BE45">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF45">
         <v>17.5</v>
@@ -12036,7 +12036,7 @@
         <v>11.5</v>
       </c>
       <c r="BO45">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP45">
         <v>70</v>
@@ -12048,22 +12048,22 @@
         <v>65</v>
       </c>
       <c r="BS45">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BT45">
         <v>4</v>
       </c>
       <c r="BU45">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV45">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BW45">
         <v>7.8</v>
       </c>
       <c r="BX45">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY45">
         <v>16.5</v>
@@ -12072,7 +12072,7 @@
         <v>14</v>
       </c>
       <c r="CA45">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB45" t="s">
         <v>279</v>
@@ -12098,10 +12098,10 @@
         <v>1.62</v>
       </c>
       <c r="G46">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I46">
         <v>6.6</v>
@@ -12125,25 +12125,25 @@
         <v>1.3</v>
       </c>
       <c r="P46">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q46">
         <v>1.85</v>
       </c>
       <c r="R46">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S46">
         <v>3.2</v>
       </c>
       <c r="T46">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U46">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W46">
         <v>2.56</v>
@@ -12152,13 +12152,13 @@
         <v>16.5</v>
       </c>
       <c r="Y46">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z46">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA46">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AB46">
         <v>8.800000000000001</v>
@@ -12167,13 +12167,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD46">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE46">
         <v>100</v>
       </c>
       <c r="AF46">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG46">
         <v>9.800000000000001</v>
@@ -12197,7 +12197,7 @@
         <v>130</v>
       </c>
       <c r="AN46">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO46">
         <v>110</v>
@@ -12206,25 +12206,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ46">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR46">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS46">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT46">
         <v>8.199999999999999</v>
       </c>
       <c r="AU46">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV46">
         <v>21</v>
       </c>
       <c r="AW46">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX46">
         <v>8.6</v>
@@ -12236,7 +12236,7 @@
         <v>19.5</v>
       </c>
       <c r="BA46">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB46">
         <v>13</v>
@@ -12248,25 +12248,25 @@
         <v>30</v>
       </c>
       <c r="BE46">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF46">
         <v>8</v>
       </c>
       <c r="BG46">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH46">
         <v>1000</v>
       </c>
       <c r="BI46">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ46">
         <v>1000</v>
       </c>
       <c r="BK46">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL46">
         <v>1000</v>
@@ -12278,7 +12278,7 @@
         <v>1000</v>
       </c>
       <c r="BO46">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP46">
         <v>1000</v>
@@ -12296,7 +12296,7 @@
         <v>1000</v>
       </c>
       <c r="BU46">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BV46">
         <v>1000</v>
@@ -12355,16 +12355,16 @@
         <v>2.9</v>
       </c>
       <c r="L47">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="M47">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N47">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="P47">
         <v>1.38</v>
@@ -12382,7 +12382,7 @@
         <v>2.66</v>
       </c>
       <c r="U47">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V47">
         <v>1.65</v>
@@ -12391,10 +12391,10 @@
         <v>1.33</v>
       </c>
       <c r="X47">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y47">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z47">
         <v>13</v>
@@ -12433,10 +12433,10 @@
         <v>90</v>
       </c>
       <c r="AL47">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AM47">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AN47">
         <v>160</v>
@@ -12451,10 +12451,10 @@
         <v>5.9</v>
       </c>
       <c r="AR47">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS47">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AT47">
         <v>8</v>
@@ -12472,37 +12472,37 @@
         <v>22</v>
       </c>
       <c r="AY47">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ47">
         <v>29</v>
       </c>
       <c r="BA47">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC47">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="BD47">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE47">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BF47">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG47">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH47">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BI47">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BJ47">
         <v>13.5</v>
@@ -12517,28 +12517,28 @@
         <v>21</v>
       </c>
       <c r="BN47">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO47">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP47">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ47">
         <v>32</v>
       </c>
       <c r="BR47">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS47">
         <v>21</v>
       </c>
       <c r="BT47">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU47">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV47">
         <v>26</v>
@@ -13807,7 +13807,7 @@
         <v>3.6</v>
       </c>
       <c r="L53">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M53">
         <v>1.07</v>
@@ -13816,7 +13816,7 @@
         <v>3.75</v>
       </c>
       <c r="O53">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P53">
         <v>1.92</v>
@@ -13828,10 +13828,10 @@
         <v>1.37</v>
       </c>
       <c r="S53">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T53">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U53">
         <v>2.16</v>
@@ -13879,7 +13879,7 @@
         <v>65</v>
       </c>
       <c r="AJ53">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK53">
         <v>24</v>
@@ -13903,13 +13903,13 @@
         <v>13.5</v>
       </c>
       <c r="AR53">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS53">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT53">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU53">
         <v>7</v>
@@ -13951,64 +13951,64 @@
         <v>10.5</v>
       </c>
       <c r="BH53">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI53">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="BJ53">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK53">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>1.1</v>
+        <v>13</v>
       </c>
       <c r="BN53">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO53">
-        <v>1.57</v>
+        <v>4.3</v>
       </c>
       <c r="BP53">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ53">
-        <v>2.18</v>
+        <v>11</v>
       </c>
       <c r="BR53">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS53">
-        <v>1.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT53">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU53">
-        <v>1.85</v>
+        <v>6.6</v>
       </c>
       <c r="BV53">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW53">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="BX53">
         <v>1000</v>
       </c>
       <c r="BY53">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="BZ53">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA53">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="CB53" t="s">
         <v>279</v>
@@ -14031,7 +14031,7 @@
         <v>256</v>
       </c>
       <c r="F54">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G54">
         <v>2.02</v>
@@ -14040,7 +14040,7 @@
         <v>4.4</v>
       </c>
       <c r="I54">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J54">
         <v>3.5</v>
@@ -14049,19 +14049,19 @@
         <v>3.6</v>
       </c>
       <c r="L54">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M54">
         <v>1.09</v>
       </c>
       <c r="N54">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O54">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P54">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q54">
         <v>2.16</v>
@@ -14073,10 +14073,10 @@
         <v>4.1</v>
       </c>
       <c r="T54">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U54">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
         <v>1.27</v>
@@ -14136,7 +14136,7 @@
         <v>17</v>
       </c>
       <c r="AO54">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP54">
         <v>10.5</v>
@@ -14169,7 +14169,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ54">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA54">
         <v>60</v>
@@ -14181,7 +14181,7 @@
         <v>20</v>
       </c>
       <c r="BD54">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE54">
         <v>14</v>
@@ -14196,13 +14196,13 @@
         <v>1000</v>
       </c>
       <c r="BI54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BJ54">
         <v>1000</v>
       </c>
       <c r="BK54">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="BL54">
         <v>1000</v>
@@ -14214,7 +14214,7 @@
         <v>1000</v>
       </c>
       <c r="BO54">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BP54">
         <v>1000</v>
@@ -14309,16 +14309,16 @@
         <v>2.26</v>
       </c>
       <c r="R55">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S55">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T55">
         <v>2.08</v>
       </c>
       <c r="U55">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V55">
         <v>1.18</v>
@@ -14339,7 +14339,7 @@
         <v>1000</v>
       </c>
       <c r="AB55">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC55">
         <v>12</v>
@@ -14351,10 +14351,10 @@
         <v>1000</v>
       </c>
       <c r="AF55">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AG55">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH55">
         <v>1000</v>
@@ -14381,64 +14381,64 @@
         <v>1000</v>
       </c>
       <c r="AP55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AQ55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AR55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AS55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AT55">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AU55">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AV55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AW55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AX55">
         <v>8.4</v>
       </c>
       <c r="AY55">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AZ55">
         <v>16</v>
       </c>
       <c r="BA55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="BB55">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="BC55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="BD55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="BE55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="BF55">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="BG55">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="BH55">
         <v>1000</v>
       </c>
       <c r="BI55">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ55">
         <v>1000</v>
@@ -14456,7 +14456,7 @@
         <v>1000</v>
       </c>
       <c r="BO55">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP55">
         <v>1000</v>
@@ -14757,22 +14757,22 @@
         <v>259</v>
       </c>
       <c r="F57">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="G57">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="H57">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I57">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J57">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K57">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -14787,16 +14787,16 @@
         <v>1.15</v>
       </c>
       <c r="P57">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>1.43</v>
       </c>
       <c r="R57">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S57">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="T57">
         <v>1.01</v>
@@ -14805,10 +14805,10 @@
         <v>1.01</v>
       </c>
       <c r="V57">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W57">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -15002,13 +15002,13 @@
         <v>1.1</v>
       </c>
       <c r="G58">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H58">
         <v>1.1</v>
       </c>
       <c r="I58">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J58">
         <v>1.1</v>
@@ -15244,13 +15244,13 @@
         <v>1.1</v>
       </c>
       <c r="G59">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H59">
         <v>1.1</v>
       </c>
       <c r="I59">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J59">
         <v>1.1</v>
@@ -15501,7 +15501,7 @@
         <v>3.9</v>
       </c>
       <c r="L60">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M60">
         <v>1.05</v>
@@ -15537,7 +15537,7 @@
         <v>1.9</v>
       </c>
       <c r="X60">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y60">
         <v>17</v>
@@ -15552,7 +15552,7 @@
         <v>11.5</v>
       </c>
       <c r="AC60">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD60">
         <v>16.5</v>
@@ -15597,10 +15597,10 @@
         <v>14.5</v>
       </c>
       <c r="AR60">
-        <v>25</v>
+        <v>8.4</v>
       </c>
       <c r="AS60">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT60">
         <v>10</v>
@@ -15624,19 +15624,19 @@
         <v>14.5</v>
       </c>
       <c r="BA60">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB60">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC60">
         <v>17.5</v>
       </c>
       <c r="BD60">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE60">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF60">
         <v>10.5</v>
@@ -15684,13 +15684,13 @@
         <v>9</v>
       </c>
       <c r="BU60">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV60">
         <v>38</v>
       </c>
       <c r="BW60">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX60">
         <v>48</v>
@@ -15728,16 +15728,16 @@
         <v>1.44</v>
       </c>
       <c r="G61">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H61">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I61">
         <v>8.4</v>
       </c>
       <c r="J61">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K61">
         <v>5.4</v>
@@ -15755,7 +15755,7 @@
         <v>1.17</v>
       </c>
       <c r="P61">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q61">
         <v>1.52</v>
@@ -15776,7 +15776,7 @@
         <v>1.13</v>
       </c>
       <c r="W61">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X61">
         <v>30</v>
@@ -15833,7 +15833,7 @@
         <v>85</v>
       </c>
       <c r="AP61">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AQ61">
         <v>32</v>
@@ -15884,13 +15884,13 @@
         <v>4.7</v>
       </c>
       <c r="BG61">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH61">
         <v>1000</v>
       </c>
       <c r="BI61">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ61">
         <v>1000</v>
@@ -15914,19 +15914,19 @@
         <v>1000</v>
       </c>
       <c r="BQ61">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR61">
         <v>1000</v>
       </c>
       <c r="BS61">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT61">
         <v>1000</v>
       </c>
       <c r="BU61">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV61">
         <v>1000</v>
@@ -16003,7 +16003,7 @@
         <v>2.14</v>
       </c>
       <c r="R62">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S62">
         <v>3.95</v>
@@ -16054,7 +16054,7 @@
         <v>19</v>
       </c>
       <c r="AI62">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ62">
         <v>60</v>
@@ -16069,7 +16069,7 @@
         <v>110</v>
       </c>
       <c r="AN62">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO62">
         <v>25</v>
@@ -16078,7 +16078,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ62">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR62">
         <v>14</v>
@@ -16087,7 +16087,7 @@
         <v>32</v>
       </c>
       <c r="AT62">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -16099,7 +16099,7 @@
         <v>26</v>
       </c>
       <c r="AX62">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY62">
         <v>12.5</v>
@@ -16111,19 +16111,19 @@
         <v>40</v>
       </c>
       <c r="BB62">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC62">
         <v>34</v>
       </c>
       <c r="BD62">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE62">
         <v>13.5</v>
       </c>
       <c r="BF62">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG62">
         <v>22</v>
@@ -16132,22 +16132,22 @@
         <v>3.55</v>
       </c>
       <c r="BI62">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="BJ62">
         <v>1000</v>
       </c>
       <c r="BK62">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BL62">
         <v>1000</v>
       </c>
       <c r="BM62">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BN62">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO62">
         <v>4.2</v>
@@ -16156,37 +16156,37 @@
         <v>1000</v>
       </c>
       <c r="BQ62">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BR62">
         <v>1000</v>
       </c>
       <c r="BS62">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BT62">
         <v>8.199999999999999</v>
       </c>
       <c r="BU62">
-        <v>1.91</v>
+        <v>3.85</v>
       </c>
       <c r="BV62">
         <v>1000</v>
       </c>
       <c r="BW62">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BX62">
         <v>1000</v>
       </c>
       <c r="BY62">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BZ62">
         <v>1000</v>
       </c>
       <c r="CA62">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="CB62" t="s">
         <v>279</v>
@@ -16212,13 +16212,13 @@
         <v>2.58</v>
       </c>
       <c r="G63">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H63">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I63">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J63">
         <v>3.85</v>
@@ -16227,28 +16227,28 @@
         <v>3.95</v>
       </c>
       <c r="L63">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M63">
         <v>1.04</v>
       </c>
       <c r="N63">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O63">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P63">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q63">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R63">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S63">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T63">
         <v>1.47</v>
@@ -16257,13 +16257,13 @@
         <v>2.98</v>
       </c>
       <c r="V63">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W63">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X63">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y63">
         <v>20</v>
@@ -16302,7 +16302,7 @@
         <v>38</v>
       </c>
       <c r="AK63">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL63">
         <v>28</v>
@@ -16317,7 +16317,7 @@
         <v>14</v>
       </c>
       <c r="AP63">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ63">
         <v>17.5</v>
@@ -16374,7 +16374,7 @@
         <v>1000</v>
       </c>
       <c r="BI63">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ63">
         <v>1000</v>
@@ -16398,7 +16398,7 @@
         <v>1000</v>
       </c>
       <c r="BQ63">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR63">
         <v>1000</v>
@@ -16475,7 +16475,7 @@
         <v>1.09</v>
       </c>
       <c r="N64">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O64">
         <v>1.41</v>
@@ -16634,7 +16634,7 @@
         <v>1000</v>
       </c>
       <c r="BO64">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP64">
         <v>1000</v>
@@ -16693,61 +16693,61 @@
         <v>267</v>
       </c>
       <c r="F65">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G65">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="H65">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I65">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J65">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K65">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L65">
         <v>1.01</v>
       </c>
       <c r="M65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P65">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q65">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R65">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S65">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T65">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U65">
         <v>1.68</v>
       </c>
       <c r="V65">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W65">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X65">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y65">
         <v>29</v>
@@ -16756,19 +16756,19 @@
         <v>110</v>
       </c>
       <c r="AA65">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="AB65">
         <v>7.4</v>
       </c>
       <c r="AC65">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD65">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE65">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AF65">
         <v>8</v>
@@ -16780,7 +16780,7 @@
         <v>34</v>
       </c>
       <c r="AI65">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AJ65">
         <v>13.5</v>
@@ -16795,16 +16795,16 @@
         <v>250</v>
       </c>
       <c r="AN65">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AO65">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AP65">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ65">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AR65">
         <v>1.03</v>
@@ -16813,10 +16813,10 @@
         <v>1.03</v>
       </c>
       <c r="AT65">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU65">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV65">
         <v>1.03</v>
@@ -16837,22 +16837,22 @@
         <v>1.03</v>
       </c>
       <c r="BB65">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC65">
         <v>13</v>
       </c>
       <c r="BD65">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE65">
         <v>1.03</v>
       </c>
       <c r="BF65">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG65">
-        <v>1.01</v>
+        <v>230</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16941,13 +16941,13 @@
         <v>2.3</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I66">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J66">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K66">
         <v>3.35</v>
@@ -16956,7 +16956,7 @@
         <v>1.51</v>
       </c>
       <c r="M66">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N66">
         <v>2.78</v>
@@ -16974,10 +16974,10 @@
         <v>1.22</v>
       </c>
       <c r="S66">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T66">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U66">
         <v>1.83</v>
@@ -16989,7 +16989,7 @@
         <v>1.77</v>
       </c>
       <c r="X66">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y66">
         <v>12</v>
@@ -17004,7 +17004,7 @@
         <v>7.6</v>
       </c>
       <c r="AC66">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD66">
         <v>19.5</v>
@@ -17052,10 +17052,10 @@
         <v>21</v>
       </c>
       <c r="AS66">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT66">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU66">
         <v>6.6</v>
@@ -17079,22 +17079,22 @@
         <v>9</v>
       </c>
       <c r="BB66">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC66">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD66">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE66">
         <v>9.4</v>
       </c>
       <c r="BF66">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG66">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -17180,7 +17180,7 @@
         <v>2.16</v>
       </c>
       <c r="G67">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="H67">
         <v>2.72</v>
@@ -17228,7 +17228,7 @@
         <v>1.28</v>
       </c>
       <c r="W67">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17703,10 +17703,10 @@
         <v>3.55</v>
       </c>
       <c r="T69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V69">
         <v>1.34</v>
@@ -17906,13 +17906,13 @@
         <v>2.3</v>
       </c>
       <c r="G70">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H70">
         <v>3.35</v>
       </c>
       <c r="I70">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J70">
         <v>3.35</v>
@@ -17933,13 +17933,13 @@
         <v>1.42</v>
       </c>
       <c r="P70">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q70">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R70">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S70">
         <v>4.1</v>
@@ -17951,10 +17951,10 @@
         <v>2</v>
       </c>
       <c r="V70">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W70">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X70">
         <v>12</v>
@@ -18032,7 +18032,7 @@
         <v>13</v>
       </c>
       <c r="AW70">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX70">
         <v>13</v>
@@ -18047,10 +18047,10 @@
         <v>8.4</v>
       </c>
       <c r="BB70">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC70">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD70">
         <v>7.8</v>
@@ -18387,16 +18387,16 @@
         <v>274</v>
       </c>
       <c r="F72">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G72">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H72">
         <v>6</v>
       </c>
       <c r="I72">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J72">
         <v>3.55</v>
@@ -18411,22 +18411,22 @@
         <v>1.1</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O72">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P72">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q72">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="R72">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S72">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T72">
         <v>2.18</v>
@@ -18435,10 +18435,10 @@
         <v>1.76</v>
       </c>
       <c r="V72">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W72">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X72">
         <v>11</v>
@@ -18447,7 +18447,7 @@
         <v>21</v>
       </c>
       <c r="Z72">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AA72">
         <v>260</v>
@@ -18456,7 +18456,7 @@
         <v>6.6</v>
       </c>
       <c r="AC72">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD72">
         <v>32</v>
@@ -18477,7 +18477,7 @@
         <v>150</v>
       </c>
       <c r="AJ72">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK72">
         <v>22</v>
@@ -18489,7 +18489,7 @@
         <v>240</v>
       </c>
       <c r="AN72">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO72">
         <v>240</v>
@@ -18501,10 +18501,10 @@
         <v>14.5</v>
       </c>
       <c r="AR72">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS72">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT72">
         <v>5.9</v>
@@ -18513,10 +18513,10 @@
         <v>7.4</v>
       </c>
       <c r="AV72">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW72">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX72">
         <v>8.199999999999999</v>
@@ -18528,25 +18528,25 @@
         <v>22</v>
       </c>
       <c r="BA72">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB72">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC72">
         <v>7.2</v>
       </c>
       <c r="BD72">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE72">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF72">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG72">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH72">
         <v>3.55</v>
@@ -18570,7 +18570,7 @@
         <v>1000</v>
       </c>
       <c r="BO72">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BP72">
         <v>1000</v>
@@ -18629,13 +18629,13 @@
         <v>275</v>
       </c>
       <c r="F73">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G73">
         <v>3.7</v>
       </c>
       <c r="H73">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="I73">
         <v>3.2</v>
@@ -18644,7 +18644,7 @@
         <v>2.74</v>
       </c>
       <c r="K73">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -19116,7 +19116,7 @@
         <v>2.9</v>
       </c>
       <c r="G75">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>2.26</v>
@@ -19143,7 +19143,7 @@
         <v>1.12</v>
       </c>
       <c r="P75">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q75">
         <v>1.38</v>
@@ -19161,13 +19161,13 @@
         <v>3.3</v>
       </c>
       <c r="V75">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W75">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X75">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Y75">
         <v>22</v>
@@ -19263,7 +19263,7 @@
         <v>17.5</v>
       </c>
       <c r="BD75">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE75">
         <v>23</v>
@@ -19278,7 +19278,7 @@
         <v>1000</v>
       </c>
       <c r="BI75">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BJ75">
         <v>1000</v>
@@ -19308,7 +19308,7 @@
         <v>1000</v>
       </c>
       <c r="BS75">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BT75">
         <v>1000</v>
@@ -19320,7 +19320,7 @@
         <v>1000</v>
       </c>
       <c r="BW75">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BX75">
         <v>1000</v>
@@ -19358,7 +19358,7 @@
         <v>3.45</v>
       </c>
       <c r="G76">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H76">
         <v>2.34</v>
@@ -19373,7 +19373,7 @@
         <v>3.45</v>
       </c>
       <c r="L76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M76">
         <v>1.09</v>
@@ -19424,7 +19424,7 @@
         <v>11.5</v>
       </c>
       <c r="AC76">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD76">
         <v>12</v>
@@ -19436,10 +19436,10 @@
         <v>25</v>
       </c>
       <c r="AG76">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH76">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI76">
         <v>48</v>
@@ -19463,7 +19463,7 @@
         <v>27</v>
       </c>
       <c r="AP76">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ76">
         <v>7.8</v>
@@ -19472,7 +19472,7 @@
         <v>12.5</v>
       </c>
       <c r="AS76">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT76">
         <v>10</v>
@@ -19490,13 +19490,13 @@
         <v>20</v>
       </c>
       <c r="AY76">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ76">
         <v>17</v>
       </c>
       <c r="BA76">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB76">
         <v>10</v>
@@ -19511,7 +19511,7 @@
         <v>10.5</v>
       </c>
       <c r="BF76">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG76">
         <v>19.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-27.xlsx
@@ -853,7 +853,7 @@
     <t>Tolima</t>
   </si>
   <si>
-    <t>2026-09-26 03:27:52</t>
+    <t>2026-09-26 05:47:07</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1456,7 @@
         <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1465,7 +1465,7 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1489,7 +1489,7 @@
         <v>2.48</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U2">
         <v>2.72</v>
@@ -1555,7 +1555,7 @@
         <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AQ2">
         <v>16</v>
@@ -1591,7 +1591,7 @@
         <v>27</v>
       </c>
       <c r="BB2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
@@ -1600,7 +1600,7 @@
         <v>23</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
@@ -1615,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK2">
         <v>7.4</v>
@@ -1627,7 +1627,7 @@
         <v>50</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO2">
         <v>5.1</v>
@@ -1645,7 +1645,7 @@
         <v>17.5</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU2">
         <v>5.9</v>
@@ -1654,13 +1654,13 @@
         <v>24</v>
       </c>
       <c r="BW2">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BZ2">
         <v>18</v>
@@ -1689,13 +1689,13 @@
         <v>205</v>
       </c>
       <c r="F3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>7.6</v>
@@ -1719,28 +1719,28 @@
         <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q3">
         <v>1.53</v>
       </c>
       <c r="R3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T3">
         <v>1.71</v>
       </c>
       <c r="U3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V3">
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X3">
         <v>30</v>
@@ -1749,13 +1749,13 @@
         <v>34</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC3">
         <v>13</v>
@@ -1764,7 +1764,7 @@
         <v>27</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF3">
         <v>11</v>
@@ -1776,7 +1776,7 @@
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
         <v>14.5</v>
@@ -1791,7 +1791,7 @@
         <v>85</v>
       </c>
       <c r="AN3">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO3">
         <v>70</v>
@@ -1824,7 +1824,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
         <v>18</v>
@@ -1836,7 +1836,7 @@
         <v>12.5</v>
       </c>
       <c r="BC3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD3">
         <v>23</v>
@@ -1845,49 +1845,49 @@
         <v>60</v>
       </c>
       <c r="BF3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG3">
         <v>55</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BI3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="BN3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
         <v>20</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="BT3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU3">
         <v>9.199999999999999</v>
@@ -1896,19 +1896,19 @@
         <v>55</v>
       </c>
       <c r="BW3">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BZ3">
         <v>11.5</v>
       </c>
       <c r="CA3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>279</v>
@@ -1934,7 +1934,7 @@
         <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
         <v>3.05</v>
@@ -1964,7 +1964,7 @@
         <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R4">
         <v>1.56</v>
@@ -1979,10 +1979,10 @@
         <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>22</v>
@@ -2030,7 +2030,7 @@
         <v>30</v>
       </c>
       <c r="AM4">
-        <v>650</v>
+        <v>90</v>
       </c>
       <c r="AN4">
         <v>14</v>
@@ -2048,7 +2048,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AT4">
         <v>12.5</v>
@@ -2072,7 +2072,7 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB4">
         <v>27</v>
@@ -2081,10 +2081,10 @@
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE4">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BF4">
         <v>12</v>
@@ -2093,64 +2093,64 @@
         <v>17.5</v>
       </c>
       <c r="BH4">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
+        <v>4.4</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>10</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
         <v>5</v>
       </c>
-      <c r="BP4">
-        <v>16</v>
-      </c>
-      <c r="BQ4">
-        <v>13.5</v>
-      </c>
-      <c r="BR4">
-        <v>27</v>
-      </c>
-      <c r="BS4">
-        <v>19.5</v>
-      </c>
-      <c r="BT4">
-        <v>6.4</v>
-      </c>
-      <c r="BU4">
-        <v>5.8</v>
-      </c>
       <c r="BV4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>279</v>
@@ -2173,10 +2173,10 @@
         <v>207</v>
       </c>
       <c r="F5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
         <v>5.7</v>
@@ -2185,10 +2185,10 @@
         <v>6.2</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -2206,7 +2206,7 @@
         <v>2.46</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
         <v>1.57</v>
@@ -2218,16 +2218,16 @@
         <v>1.75</v>
       </c>
       <c r="U5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
         <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5">
         <v>25</v>
@@ -2257,7 +2257,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>65</v>
@@ -2266,10 +2266,10 @@
         <v>16</v>
       </c>
       <c r="AK5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM5">
         <v>85</v>
@@ -2284,25 +2284,25 @@
         <v>20</v>
       </c>
       <c r="AQ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS5">
         <v>44</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX5">
         <v>10</v>
@@ -2314,43 +2314,43 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC5">
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BE5">
         <v>36</v>
       </c>
       <c r="BF5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BN5">
         <v>5.4</v>
@@ -2362,13 +2362,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="BT5">
         <v>1000</v>
@@ -2380,19 +2380,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="CB5" t="s">
         <v>279</v>
@@ -2418,13 +2418,13 @@
         <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H6">
         <v>2.84</v>
       </c>
       <c r="I6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -2445,10 +2445,10 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R6">
         <v>1.59</v>
@@ -2463,16 +2463,16 @@
         <v>2.66</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X6">
         <v>23</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z6">
         <v>23</v>
@@ -2535,7 +2535,7 @@
         <v>36</v>
       </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU6">
         <v>8.199999999999999</v>
@@ -2556,7 +2556,7 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB6">
         <v>30</v>
@@ -2565,76 +2565,76 @@
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE6">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BF6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>279</v>
@@ -2666,13 +2666,13 @@
         <v>3.55</v>
       </c>
       <c r="I7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J7">
         <v>3.45</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.38</v>
@@ -2705,7 +2705,7 @@
         <v>2.14</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
         <v>1.79</v>
@@ -2735,7 +2735,7 @@
         <v>55</v>
       </c>
       <c r="AF7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
         <v>11</v>
@@ -2771,10 +2771,10 @@
         <v>12</v>
       </c>
       <c r="AR7">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS7">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="AT7">
         <v>8.6</v>
@@ -2786,7 +2786,7 @@
         <v>13.5</v>
       </c>
       <c r="AW7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
@@ -2798,25 +2798,25 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BB7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC7">
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BE7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
         <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2902,10 +2902,10 @@
         <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I8">
         <v>3.35</v>
@@ -2932,7 +2932,7 @@
         <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R8">
         <v>1.4</v>
@@ -2941,7 +2941,7 @@
         <v>3.3</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U8">
         <v>2.24</v>
@@ -2950,7 +2950,7 @@
         <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X8">
         <v>18.5</v>
@@ -3001,7 +3001,7 @@
         <v>100</v>
       </c>
       <c r="AN8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AO8">
         <v>40</v>
@@ -3016,7 +3016,7 @@
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT8">
         <v>9.800000000000001</v>
@@ -3028,7 +3028,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX8">
         <v>14</v>
@@ -3040,7 +3040,7 @@
         <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB8">
         <v>22</v>
@@ -3052,13 +3052,13 @@
         <v>26</v>
       </c>
       <c r="BE8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF8">
         <v>16</v>
       </c>
       <c r="BG8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3234,7 +3234,7 @@
         <v>38</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL9">
         <v>30</v>
@@ -3392,10 +3392,10 @@
         <v>2.22</v>
       </c>
       <c r="I10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
         <v>3.8</v>
@@ -3407,31 +3407,31 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>1.3</v>
       </c>
       <c r="P10">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q10">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
         <v>1.4</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
         <v>1.69</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W10">
         <v>1.38</v>
@@ -3449,7 +3449,7 @@
         <v>34</v>
       </c>
       <c r="AB10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10">
         <v>8.800000000000001</v>
@@ -3461,10 +3461,10 @@
         <v>28</v>
       </c>
       <c r="AF10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH10">
         <v>17.5</v>
@@ -3527,31 +3527,31 @@
         <v>24</v>
       </c>
       <c r="BB10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD10">
         <v>30</v>
       </c>
       <c r="BE10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG10">
         <v>12.5</v>
       </c>
       <c r="BH10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI10">
         <v>2.92</v>
       </c>
       <c r="BJ10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
         <v>7.2</v>
@@ -3566,13 +3566,13 @@
         <v>7.6</v>
       </c>
       <c r="BO10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BR10">
         <v>42</v>
@@ -3581,10 +3581,10 @@
         <v>27</v>
       </c>
       <c r="BT10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV10">
         <v>19</v>
@@ -3625,19 +3625,19 @@
         <v>213</v>
       </c>
       <c r="F11">
+        <v>1.27</v>
+      </c>
+      <c r="G11">
         <v>1.29</v>
-      </c>
-      <c r="G11">
-        <v>1.3</v>
       </c>
       <c r="H11">
         <v>11.5</v>
       </c>
       <c r="I11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>7.4</v>
@@ -3676,10 +3676,10 @@
         <v>1.08</v>
       </c>
       <c r="W11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y11">
         <v>48</v>
@@ -3694,13 +3694,13 @@
         <v>13</v>
       </c>
       <c r="AC11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD11">
         <v>42</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF11">
         <v>9.6</v>
@@ -3709,7 +3709,7 @@
         <v>11</v>
       </c>
       <c r="AH11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI11">
         <v>130</v>
@@ -3718,31 +3718,31 @@
         <v>10</v>
       </c>
       <c r="AK11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM11">
         <v>130</v>
       </c>
       <c r="AN11">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AO11">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP11">
         <v>30</v>
       </c>
       <c r="AQ11">
+        <v>44</v>
+      </c>
+      <c r="AR11">
         <v>38</v>
       </c>
-      <c r="AR11">
-        <v>85</v>
-      </c>
       <c r="AS11">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT11">
         <v>11.5</v>
@@ -3751,7 +3751,7 @@
         <v>14.5</v>
       </c>
       <c r="AV11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AW11">
         <v>44</v>
@@ -3763,13 +3763,13 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA11">
         <v>40</v>
       </c>
       <c r="BB11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC11">
         <v>12</v>
@@ -3867,7 +3867,7 @@
         <v>214</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G12">
         <v>2.08</v>
@@ -3876,19 +3876,19 @@
         <v>3.6</v>
       </c>
       <c r="I12">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J12">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.25</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>7.4</v>
@@ -3897,22 +3897,22 @@
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R12">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U12">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V12">
         <v>1.36</v>
@@ -3921,10 +3921,10 @@
         <v>1.92</v>
       </c>
       <c r="X12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z12">
         <v>38</v>
@@ -3933,10 +3933,10 @@
         <v>80</v>
       </c>
       <c r="AB12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
         <v>16.5</v>
@@ -3945,16 +3945,16 @@
         <v>36</v>
       </c>
       <c r="AF12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12">
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>18.5</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12">
         <v>42</v>
@@ -3972,31 +3972,31 @@
         <v>7.8</v>
       </c>
       <c r="AO12">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AQ12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS12">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AT12">
         <v>16</v>
       </c>
       <c r="AU12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX12">
         <v>16.5</v>
@@ -4008,10 +4008,10 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC12">
         <v>16</v>
@@ -4020,19 +4020,19 @@
         <v>20</v>
       </c>
       <c r="BE12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH12">
         <v>5.2</v>
       </c>
       <c r="BI12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ12">
         <v>8.4</v>
@@ -4041,28 +4041,28 @@
         <v>7.4</v>
       </c>
       <c r="BL12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BN12">
         <v>5.6</v>
       </c>
       <c r="BO12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP12">
         <v>13</v>
       </c>
       <c r="BQ12">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BR12">
         <v>19</v>
       </c>
       <c r="BS12">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BT12">
         <v>7.6</v>
@@ -4077,16 +4077,16 @@
         <v>17</v>
       </c>
       <c r="BX12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY12">
         <v>19</v>
       </c>
       <c r="BZ12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="s">
         <v>279</v>
@@ -4118,7 +4118,7 @@
         <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J13">
         <v>4.1</v>
@@ -4139,16 +4139,16 @@
         <v>1.2</v>
       </c>
       <c r="P13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R13">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S13">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T13">
         <v>1.55</v>
@@ -4157,7 +4157,7 @@
         <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W13">
         <v>1.76</v>
@@ -4166,7 +4166,7 @@
         <v>25</v>
       </c>
       <c r="Y13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z13">
         <v>26</v>
@@ -4181,7 +4181,7 @@
         <v>9.6</v>
       </c>
       <c r="AD13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE13">
         <v>30</v>
@@ -4217,7 +4217,7 @@
         <v>19.5</v>
       </c>
       <c r="AP13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ13">
         <v>16.5</v>
@@ -4351,7 +4351,7 @@
         <v>216</v>
       </c>
       <c r="F14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G14">
         <v>3.4</v>
@@ -4402,7 +4402,7 @@
         <v>1.79</v>
       </c>
       <c r="W14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X14">
         <v>25</v>
@@ -4429,7 +4429,7 @@
         <v>22</v>
       </c>
       <c r="AF14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG14">
         <v>14.5</v>
@@ -4438,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="AI14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ14">
         <v>60</v>
@@ -4447,10 +4447,10 @@
         <v>36</v>
       </c>
       <c r="AL14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN14">
         <v>23</v>
@@ -4480,7 +4480,7 @@
         <v>10</v>
       </c>
       <c r="AW14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX14">
         <v>20</v>
@@ -4492,19 +4492,19 @@
         <v>13</v>
       </c>
       <c r="BA14">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BB14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC14">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BD14">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BE14">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BF14">
         <v>17.5</v>
@@ -4593,7 +4593,7 @@
         <v>217</v>
       </c>
       <c r="F15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G15">
         <v>1.65</v>
@@ -4602,7 +4602,7 @@
         <v>5.6</v>
       </c>
       <c r="I15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>4.5</v>
@@ -4632,7 +4632,7 @@
         <v>1.49</v>
       </c>
       <c r="S15">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T15">
         <v>1.83</v>
@@ -4647,7 +4647,7 @@
         <v>2.52</v>
       </c>
       <c r="X15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y15">
         <v>22</v>
@@ -4704,10 +4704,10 @@
         <v>17.5</v>
       </c>
       <c r="AQ15">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="AR15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS15">
         <v>13</v>
@@ -4722,7 +4722,7 @@
         <v>19</v>
       </c>
       <c r="AW15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX15">
         <v>9.199999999999999</v>
@@ -4731,10 +4731,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BA15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB15">
         <v>13.5</v>
@@ -4743,7 +4743,7 @@
         <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE15">
         <v>12.5</v>
@@ -4752,67 +4752,67 @@
         <v>7</v>
       </c>
       <c r="BG15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH15">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BJ15">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>279</v>
@@ -4844,7 +4844,7 @@
         <v>2.64</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>3.65</v>
@@ -4859,7 +4859,7 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O16">
         <v>1.19</v>
@@ -4883,7 +4883,7 @@
         <v>2.42</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.62</v>
@@ -4943,37 +4943,37 @@
         <v>21</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS16">
         <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA16">
         <v>1.03</v>
@@ -4982,7 +4982,7 @@
         <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD16">
         <v>1.03</v>
@@ -5239,7 +5239,7 @@
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
         <v>2.68</v>
@@ -5248,55 +5248,55 @@
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>279</v>
@@ -5567,16 +5567,16 @@
         <v>2.6</v>
       </c>
       <c r="H19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I19">
         <v>3.45</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L19">
         <v>1.52</v>
@@ -5591,7 +5591,7 @@
         <v>1.52</v>
       </c>
       <c r="P19">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5609,7 +5609,7 @@
         <v>1.79</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
         <v>1.62</v>
@@ -5803,7 +5803,7 @@
         <v>222</v>
       </c>
       <c r="F20">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G20">
         <v>2.18</v>
@@ -5815,19 +5815,19 @@
         <v>4.7</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L20">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O20">
         <v>1.01</v>
@@ -5836,13 +5836,13 @@
         <v>1.98</v>
       </c>
       <c r="Q20">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="R20">
         <v>1.37</v>
       </c>
       <c r="S20">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -6084,7 +6084,7 @@
         <v>1.55</v>
       </c>
       <c r="S21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -6305,13 +6305,13 @@
         <v>3.6</v>
       </c>
       <c r="L22">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M22">
         <v>1.07</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O22">
         <v>1.31</v>
@@ -6320,13 +6320,13 @@
         <v>2</v>
       </c>
       <c r="Q22">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T22">
         <v>1.75</v>
@@ -6401,7 +6401,7 @@
         <v>12</v>
       </c>
       <c r="AR22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS22">
         <v>44</v>
@@ -6437,7 +6437,7 @@
         <v>23</v>
       </c>
       <c r="BD22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE22">
         <v>12.5</v>
@@ -6529,19 +6529,19 @@
         <v>225</v>
       </c>
       <c r="F23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="G23">
         <v>110</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="I23">
         <v>110</v>
       </c>
       <c r="J23">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="K23">
         <v>930</v>
@@ -6577,10 +6577,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6774,13 +6774,13 @@
         <v>1.1</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H24">
         <v>1.1</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J24">
         <v>1.1</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -7013,22 +7013,22 @@
         <v>227</v>
       </c>
       <c r="F25">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G25">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="I25">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="J25">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="K25">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -7046,13 +7046,13 @@
         <v>3.55</v>
       </c>
       <c r="Q25">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="T25">
         <v>1.29</v>
@@ -7061,7 +7061,7 @@
         <v>3.2</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.83</v>
@@ -7500,13 +7500,13 @@
         <v>1.1</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H27">
         <v>1.1</v>
       </c>
       <c r="I27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J27">
         <v>1.1</v>
@@ -7545,10 +7545,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7742,13 +7742,13 @@
         <v>1.1</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H28">
         <v>1.1</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J28">
         <v>1.1</v>
@@ -7787,10 +7787,10 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7984,13 +7984,13 @@
         <v>1.1</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H29">
         <v>1.1</v>
       </c>
       <c r="I29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J29">
         <v>1.12</v>
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -8223,10 +8223,10 @@
         <v>232</v>
       </c>
       <c r="F30">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H30">
         <v>1.1</v>
@@ -8235,7 +8235,7 @@
         <v>110</v>
       </c>
       <c r="J30">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K30">
         <v>930</v>
@@ -8271,10 +8271,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8468,13 +8468,13 @@
         <v>1.1</v>
       </c>
       <c r="G31">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H31">
         <v>1.1</v>
       </c>
       <c r="I31">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J31">
         <v>1.1</v>
@@ -8513,10 +8513,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8707,7 +8707,7 @@
         <v>234</v>
       </c>
       <c r="F32">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="G32">
         <v>110</v>
@@ -8719,7 +8719,7 @@
         <v>110</v>
       </c>
       <c r="J32">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="K32">
         <v>920</v>
@@ -8755,10 +8755,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8952,22 +8952,22 @@
         <v>2.52</v>
       </c>
       <c r="G33">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H33">
         <v>3.25</v>
       </c>
       <c r="I33">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J33">
         <v>3.15</v>
       </c>
       <c r="K33">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M33">
         <v>1.12</v>
@@ -8982,22 +8982,22 @@
         <v>1.59</v>
       </c>
       <c r="Q33">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S33">
         <v>5.3</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U33">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V33">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
         <v>1.6</v>
@@ -9033,7 +9033,7 @@
         <v>13</v>
       </c>
       <c r="AH33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI33">
         <v>85</v>
@@ -9057,7 +9057,7 @@
         <v>70</v>
       </c>
       <c r="AP33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ33">
         <v>8.4</v>
@@ -9087,7 +9087,7 @@
         <v>11</v>
       </c>
       <c r="AZ33">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BA33">
         <v>10</v>
@@ -9111,10 +9111,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH33">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI33">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ33">
         <v>11.5</v>
@@ -9194,13 +9194,13 @@
         <v>1.1</v>
       </c>
       <c r="G34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H34">
         <v>1.1</v>
       </c>
       <c r="I34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J34">
         <v>1.1</v>
@@ -9239,10 +9239,10 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9436,13 +9436,13 @@
         <v>1.1</v>
       </c>
       <c r="G35">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H35">
         <v>1.1</v>
       </c>
       <c r="I35">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J35">
         <v>1.1</v>
@@ -9481,10 +9481,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9675,37 +9675,37 @@
         <v>238</v>
       </c>
       <c r="F36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G36">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H36">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I36">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J36">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K36">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L36">
         <v>1.44</v>
       </c>
       <c r="M36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O36">
         <v>1.41</v>
       </c>
       <c r="P36">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9714,22 +9714,22 @@
         <v>1.21</v>
       </c>
       <c r="S36">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T36">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U36">
         <v>1.8</v>
       </c>
       <c r="V36">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X36">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y36">
         <v>970</v>
@@ -9783,7 +9783,7 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.48</v>
+        <v>7.4</v>
       </c>
       <c r="AQ36">
         <v>5.9</v>
@@ -9792,49 +9792,49 @@
         <v>7.2</v>
       </c>
       <c r="AS36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AT36">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AU36">
         <v>5.6</v>
       </c>
       <c r="AV36">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AW36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AX36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AY36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AZ36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BA36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BB36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BC36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BD36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BE36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BF36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BG36">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -10404,13 +10404,13 @@
         <v>1.1</v>
       </c>
       <c r="G39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H39">
         <v>1.1</v>
       </c>
       <c r="I39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J39">
         <v>1.12</v>
@@ -10449,10 +10449,10 @@
         <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10646,13 +10646,13 @@
         <v>1.1</v>
       </c>
       <c r="G40">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H40">
         <v>1.1</v>
       </c>
       <c r="I40">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J40">
         <v>1.12</v>
@@ -10691,10 +10691,10 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10888,13 +10888,13 @@
         <v>1.1</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H41">
         <v>1.1</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J41">
         <v>1.12</v>
@@ -10933,10 +10933,10 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -11127,10 +11127,10 @@
         <v>244</v>
       </c>
       <c r="F42">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G42">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H42">
         <v>5.6</v>
@@ -11142,7 +11142,7 @@
         <v>3.4</v>
       </c>
       <c r="K42">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L42">
         <v>1.42</v>
@@ -11157,7 +11157,7 @@
         <v>1.36</v>
       </c>
       <c r="P42">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q42">
         <v>2.04</v>
@@ -11166,10 +11166,10 @@
         <v>1.29</v>
       </c>
       <c r="S42">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T42">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U42">
         <v>1.77</v>
@@ -11178,7 +11178,7 @@
         <v>1.17</v>
       </c>
       <c r="W42">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="X42">
         <v>26</v>
@@ -11235,7 +11235,7 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ42">
         <v>10</v>
@@ -11274,7 +11274,7 @@
         <v>10.5</v>
       </c>
       <c r="BC42">
-        <v>1.63</v>
+        <v>11.5</v>
       </c>
       <c r="BD42">
         <v>1.63</v>
@@ -11399,13 +11399,13 @@
         <v>1.33</v>
       </c>
       <c r="P43">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q43">
         <v>1.99</v>
       </c>
       <c r="R43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S43">
         <v>3.5</v>
@@ -11414,7 +11414,7 @@
         <v>1.79</v>
       </c>
       <c r="U43">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V43">
         <v>1.32</v>
@@ -11611,10 +11611,10 @@
         <v>246</v>
       </c>
       <c r="F44">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G44">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H44">
         <v>7.8</v>
@@ -11623,16 +11623,16 @@
         <v>8</v>
       </c>
       <c r="J44">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K44">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M44">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N44">
         <v>4.3</v>
@@ -11641,7 +11641,7 @@
         <v>1.28</v>
       </c>
       <c r="P44">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q44">
         <v>1.82</v>
@@ -11662,7 +11662,7 @@
         <v>1.14</v>
       </c>
       <c r="W44">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X44">
         <v>18</v>
@@ -11674,7 +11674,7 @@
         <v>70</v>
       </c>
       <c r="AA44">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB44">
         <v>8.6</v>
@@ -11719,7 +11719,7 @@
         <v>160</v>
       </c>
       <c r="AP44">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ44">
         <v>22</v>
@@ -11853,16 +11853,16 @@
         <v>247</v>
       </c>
       <c r="F45">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G45">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H45">
+        <v>1.45</v>
+      </c>
+      <c r="I45">
         <v>1.46</v>
-      </c>
-      <c r="I45">
-        <v>1.47</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -11871,7 +11871,7 @@
         <v>5.2</v>
       </c>
       <c r="L45">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M45">
         <v>1.04</v>
@@ -11886,13 +11886,13 @@
         <v>2.44</v>
       </c>
       <c r="Q45">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R45">
         <v>1.56</v>
       </c>
       <c r="S45">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T45">
         <v>1.9</v>
@@ -11901,10 +11901,10 @@
         <v>2.04</v>
       </c>
       <c r="V45">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
         <v>22</v>
@@ -11913,13 +11913,13 @@
         <v>10</v>
       </c>
       <c r="Z45">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA45">
         <v>13</v>
       </c>
       <c r="AB45">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC45">
         <v>11.5</v>
@@ -11931,10 +11931,10 @@
         <v>14.5</v>
       </c>
       <c r="AF45">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AG45">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH45">
         <v>23</v>
@@ -11943,10 +11943,10 @@
         <v>34</v>
       </c>
       <c r="AJ45">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AK45">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL45">
         <v>100</v>
@@ -11958,7 +11958,7 @@
         <v>120</v>
       </c>
       <c r="AO45">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP45">
         <v>19</v>
@@ -11997,82 +11997,82 @@
         <v>27</v>
       </c>
       <c r="BB45">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC45">
         <v>17</v>
       </c>
       <c r="BD45">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="BE45">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BF45">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG45">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH45">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI45">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BJ45">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK45">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL45">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM45">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO45">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BP45">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BQ45">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BR45">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS45">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BT45">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BU45">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BV45">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BW45">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BX45">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY45">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA45">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB45" t="s">
         <v>279</v>
@@ -12095,25 +12095,25 @@
         <v>248</v>
       </c>
       <c r="F46">
+        <v>1.61</v>
+      </c>
+      <c r="G46">
         <v>1.62</v>
-      </c>
-      <c r="G46">
-        <v>1.63</v>
       </c>
       <c r="H46">
         <v>6.2</v>
       </c>
       <c r="I46">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J46">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K46">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L46">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M46">
         <v>1.06</v>
@@ -12125,28 +12125,28 @@
         <v>1.3</v>
       </c>
       <c r="P46">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q46">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R46">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S46">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T46">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U46">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V46">
         <v>1.18</v>
       </c>
       <c r="W46">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X46">
         <v>16.5</v>
@@ -12164,13 +12164,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC46">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD46">
         <v>25</v>
       </c>
       <c r="AE46">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF46">
         <v>9.4</v>
@@ -12197,7 +12197,7 @@
         <v>130</v>
       </c>
       <c r="AN46">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO46">
         <v>110</v>
@@ -12212,7 +12212,7 @@
         <v>46</v>
       </c>
       <c r="AS46">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT46">
         <v>8.199999999999999</v>
@@ -12224,19 +12224,19 @@
         <v>21</v>
       </c>
       <c r="AW46">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX46">
         <v>8.6</v>
       </c>
       <c r="AY46">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ46">
         <v>19.5</v>
       </c>
       <c r="BA46">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB46">
         <v>13</v>
@@ -12248,13 +12248,13 @@
         <v>30</v>
       </c>
       <c r="BE46">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF46">
         <v>8</v>
       </c>
       <c r="BG46">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12343,121 +12343,121 @@
         <v>4</v>
       </c>
       <c r="H47">
+        <v>2.46</v>
+      </c>
+      <c r="I47">
         <v>2.5</v>
       </c>
-      <c r="I47">
-        <v>2.52</v>
-      </c>
       <c r="J47">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K47">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="L47">
+        <v>1.66</v>
+      </c>
+      <c r="M47">
+        <v>1.16</v>
+      </c>
+      <c r="N47">
+        <v>2.2</v>
+      </c>
+      <c r="O47">
         <v>1.75</v>
       </c>
-      <c r="M47">
-        <v>1.19</v>
-      </c>
-      <c r="N47">
-        <v>2.1</v>
-      </c>
-      <c r="O47">
-        <v>1.8</v>
-      </c>
       <c r="P47">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R47">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S47">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="T47">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="U47">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V47">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W47">
         <v>1.33</v>
       </c>
       <c r="X47">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="Y47">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z47">
         <v>13</v>
       </c>
       <c r="AA47">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB47">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC47">
         <v>7.4</v>
       </c>
       <c r="AD47">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE47">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF47">
         <v>26</v>
       </c>
       <c r="AG47">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH47">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI47">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ47">
         <v>100</v>
       </c>
       <c r="AK47">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL47">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM47">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AN47">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AO47">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP47">
+        <v>6</v>
+      </c>
+      <c r="AQ47">
         <v>5.8</v>
-      </c>
-      <c r="AQ47">
-        <v>5.9</v>
       </c>
       <c r="AR47">
         <v>12</v>
       </c>
       <c r="AS47">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="AT47">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU47">
         <v>6.6</v>
@@ -12466,49 +12466,49 @@
         <v>12.5</v>
       </c>
       <c r="AW47">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX47">
         <v>22</v>
       </c>
       <c r="AY47">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ47">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA47">
+        <v>16</v>
+      </c>
+      <c r="BB47">
+        <v>16</v>
+      </c>
+      <c r="BC47">
         <v>15.5</v>
       </c>
-      <c r="BB47">
-        <v>15</v>
-      </c>
-      <c r="BC47">
-        <v>75</v>
-      </c>
       <c r="BD47">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE47">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF47">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG47">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BH47">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BI47">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ47">
         <v>13.5</v>
       </c>
       <c r="BK47">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BL47">
         <v>1000</v>
@@ -12529,7 +12529,7 @@
         <v>32</v>
       </c>
       <c r="BR47">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BS47">
         <v>21</v>
@@ -12541,19 +12541,19 @@
         <v>4.5</v>
       </c>
       <c r="BV47">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW47">
         <v>18.5</v>
       </c>
       <c r="BX47">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY47">
         <v>44</v>
       </c>
       <c r="BZ47">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="CA47">
         <v>21</v>
@@ -12582,13 +12582,13 @@
         <v>1.1</v>
       </c>
       <c r="G48">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H48">
         <v>1.1</v>
       </c>
       <c r="I48">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J48">
         <v>1.1</v>
@@ -12627,10 +12627,10 @@
         <v>1.01</v>
       </c>
       <c r="V48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
         <v>1000</v>
@@ -12824,13 +12824,13 @@
         <v>1.1</v>
       </c>
       <c r="G49">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H49">
         <v>1.1</v>
       </c>
       <c r="I49">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J49">
         <v>1.1</v>
@@ -12869,10 +12869,10 @@
         <v>1.01</v>
       </c>
       <c r="V49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
         <v>1000</v>
@@ -13072,7 +13072,7 @@
         <v>1.1</v>
       </c>
       <c r="I50">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J50">
         <v>1.1</v>
@@ -13111,10 +13111,10 @@
         <v>1.01</v>
       </c>
       <c r="V50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
         <v>1000</v>
@@ -13547,10 +13547,10 @@
         <v>254</v>
       </c>
       <c r="F52">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G52">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="H52">
         <v>1.12</v>
@@ -13559,7 +13559,7 @@
         <v>110</v>
       </c>
       <c r="J52">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="K52">
         <v>830</v>
@@ -13595,10 +13595,10 @@
         <v>1.01</v>
       </c>
       <c r="V52">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
         <v>1000</v>
@@ -13798,10 +13798,10 @@
         <v>4.2</v>
       </c>
       <c r="I53">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J53">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K53">
         <v>3.6</v>
@@ -13813,7 +13813,7 @@
         <v>1.07</v>
       </c>
       <c r="N53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O53">
         <v>1.33</v>
@@ -13879,7 +13879,7 @@
         <v>65</v>
       </c>
       <c r="AJ53">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK53">
         <v>24</v>
@@ -13978,7 +13978,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ53">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BR53">
         <v>30</v>
@@ -14031,7 +14031,7 @@
         <v>256</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G54">
         <v>2.02</v>
@@ -14040,7 +14040,7 @@
         <v>4.4</v>
       </c>
       <c r="I54">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J54">
         <v>3.5</v>
@@ -14055,7 +14055,7 @@
         <v>1.09</v>
       </c>
       <c r="N54">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O54">
         <v>1.39</v>
@@ -14076,7 +14076,7 @@
         <v>1.95</v>
       </c>
       <c r="U54">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V54">
         <v>1.27</v>
@@ -14136,7 +14136,7 @@
         <v>17</v>
       </c>
       <c r="AO54">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP54">
         <v>10.5</v>
@@ -14169,7 +14169,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ54">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA54">
         <v>60</v>
@@ -14196,37 +14196,37 @@
         <v>1000</v>
       </c>
       <c r="BI54">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BJ54">
         <v>1000</v>
       </c>
       <c r="BK54">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BL54">
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BN54">
         <v>1000</v>
       </c>
       <c r="BO54">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="BP54">
         <v>1000</v>
       </c>
       <c r="BQ54">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BR54">
         <v>1000</v>
       </c>
       <c r="BS54">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BT54">
         <v>1000</v>
@@ -14238,19 +14238,19 @@
         <v>1000</v>
       </c>
       <c r="BW54">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BX54">
         <v>1000</v>
       </c>
       <c r="BY54">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BZ54">
         <v>1000</v>
       </c>
       <c r="CA54">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="CB54" t="s">
         <v>279</v>
@@ -14285,10 +14285,10 @@
         <v>6.6</v>
       </c>
       <c r="J55">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K55">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14318,7 +14318,7 @@
         <v>2.08</v>
       </c>
       <c r="U55">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V55">
         <v>1.18</v>
@@ -14327,7 +14327,7 @@
         <v>2.12</v>
       </c>
       <c r="X55">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y55">
         <v>1000</v>
@@ -14339,7 +14339,7 @@
         <v>1000</v>
       </c>
       <c r="AB55">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC55">
         <v>12</v>
@@ -14351,10 +14351,10 @@
         <v>1000</v>
       </c>
       <c r="AF55">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AG55">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH55">
         <v>1000</v>
@@ -14363,7 +14363,7 @@
         <v>1000</v>
       </c>
       <c r="AJ55">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK55">
         <v>1000</v>
@@ -14381,58 +14381,58 @@
         <v>1000</v>
       </c>
       <c r="AP55">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AQ55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AR55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AS55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AT55">
-        <v>1.59</v>
+        <v>5.5</v>
       </c>
       <c r="AU55">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AV55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AW55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AX55">
-        <v>8.4</v>
+        <v>1.67</v>
       </c>
       <c r="AY55">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="AZ55">
         <v>16</v>
       </c>
       <c r="BA55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="BB55">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BC55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="BD55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="BE55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="BF55">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BG55">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14766,10 +14766,10 @@
         <v>2.84</v>
       </c>
       <c r="I57">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="J57">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K57">
         <v>7.8</v>
@@ -14790,13 +14790,13 @@
         <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R57">
         <v>1.61</v>
       </c>
       <c r="S57">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="T57">
         <v>1.01</v>
@@ -14805,7 +14805,7 @@
         <v>1.01</v>
       </c>
       <c r="V57">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
         <v>1.79</v>
@@ -15047,10 +15047,10 @@
         <v>1.01</v>
       </c>
       <c r="V58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
         <v>1000</v>
@@ -15289,10 +15289,10 @@
         <v>1.01</v>
       </c>
       <c r="V59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -15525,16 +15525,16 @@
         <v>2.96</v>
       </c>
       <c r="T60">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U60">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V60">
         <v>1.33</v>
       </c>
       <c r="W60">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X60">
         <v>21</v>
@@ -15725,7 +15725,7 @@
         <v>263</v>
       </c>
       <c r="F61">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G61">
         <v>1.45</v>
@@ -15734,13 +15734,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I61">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J61">
         <v>5.3</v>
       </c>
       <c r="K61">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L61">
         <v>1.26</v>
@@ -15785,10 +15785,10 @@
         <v>38</v>
       </c>
       <c r="Z61">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA61">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AB61">
         <v>12</v>
@@ -15806,7 +15806,7 @@
         <v>11</v>
       </c>
       <c r="AG61">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH61">
         <v>22</v>
@@ -15842,7 +15842,7 @@
         <v>60</v>
       </c>
       <c r="AS61">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT61">
         <v>11</v>
@@ -15854,19 +15854,19 @@
         <v>26</v>
       </c>
       <c r="AW61">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AX61">
         <v>9.800000000000001</v>
       </c>
       <c r="AY61">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ61">
         <v>19</v>
       </c>
       <c r="BA61">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BB61">
         <v>12</v>
@@ -15878,13 +15878,13 @@
         <v>23</v>
       </c>
       <c r="BE61">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF61">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG61">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH61">
         <v>1000</v>
@@ -15920,13 +15920,13 @@
         <v>1000</v>
       </c>
       <c r="BS61">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BT61">
         <v>1000</v>
       </c>
       <c r="BU61">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BV61">
         <v>1000</v>
@@ -15970,13 +15970,13 @@
         <v>3.15</v>
       </c>
       <c r="G62">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H62">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I62">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J62">
         <v>3.4</v>
@@ -16000,13 +16000,13 @@
         <v>1.82</v>
       </c>
       <c r="Q62">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R62">
         <v>1.32</v>
       </c>
       <c r="S62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T62">
         <v>1.86</v>
@@ -16018,7 +16018,7 @@
         <v>1.64</v>
       </c>
       <c r="W62">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X62">
         <v>13</v>
@@ -16069,7 +16069,7 @@
         <v>110</v>
       </c>
       <c r="AN62">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO62">
         <v>25</v>
@@ -16078,10 +16078,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ62">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR62">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS62">
         <v>32</v>
@@ -16096,7 +16096,7 @@
         <v>10.5</v>
       </c>
       <c r="AW62">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX62">
         <v>19</v>
@@ -16108,7 +16108,7 @@
         <v>18</v>
       </c>
       <c r="BA62">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB62">
         <v>50</v>
@@ -16120,19 +16120,19 @@
         <v>46</v>
       </c>
       <c r="BE62">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF62">
         <v>34</v>
       </c>
       <c r="BG62">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH62">
         <v>3.55</v>
       </c>
       <c r="BI62">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ62">
         <v>1000</v>
@@ -16215,31 +16215,31 @@
         <v>2.6</v>
       </c>
       <c r="H63">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I63">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J63">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K63">
         <v>3.95</v>
       </c>
       <c r="L63">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M63">
         <v>1.04</v>
       </c>
       <c r="N63">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O63">
         <v>1.17</v>
       </c>
       <c r="P63">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q63">
         <v>1.53</v>
@@ -16248,7 +16248,7 @@
         <v>1.74</v>
       </c>
       <c r="S63">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T63">
         <v>1.47</v>
@@ -16302,7 +16302,7 @@
         <v>38</v>
       </c>
       <c r="AK63">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL63">
         <v>28</v>
@@ -16475,7 +16475,7 @@
         <v>1.09</v>
       </c>
       <c r="N64">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O64">
         <v>1.41</v>
@@ -16490,10 +16490,10 @@
         <v>1.28</v>
       </c>
       <c r="S64">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T64">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U64">
         <v>1.93</v>
@@ -16538,10 +16538,10 @@
         <v>24</v>
       </c>
       <c r="AI64">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ64">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK64">
         <v>29</v>
@@ -16565,10 +16565,10 @@
         <v>12</v>
       </c>
       <c r="AR64">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS64">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT64">
         <v>7</v>
@@ -16580,7 +16580,7 @@
         <v>16</v>
       </c>
       <c r="AW64">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AX64">
         <v>10</v>
@@ -16592,25 +16592,25 @@
         <v>18</v>
       </c>
       <c r="BA64">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB64">
         <v>20</v>
       </c>
       <c r="BC64">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BD64">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE64">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF64">
         <v>15</v>
       </c>
       <c r="BG64">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH64">
         <v>1000</v>
@@ -16693,76 +16693,76 @@
         <v>267</v>
       </c>
       <c r="F65">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G65">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="H65">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I65">
         <v>11.5</v>
       </c>
       <c r="J65">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="K65">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L65">
         <v>1.01</v>
       </c>
       <c r="M65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N65">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O65">
         <v>1.32</v>
       </c>
       <c r="P65">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="Q65">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="R65">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S65">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T65">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U65">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V65">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W65">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="X65">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y65">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z65">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA65">
         <v>470</v>
       </c>
       <c r="AB65">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC65">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD65">
         <v>42</v>
@@ -16795,10 +16795,10 @@
         <v>250</v>
       </c>
       <c r="AN65">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AO65">
-        <v>370</v>
+        <v>440</v>
       </c>
       <c r="AP65">
         <v>1.03</v>
@@ -16816,7 +16816,7 @@
         <v>1.03</v>
       </c>
       <c r="AU65">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV65">
         <v>1.03</v>
@@ -16825,10 +16825,10 @@
         <v>1.03</v>
       </c>
       <c r="AX65">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY65">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ65">
         <v>1.03</v>
@@ -16840,19 +16840,19 @@
         <v>1.03</v>
       </c>
       <c r="BC65">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD65">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE65">
         <v>1.03</v>
       </c>
       <c r="BF65">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG65">
-        <v>230</v>
+        <v>1.01</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16947,7 +16947,7 @@
         <v>4.4</v>
       </c>
       <c r="J66">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K66">
         <v>3.35</v>
@@ -16959,13 +16959,13 @@
         <v>1.11</v>
       </c>
       <c r="N66">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O66">
         <v>1.5</v>
       </c>
       <c r="P66">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q66">
         <v>2.46</v>
@@ -17180,7 +17180,7 @@
         <v>2.16</v>
       </c>
       <c r="G67">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="H67">
         <v>2.72</v>
@@ -17204,7 +17204,7 @@
         <v>2.54</v>
       </c>
       <c r="O67">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P67">
         <v>1.5</v>
@@ -17228,7 +17228,7 @@
         <v>1.28</v>
       </c>
       <c r="W67">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17927,13 +17927,13 @@
         <v>1.09</v>
       </c>
       <c r="N70">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O70">
         <v>1.42</v>
       </c>
       <c r="P70">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q70">
         <v>2.18</v>
@@ -18393,7 +18393,7 @@
         <v>1.78</v>
       </c>
       <c r="H72">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I72">
         <v>7</v>
@@ -18402,7 +18402,7 @@
         <v>3.55</v>
       </c>
       <c r="K72">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L72">
         <v>1.45</v>
@@ -18417,16 +18417,16 @@
         <v>1.44</v>
       </c>
       <c r="P72">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="Q72">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R72">
         <v>1.21</v>
       </c>
       <c r="S72">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T72">
         <v>2.18</v>
@@ -18465,7 +18465,7 @@
         <v>150</v>
       </c>
       <c r="AF72">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG72">
         <v>10.5</v>
@@ -18480,7 +18480,7 @@
         <v>18</v>
       </c>
       <c r="AK72">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL72">
         <v>60</v>
@@ -18513,7 +18513,7 @@
         <v>7.4</v>
       </c>
       <c r="AV72">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW72">
         <v>9.6</v>
@@ -18540,7 +18540,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE72">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF72">
         <v>13.5</v>
@@ -19116,7 +19116,7 @@
         <v>2.9</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H75">
         <v>2.26</v>
@@ -19137,28 +19137,28 @@
         <v>1.02</v>
       </c>
       <c r="N75">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O75">
         <v>1.12</v>
       </c>
       <c r="P75">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q75">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S75">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="T75">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U75">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V75">
         <v>1.75</v>
@@ -19167,10 +19167,10 @@
         <v>1.49</v>
       </c>
       <c r="X75">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="Y75">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z75">
         <v>24</v>
@@ -19179,28 +19179,28 @@
         <v>34</v>
       </c>
       <c r="AB75">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC75">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD75">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE75">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF75">
         <v>32</v>
       </c>
       <c r="AG75">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH75">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI75">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ75">
         <v>65</v>
@@ -19209,16 +19209,16 @@
         <v>28</v>
       </c>
       <c r="AL75">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM75">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AN75">
         <v>12</v>
       </c>
       <c r="AO75">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP75">
         <v>25</v>
@@ -19233,28 +19233,28 @@
         <v>21</v>
       </c>
       <c r="AT75">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU75">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV75">
         <v>11.5</v>
       </c>
       <c r="AW75">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX75">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY75">
         <v>13</v>
       </c>
       <c r="AZ75">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA75">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB75">
         <v>29</v>
@@ -19263,16 +19263,16 @@
         <v>17.5</v>
       </c>
       <c r="BD75">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BE75">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BF75">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG75">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH75">
         <v>1000</v>
@@ -19358,10 +19358,10 @@
         <v>3.45</v>
       </c>
       <c r="G76">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H76">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I76">
         <v>2.46</v>
@@ -19385,7 +19385,7 @@
         <v>1.42</v>
       </c>
       <c r="P76">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q76">
         <v>2.24</v>
